--- a/AAII_Financials/Quarterly/RVSN_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/RVSN_QTR_FIN.xlsx
@@ -5,7 +5,7 @@
   <workbookPr codeName="ThisWorkbook" defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\sundeep\Stocks_Automation\AAII_Financials\Quarterly\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\sundeep\Private\Investing\Automation\AAII\AAII_Financials\Quarterly\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
@@ -17,12 +17,12 @@
   <definedNames>
     <definedName name="Ticker">#REF!</definedName>
   </definedNames>
-  <calcPr calcId="152511" calcMode="manual" concurrentCalc="0"/>
+  <calcPr calcId="152511" calcMode="manual"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="295" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="291" uniqueCount="92">
   <si>
     <t>RVSN</t>
   </si>
@@ -656,85 +656,89 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:P102"/>
+  <dimension ref="A5:Q102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="7.5703125" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="7" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="16" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="8" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="17" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:17" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:17" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45199</v>
+      </c>
+      <c r="E7" s="2">
         <v>45107</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45016</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>44926</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>44834</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>44742</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>44651</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>44561</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>44377</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>44196</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>44012</v>
       </c>
-      <c r="N7" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="O7" s="2" t="s">
         <v>3</v>
       </c>
       <c r="P7" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="8" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="Q7" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="8" spans="1:17" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D8" s="3" t="s">
-        <v>3</v>
+      <c r="D8" s="3">
+        <v>100</v>
       </c>
       <c r="E8" s="3">
         <v>0</v>
@@ -743,28 +747,28 @@
         <v>0</v>
       </c>
       <c r="G8" s="3">
+        <v>0</v>
+      </c>
+      <c r="H8" s="3">
         <v>200</v>
       </c>
-      <c r="H8" s="3">
-        <v>0</v>
-      </c>
       <c r="I8" s="3">
+        <v>0</v>
+      </c>
+      <c r="J8" s="3">
         <v>200</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>900</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>400</v>
       </c>
-      <c r="L8" s="3">
-        <v>0</v>
-      </c>
       <c r="M8" s="3">
         <v>0</v>
       </c>
-      <c r="N8" s="3" t="s">
-        <v>3</v>
+      <c r="N8" s="3">
+        <v>0</v>
       </c>
       <c r="O8" s="3" t="s">
         <v>3</v>
@@ -772,13 +776,16 @@
       <c r="P8" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="9" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="Q8" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="9" spans="1:17" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="D9" s="3" t="s">
-        <v>3</v>
+      <c r="D9" s="3">
+        <v>100</v>
       </c>
       <c r="E9" s="3" t="s">
         <v>3</v>
@@ -786,24 +793,24 @@
       <c r="F9" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="G9" s="3">
+      <c r="G9" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="H9" s="3">
         <v>300</v>
       </c>
-      <c r="H9" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="I9" s="3">
+      <c r="I9" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="J9" s="3">
         <v>400</v>
       </c>
-      <c r="J9" s="3">
+      <c r="K9" s="3">
         <v>700</v>
       </c>
-      <c r="K9" s="3">
+      <c r="L9" s="3">
         <v>100</v>
       </c>
-      <c r="L9" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="M9" s="3" t="s">
         <v>3</v>
       </c>
@@ -816,13 +823,16 @@
       <c r="P9" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="10" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="Q9" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="10" spans="1:17" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="D10" s="3" t="s">
-        <v>3</v>
+      <c r="D10" s="3">
+        <v>0</v>
       </c>
       <c r="E10" s="3" t="s">
         <v>3</v>
@@ -830,24 +840,24 @@
       <c r="F10" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="G10" s="3">
+      <c r="G10" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="H10" s="3">
         <v>-100</v>
       </c>
-      <c r="H10" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="I10" s="3">
+      <c r="I10" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="J10" s="3">
         <v>-200</v>
       </c>
-      <c r="J10" s="3">
+      <c r="K10" s="3">
         <v>200</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>300</v>
       </c>
-      <c r="L10" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="M10" s="3" t="s">
         <v>3</v>
       </c>
@@ -860,8 +870,11 @@
       <c r="P10" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="11" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="Q10" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="11" spans="1:17" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -878,52 +891,56 @@
       <c r="N11" s="3"/>
       <c r="O11" s="3"/>
       <c r="P11" s="3"/>
-    </row>
-    <row r="12" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="Q11" s="3"/>
+    </row>
+    <row r="12" spans="1:17" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
       <c r="D12" s="3">
-        <v>1800</v>
+        <v>1900</v>
       </c>
       <c r="E12" s="3">
         <v>1800</v>
       </c>
       <c r="F12" s="3">
+        <v>1800</v>
+      </c>
+      <c r="G12" s="3">
         <v>1500</v>
-      </c>
-      <c r="G12" s="3">
-        <v>1700</v>
       </c>
       <c r="H12" s="3">
         <v>1700</v>
       </c>
       <c r="I12" s="3">
+        <v>1700</v>
+      </c>
+      <c r="J12" s="3">
         <v>1400</v>
       </c>
-      <c r="J12" s="3">
+      <c r="K12" s="3">
         <v>7200</v>
       </c>
-      <c r="K12" s="3">
+      <c r="L12" s="3">
         <v>3800</v>
       </c>
-      <c r="L12" s="3">
+      <c r="M12" s="3">
         <v>7200</v>
       </c>
-      <c r="M12" s="3">
+      <c r="N12" s="3">
         <v>3600</v>
       </c>
-      <c r="N12" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="O12" s="3" t="s">
         <v>3</v>
       </c>
       <c r="P12" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="13" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="Q12" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="13" spans="1:17" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -966,8 +983,11 @@
       <c r="P13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="Q13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:17" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
@@ -1010,8 +1030,11 @@
       <c r="P14" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="15" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="Q14" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:17" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
@@ -1054,8 +1077,11 @@
       <c r="P15" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="16" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="Q15" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:17" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1069,8 +1095,9 @@
       <c r="N16" s="3"/>
       <c r="O16" s="3"/>
       <c r="P16" s="3"/>
-    </row>
-    <row r="17" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q16" s="3"/>
+    </row>
+    <row r="17" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
@@ -1081,84 +1108,90 @@
         <v>3000</v>
       </c>
       <c r="F17" s="3">
+        <v>3000</v>
+      </c>
+      <c r="G17" s="3">
         <v>2600</v>
-      </c>
-      <c r="G17" s="3">
-        <v>3000</v>
       </c>
       <c r="H17" s="3">
         <v>3000</v>
       </c>
       <c r="I17" s="3">
+        <v>3000</v>
+      </c>
+      <c r="J17" s="3">
         <v>2600</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>11200</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>5700</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>10700</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>5100</v>
       </c>
-      <c r="N17" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="O17" s="3" t="s">
         <v>3</v>
       </c>
       <c r="P17" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="18" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q17" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="18" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="D18" s="3" t="s">
-        <v>3</v>
+      <c r="D18" s="3">
+        <v>-2900</v>
       </c>
       <c r="E18" s="3">
         <v>-3000</v>
       </c>
       <c r="F18" s="3">
+        <v>-3000</v>
+      </c>
+      <c r="G18" s="3">
         <v>-2600</v>
       </c>
-      <c r="G18" s="3">
+      <c r="H18" s="3">
         <v>-2800</v>
       </c>
-      <c r="H18" s="3">
+      <c r="I18" s="3">
         <v>-3000</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>-2400</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>-10300</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>-5300</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>-10700</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>-5100</v>
       </c>
-      <c r="N18" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="O18" s="3" t="s">
         <v>3</v>
       </c>
       <c r="P18" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="19" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q18" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="19" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1175,43 +1208,44 @@
       <c r="N19" s="3"/>
       <c r="O19" s="3"/>
       <c r="P19" s="3"/>
-    </row>
-    <row r="20" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q19" s="3"/>
+    </row>
+    <row r="20" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="D20" s="3" t="s">
-        <v>3</v>
+      <c r="D20" s="3">
+        <v>100</v>
       </c>
       <c r="E20" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="F20" s="3">
         <v>100</v>
       </c>
       <c r="G20" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="H20" s="3">
+        <v>0</v>
+      </c>
+      <c r="I20" s="3">
         <v>100</v>
       </c>
-      <c r="I20" s="3">
-        <v>0</v>
-      </c>
       <c r="J20" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="K20" s="3">
         <v>100</v>
       </c>
       <c r="L20" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="M20" s="3">
         <v>0</v>
       </c>
-      <c r="N20" s="3" t="s">
-        <v>3</v>
+      <c r="N20" s="3">
+        <v>0</v>
       </c>
       <c r="O20" s="3" t="s">
         <v>3</v>
@@ -1219,52 +1253,58 @@
       <c r="P20" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="21" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q20" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="21" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="D21" s="3" t="s">
-        <v>3</v>
+      <c r="D21" s="3">
+        <v>-2700</v>
       </c>
       <c r="E21" s="3">
+        <v>-2900</v>
+      </c>
+      <c r="F21" s="3">
         <v>-2800</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>-2400</v>
       </c>
-      <c r="G21" s="3">
+      <c r="H21" s="3">
         <v>-2700</v>
       </c>
-      <c r="H21" s="3">
+      <c r="I21" s="3">
         <v>-2900</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>-2300</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>-10100</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>-5100</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>-10500</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>-5000</v>
       </c>
-      <c r="N21" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="O21" s="3" t="s">
         <v>3</v>
       </c>
       <c r="P21" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="22" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q21" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="22" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
@@ -1307,52 +1347,58 @@
       <c r="P22" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="23" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q22" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>-2800</v>
+      </c>
+      <c r="E23" s="3">
         <v>-3000</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>-2900</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>-2500</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>-2800</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>-2900</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>-2300</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>-10200</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>-5100</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>-10700</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>-5100</v>
       </c>
-      <c r="N23" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="O23" s="3" t="s">
         <v>3</v>
       </c>
       <c r="P23" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="24" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q23" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="24" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
@@ -1395,8 +1441,11 @@
       <c r="P24" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="25" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q24" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -1439,96 +1488,105 @@
       <c r="P25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>-2800</v>
+      </c>
+      <c r="E26" s="3">
         <v>-3000</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>-2900</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>-2500</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>-2800</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>-2900</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>-2300</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>-10200</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>-5100</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>-10700</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>-5100</v>
       </c>
-      <c r="N26" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="O26" s="3" t="s">
         <v>3</v>
       </c>
       <c r="P26" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="27" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q26" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="27" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>-2800</v>
+      </c>
+      <c r="E27" s="3">
         <v>-3000</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>-2900</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>-2500</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>-2800</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>-2900</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>-2300</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>-10200</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>-5100</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>-10700</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>-5100</v>
       </c>
-      <c r="N27" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="O27" s="3" t="s">
         <v>3</v>
       </c>
       <c r="P27" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="28" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q27" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="28" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -1571,8 +1629,11 @@
       <c r="P28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -1615,8 +1676,11 @@
       <c r="P29" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="30" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q29" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -1659,8 +1723,11 @@
       <c r="P30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -1703,43 +1770,46 @@
       <c r="P31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
-      <c r="D32" s="3" t="s">
-        <v>3</v>
+      <c r="D32" s="3">
+        <v>-100</v>
       </c>
       <c r="E32" s="3">
-        <v>-100</v>
+        <v>0</v>
       </c>
       <c r="F32" s="3">
         <v>-100</v>
       </c>
       <c r="G32" s="3">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="H32" s="3">
+        <v>0</v>
+      </c>
+      <c r="I32" s="3">
         <v>-100</v>
       </c>
-      <c r="I32" s="3">
-        <v>0</v>
-      </c>
       <c r="J32" s="3">
-        <v>-100</v>
+        <v>0</v>
       </c>
       <c r="K32" s="3">
         <v>-100</v>
       </c>
       <c r="L32" s="3">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="M32" s="3">
         <v>0</v>
       </c>
-      <c r="N32" s="3" t="s">
-        <v>3</v>
+      <c r="N32" s="3">
+        <v>0</v>
       </c>
       <c r="O32" s="3" t="s">
         <v>3</v>
@@ -1747,52 +1817,58 @@
       <c r="P32" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="33" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q32" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="33" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>-2800</v>
+      </c>
+      <c r="E33" s="3">
         <v>-3000</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>-2900</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>-2500</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>-2800</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>-2900</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>-2300</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>-10200</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>-5100</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>-10700</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>-5100</v>
       </c>
-      <c r="N33" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="O33" s="3" t="s">
         <v>3</v>
       </c>
       <c r="P33" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="34" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q33" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="34" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -1835,101 +1911,110 @@
       <c r="P34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>-2800</v>
+      </c>
+      <c r="E35" s="3">
         <v>-3000</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>-2900</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>-2500</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>-2800</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>-2900</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>-2300</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>-10200</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>-5100</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>-10700</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>-5100</v>
       </c>
-      <c r="N35" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="O35" s="3" t="s">
         <v>3</v>
       </c>
       <c r="P35" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="37" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q35" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="37" spans="2:17" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:16" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45199</v>
+      </c>
+      <c r="E38" s="2">
         <v>45107</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45016</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>44926</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>44834</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>44742</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>44651</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>44561</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>44377</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>44196</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>44012</v>
       </c>
-      <c r="N38" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="O38" s="2" t="s">
         <v>3</v>
       </c>
       <c r="P38" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="39" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q38" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="39" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -1946,8 +2031,9 @@
       <c r="N39" s="3"/>
       <c r="O39" s="3"/>
       <c r="P39" s="3"/>
-    </row>
-    <row r="40" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q39" s="3"/>
+    </row>
+    <row r="40" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -1964,32 +2050,33 @@
       <c r="N40" s="3"/>
       <c r="O40" s="3"/>
       <c r="P40" s="3"/>
-    </row>
-    <row r="41" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q40" s="3"/>
+    </row>
+    <row r="41" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>4900</v>
+      </c>
+      <c r="E41" s="3">
         <v>8200</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>5600</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>8300</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>10400</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>12900</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>2200</v>
       </c>
-      <c r="J41" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="K41" s="3" t="s">
         <v>3</v>
       </c>
@@ -2008,8 +2095,11 @@
       <c r="P41" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="42" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q41" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="42" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
@@ -2052,31 +2142,34 @@
       <c r="P42" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="43" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q42" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
-      <c r="D43" s="3" t="s">
-        <v>3</v>
+      <c r="D43" s="3">
+        <v>0</v>
       </c>
       <c r="E43" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="F43" s="3">
-        <v>100</v>
+      <c r="F43" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="G43" s="3">
         <v>100</v>
       </c>
-      <c r="H43" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="I43" s="3">
+      <c r="H43" s="3">
         <v>100</v>
       </c>
-      <c r="J43" s="3" t="s">
-        <v>3</v>
+      <c r="I43" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="J43" s="3">
+        <v>100</v>
       </c>
       <c r="K43" s="3" t="s">
         <v>3</v>
@@ -2096,20 +2189,23 @@
       <c r="P43" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="44" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q43" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="44" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
       <c r="D44" s="3">
+        <v>1000</v>
+      </c>
+      <c r="E44" s="3">
         <v>500</v>
       </c>
-      <c r="E44" s="3">
+      <c r="F44" s="3">
         <v>100</v>
       </c>
-      <c r="F44" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="G44" s="3" t="s">
         <v>3</v>
       </c>
@@ -2122,8 +2218,8 @@
       <c r="J44" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="K44" s="3">
-        <v>0</v>
+      <c r="K44" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="L44" s="3">
         <v>0</v>
@@ -2140,31 +2236,34 @@
       <c r="P44" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="45" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q44" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="45" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
-        <v>600</v>
+        <v>500</v>
       </c>
       <c r="E45" s="3">
         <v>600</v>
       </c>
       <c r="F45" s="3">
+        <v>600</v>
+      </c>
+      <c r="G45" s="3">
         <v>400</v>
       </c>
-      <c r="G45" s="3">
+      <c r="H45" s="3">
         <v>700</v>
-      </c>
-      <c r="H45" s="3">
-        <v>1000</v>
       </c>
       <c r="I45" s="3">
         <v>1000</v>
       </c>
-      <c r="J45" s="3" t="s">
-        <v>3</v>
+      <c r="J45" s="3">
+        <v>1000</v>
       </c>
       <c r="K45" s="3" t="s">
         <v>3</v>
@@ -2184,32 +2283,35 @@
       <c r="P45" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="46" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q45" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="46" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>6400</v>
+      </c>
+      <c r="E46" s="3">
         <v>9300</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>6300</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>8800</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>11200</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>14000</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>3300</v>
       </c>
-      <c r="J46" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="K46" s="3" t="s">
         <v>3</v>
       </c>
@@ -2228,8 +2330,11 @@
       <c r="P46" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="47" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q46" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="47" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
@@ -2272,32 +2377,35 @@
       <c r="P47" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="48" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q47" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="48" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>1400</v>
+      </c>
+      <c r="E48" s="3">
         <v>1500</v>
-      </c>
-      <c r="E48" s="3">
-        <v>1600</v>
       </c>
       <c r="F48" s="3">
         <v>1600</v>
       </c>
       <c r="G48" s="3">
+        <v>1600</v>
+      </c>
+      <c r="H48" s="3">
         <v>1700</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>1800</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>1900</v>
       </c>
-      <c r="J48" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="K48" s="3" t="s">
         <v>3</v>
       </c>
@@ -2316,8 +2424,11 @@
       <c r="P48" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="49" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q48" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="49" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
@@ -2360,8 +2471,11 @@
       <c r="P49" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="50" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q49" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="50" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -2404,8 +2518,11 @@
       <c r="P50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -2448,8 +2565,11 @@
       <c r="P51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
@@ -2492,8 +2612,11 @@
       <c r="P52" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="53" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q52" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="53" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -2536,32 +2659,35 @@
       <c r="P53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>7900</v>
+      </c>
+      <c r="E54" s="3">
         <v>10800</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>7900</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>10400</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>12900</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>15700</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>5200</v>
       </c>
-      <c r="J54" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="K54" s="3" t="s">
         <v>3</v>
       </c>
@@ -2580,8 +2706,11 @@
       <c r="P54" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="55" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q54" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="55" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -2598,8 +2727,9 @@
       <c r="N55" s="3"/>
       <c r="O55" s="3"/>
       <c r="P55" s="3"/>
-    </row>
-    <row r="56" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q55" s="3"/>
+    </row>
+    <row r="56" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -2616,19 +2746,20 @@
       <c r="N56" s="3"/>
       <c r="O56" s="3"/>
       <c r="P56" s="3"/>
-    </row>
-    <row r="57" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q56" s="3"/>
+    </row>
+    <row r="57" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
-        <v>200</v>
+        <v>300</v>
       </c>
       <c r="E57" s="3">
         <v>200</v>
       </c>
       <c r="F57" s="3">
-        <v>100</v>
+        <v>200</v>
       </c>
       <c r="G57" s="3">
         <v>100</v>
@@ -2639,8 +2770,8 @@
       <c r="I57" s="3">
         <v>100</v>
       </c>
-      <c r="J57" s="3" t="s">
-        <v>3</v>
+      <c r="J57" s="3">
+        <v>100</v>
       </c>
       <c r="K57" s="3" t="s">
         <v>3</v>
@@ -2660,8 +2791,11 @@
       <c r="P57" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="58" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q57" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="58" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
@@ -2680,12 +2814,12 @@
       <c r="H58" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="I58" s="3">
+      <c r="I58" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="J58" s="3">
         <v>1000</v>
       </c>
-      <c r="J58" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="K58" s="3" t="s">
         <v>3</v>
       </c>
@@ -2704,32 +2838,35 @@
       <c r="P58" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="59" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q58" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="59" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>1800</v>
+      </c>
+      <c r="E59" s="3">
         <v>2000</v>
       </c>
-      <c r="E59" s="3">
+      <c r="F59" s="3">
         <v>1500</v>
-      </c>
-      <c r="F59" s="3">
-        <v>1300</v>
       </c>
       <c r="G59" s="3">
         <v>1300</v>
       </c>
       <c r="H59" s="3">
+        <v>1300</v>
+      </c>
+      <c r="I59" s="3">
         <v>1400</v>
       </c>
-      <c r="I59" s="3">
+      <c r="J59" s="3">
         <v>1600</v>
       </c>
-      <c r="J59" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="K59" s="3" t="s">
         <v>3</v>
       </c>
@@ -2748,32 +2885,35 @@
       <c r="P59" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="60" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q59" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="60" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>2000</v>
+      </c>
+      <c r="E60" s="3">
         <v>2200</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>1800</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>1400</v>
-      </c>
-      <c r="G60" s="3">
-        <v>1500</v>
       </c>
       <c r="H60" s="3">
         <v>1500</v>
       </c>
       <c r="I60" s="3">
+        <v>1500</v>
+      </c>
+      <c r="J60" s="3">
         <v>2700</v>
       </c>
-      <c r="J60" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="K60" s="3" t="s">
         <v>3</v>
       </c>
@@ -2792,8 +2932,11 @@
       <c r="P60" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="61" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q60" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="61" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
@@ -2836,32 +2979,35 @@
       <c r="P61" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="62" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q61" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
+        <v>500</v>
+      </c>
+      <c r="E62" s="3">
         <v>600</v>
       </c>
-      <c r="E62" s="3">
+      <c r="F62" s="3">
         <v>700</v>
-      </c>
-      <c r="F62" s="3">
-        <v>800</v>
       </c>
       <c r="G62" s="3">
         <v>800</v>
       </c>
       <c r="H62" s="3">
+        <v>800</v>
+      </c>
+      <c r="I62" s="3">
         <v>900</v>
       </c>
-      <c r="I62" s="3">
+      <c r="J62" s="3">
         <v>1100</v>
       </c>
-      <c r="J62" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="K62" s="3" t="s">
         <v>3</v>
       </c>
@@ -2880,8 +3026,11 @@
       <c r="P62" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="63" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q62" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="63" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -2924,8 +3073,11 @@
       <c r="P63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -2968,8 +3120,11 @@
       <c r="P64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -3012,32 +3167,35 @@
       <c r="P65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>2600</v>
+      </c>
+      <c r="E66" s="3">
         <v>2800</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>2500</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>2200</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>2300</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>2500</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>3800</v>
       </c>
-      <c r="J66" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="K66" s="3" t="s">
         <v>3</v>
       </c>
@@ -3056,8 +3214,11 @@
       <c r="P66" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="67" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q66" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="67" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -3074,8 +3235,9 @@
       <c r="N67" s="3"/>
       <c r="O67" s="3"/>
       <c r="P67" s="3"/>
-    </row>
-    <row r="68" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q67" s="3"/>
+    </row>
+    <row r="68" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -3118,8 +3280,11 @@
       <c r="P68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -3162,8 +3327,11 @@
       <c r="P69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -3183,11 +3351,11 @@
         <v>0</v>
       </c>
       <c r="I70" s="3">
+        <v>0</v>
+      </c>
+      <c r="J70" s="3">
         <v>12000</v>
       </c>
-      <c r="J70" s="3">
-        <v>0</v>
-      </c>
       <c r="K70" s="3">
         <v>0</v>
       </c>
@@ -3206,8 +3374,11 @@
       <c r="P70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -3250,32 +3421,35 @@
       <c r="P71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>-63400</v>
+      </c>
+      <c r="E72" s="3">
         <v>-60600</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>-57700</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>-54800</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>-52400</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>-49600</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>-46700</v>
       </c>
-      <c r="J72" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="K72" s="3" t="s">
         <v>3</v>
       </c>
@@ -3294,8 +3468,11 @@
       <c r="P72" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="73" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q72" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="73" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -3338,8 +3515,11 @@
       <c r="P73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -3382,8 +3562,11 @@
       <c r="P74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -3426,32 +3609,35 @@
       <c r="P75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>5300</v>
+      </c>
+      <c r="E76" s="3">
         <v>8000</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>5400</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>8300</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>10600</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>13300</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>-10500</v>
       </c>
-      <c r="J76" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="K76" s="3" t="s">
         <v>3</v>
       </c>
@@ -3470,8 +3656,11 @@
       <c r="P76" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="77" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q76" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="77" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -3514,101 +3703,110 @@
       <c r="P77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:17" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:16" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45199</v>
+      </c>
+      <c r="E80" s="2">
         <v>45107</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45016</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>44926</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>44834</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>44742</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>44651</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>44561</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>44377</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>44196</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>44012</v>
       </c>
-      <c r="N80" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="O80" s="2" t="s">
         <v>3</v>
       </c>
       <c r="P80" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="81" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q80" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="81" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>-2800</v>
+      </c>
+      <c r="E81" s="3">
         <v>-3000</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>-2900</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>-2500</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>-2800</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>-2900</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>-2300</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>-10200</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>-5100</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>-10700</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>-5100</v>
       </c>
-      <c r="N81" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="O81" s="3" t="s">
         <v>3</v>
       </c>
       <c r="P81" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="82" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q81" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="82" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -3625,8 +3823,9 @@
       <c r="N82" s="3"/>
       <c r="O82" s="3"/>
       <c r="P82" s="3"/>
-    </row>
-    <row r="83" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q82" s="3"/>
+    </row>
+    <row r="83" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
@@ -3649,28 +3848,31 @@
         <v>0</v>
       </c>
       <c r="J83" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="K83" s="3">
         <v>100</v>
       </c>
       <c r="L83" s="3">
+        <v>100</v>
+      </c>
+      <c r="M83" s="3">
         <v>200</v>
       </c>
-      <c r="M83" s="3">
+      <c r="N83" s="3">
         <v>100</v>
       </c>
-      <c r="N83" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="O83" s="3" t="s">
         <v>3</v>
       </c>
       <c r="P83" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="84" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q83" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="84" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -3713,8 +3915,11 @@
       <c r="P84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -3757,8 +3962,11 @@
       <c r="P85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -3801,8 +4009,11 @@
       <c r="P86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -3845,8 +4056,11 @@
       <c r="P87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -3889,52 +4103,58 @@
       <c r="P88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>-3200</v>
+      </c>
+      <c r="E89" s="3">
         <v>-2900</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>-2500</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>-2100</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>-2500</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>-2900</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>-2500</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>-9900</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>-5000</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>-7200</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>-4100</v>
       </c>
-      <c r="N89" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="O89" s="3" t="s">
         <v>3</v>
       </c>
       <c r="P89" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="90" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q89" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="90" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -3951,19 +4171,20 @@
       <c r="N90" s="3"/>
       <c r="O90" s="3"/>
       <c r="P90" s="3"/>
-    </row>
-    <row r="91" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q90" s="3"/>
+    </row>
+    <row r="91" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
-        <v>-100</v>
+        <v>0</v>
       </c>
       <c r="E91" s="3">
         <v>-100</v>
       </c>
       <c r="F91" s="3">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="G91" s="3">
         <v>0</v>
@@ -3975,28 +4196,31 @@
         <v>0</v>
       </c>
       <c r="J91" s="3">
+        <v>0</v>
+      </c>
+      <c r="K91" s="3">
         <v>-200</v>
       </c>
-      <c r="K91" s="3">
-        <v>0</v>
-      </c>
       <c r="L91" s="3">
         <v>0</v>
       </c>
       <c r="M91" s="3">
+        <v>0</v>
+      </c>
+      <c r="N91" s="3">
         <v>-100</v>
       </c>
-      <c r="N91" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="O91" s="3" t="s">
         <v>3</v>
       </c>
       <c r="P91" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="92" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q91" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="92" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -4039,8 +4263,11 @@
       <c r="P92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -4083,19 +4310,22 @@
       <c r="P93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
-        <v>-100</v>
+        <v>0</v>
       </c>
       <c r="E94" s="3">
         <v>-100</v>
       </c>
       <c r="F94" s="3">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="G94" s="3">
         <v>0</v>
@@ -4107,19 +4337,19 @@
         <v>0</v>
       </c>
       <c r="J94" s="3">
+        <v>0</v>
+      </c>
+      <c r="K94" s="3">
         <v>-300</v>
       </c>
-      <c r="K94" s="3">
-        <v>0</v>
-      </c>
       <c r="L94" s="3">
-        <v>-100</v>
+        <v>0</v>
       </c>
       <c r="M94" s="3">
         <v>-100</v>
       </c>
-      <c r="N94" s="3" t="s">
-        <v>3</v>
+      <c r="N94" s="3">
+        <v>-100</v>
       </c>
       <c r="O94" s="3" t="s">
         <v>3</v>
@@ -4127,8 +4357,11 @@
       <c r="P94" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="95" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q94" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="95" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -4145,8 +4378,9 @@
       <c r="N95" s="3"/>
       <c r="O95" s="3"/>
       <c r="P95" s="3"/>
-    </row>
-    <row r="96" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q95" s="3"/>
+    </row>
+    <row r="96" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -4189,8 +4423,11 @@
       <c r="P96" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="97" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q96" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -4233,8 +4470,11 @@
       <c r="P97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -4277,8 +4517,11 @@
       <c r="P98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -4321,17 +4564,20 @@
       <c r="P99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>-100</v>
+      </c>
+      <c r="E100" s="3">
         <v>5500</v>
       </c>
-      <c r="E100" s="3">
-        <v>0</v>
-      </c>
       <c r="F100" s="3">
         <v>0</v>
       </c>
@@ -4339,25 +4585,25 @@
         <v>0</v>
       </c>
       <c r="H100" s="3">
+        <v>0</v>
+      </c>
+      <c r="I100" s="3">
         <v>13600</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>3000</v>
-      </c>
-      <c r="J100" s="3">
-        <v>5100</v>
       </c>
       <c r="K100" s="3">
         <v>5100</v>
       </c>
       <c r="L100" s="3">
+        <v>5100</v>
+      </c>
+      <c r="M100" s="3">
         <v>5000</v>
       </c>
-      <c r="M100" s="3">
-        <v>0</v>
-      </c>
-      <c r="N100" s="3" t="s">
-        <v>3</v>
+      <c r="N100" s="3">
+        <v>0</v>
       </c>
       <c r="O100" s="3" t="s">
         <v>3</v>
@@ -4365,8 +4611,11 @@
       <c r="P100" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="101" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q100" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="101" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
@@ -4409,48 +4658,54 @@
       <c r="P101" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="102" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q101" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="102" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>-3300</v>
+      </c>
+      <c r="E102" s="3">
         <v>2500</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>-2600</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>-2200</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>-2500</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>10700</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>600</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>-5100</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>100</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>-2400</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>-4200</v>
       </c>
-      <c r="N102" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="O102" s="3" t="s">
         <v>3</v>
       </c>
       <c r="P102" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q102" s="3" t="s">
         <v>3</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/RVSN_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/RVSN_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="291" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="299" uniqueCount="92">
   <si>
     <t>RVSN</t>
   </si>
@@ -656,93 +656,96 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:Q102"/>
+  <dimension ref="A5:R102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="7.5703125" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="8" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="17" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="18" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="5" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="9" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="18" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="19" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:18" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:18" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45291</v>
+      </c>
+      <c r="E7" s="2">
         <v>45199</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45107</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45016</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>44926</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>44834</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>44742</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>44651</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>44561</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>44377</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>44196</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>44012</v>
       </c>
-      <c r="O7" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="P7" s="2" t="s">
         <v>3</v>
       </c>
       <c r="Q7" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="8" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="R7" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="8" spans="1:18" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D8" s="3">
+      <c r="D8" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="E8" s="3">
         <v>100</v>
       </c>
-      <c r="E8" s="3">
-        <v>0</v>
-      </c>
       <c r="F8" s="3">
         <v>0</v>
       </c>
@@ -750,28 +753,28 @@
         <v>0</v>
       </c>
       <c r="H8" s="3">
+        <v>0</v>
+      </c>
+      <c r="I8" s="3">
         <v>200</v>
       </c>
-      <c r="I8" s="3">
-        <v>0</v>
-      </c>
       <c r="J8" s="3">
+        <v>0</v>
+      </c>
+      <c r="K8" s="3">
         <v>200</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>900</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>400</v>
       </c>
-      <c r="M8" s="3">
-        <v>0</v>
-      </c>
       <c r="N8" s="3">
         <v>0</v>
       </c>
-      <c r="O8" s="3" t="s">
-        <v>3</v>
+      <c r="O8" s="3">
+        <v>0</v>
       </c>
       <c r="P8" s="3" t="s">
         <v>3</v>
@@ -779,41 +782,44 @@
       <c r="Q8" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="9" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="R8" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="9" spans="1:18" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="D9" s="3">
+      <c r="D9" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="E9" s="3">
         <v>100</v>
       </c>
-      <c r="E9" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="F9" s="3" t="s">
         <v>3</v>
       </c>
       <c r="G9" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="H9" s="3">
+      <c r="H9" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="I9" s="3">
         <v>300</v>
       </c>
-      <c r="I9" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="J9" s="3">
+      <c r="J9" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="K9" s="3">
         <v>400</v>
       </c>
-      <c r="K9" s="3">
+      <c r="L9" s="3">
         <v>700</v>
       </c>
-      <c r="L9" s="3">
+      <c r="M9" s="3">
         <v>100</v>
       </c>
-      <c r="M9" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="N9" s="3" t="s">
         <v>3</v>
       </c>
@@ -826,16 +832,19 @@
       <c r="Q9" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="10" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="R9" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="10" spans="1:18" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="D10" s="3">
-        <v>0</v>
-      </c>
-      <c r="E10" s="3" t="s">
-        <v>3</v>
+      <c r="D10" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="E10" s="3">
+        <v>0</v>
       </c>
       <c r="F10" s="3" t="s">
         <v>3</v>
@@ -843,24 +852,24 @@
       <c r="G10" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="H10" s="3">
+      <c r="H10" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="I10" s="3">
         <v>-100</v>
       </c>
-      <c r="I10" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="J10" s="3">
+      <c r="J10" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="K10" s="3">
         <v>-200</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>200</v>
       </c>
-      <c r="L10" s="3">
+      <c r="M10" s="3">
         <v>300</v>
       </c>
-      <c r="M10" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="N10" s="3" t="s">
         <v>3</v>
       </c>
@@ -873,8 +882,11 @@
       <c r="Q10" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="11" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="R10" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="11" spans="1:18" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -892,55 +904,59 @@
       <c r="O11" s="3"/>
       <c r="P11" s="3"/>
       <c r="Q11" s="3"/>
-    </row>
-    <row r="12" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="R11" s="3"/>
+    </row>
+    <row r="12" spans="1:18" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
       <c r="D12" s="3">
+        <v>1600</v>
+      </c>
+      <c r="E12" s="3">
         <v>1900</v>
-      </c>
-      <c r="E12" s="3">
-        <v>1800</v>
       </c>
       <c r="F12" s="3">
         <v>1800</v>
       </c>
       <c r="G12" s="3">
+        <v>1800</v>
+      </c>
+      <c r="H12" s="3">
         <v>1500</v>
-      </c>
-      <c r="H12" s="3">
-        <v>1700</v>
       </c>
       <c r="I12" s="3">
         <v>1700</v>
       </c>
       <c r="J12" s="3">
+        <v>1700</v>
+      </c>
+      <c r="K12" s="3">
         <v>1400</v>
       </c>
-      <c r="K12" s="3">
+      <c r="L12" s="3">
         <v>7200</v>
       </c>
-      <c r="L12" s="3">
+      <c r="M12" s="3">
         <v>3800</v>
       </c>
-      <c r="M12" s="3">
+      <c r="N12" s="3">
         <v>7200</v>
       </c>
-      <c r="N12" s="3">
+      <c r="O12" s="3">
         <v>3600</v>
       </c>
-      <c r="O12" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="P12" s="3" t="s">
         <v>3</v>
       </c>
       <c r="Q12" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="13" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="R12" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="13" spans="1:18" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -986,8 +1002,11 @@
       <c r="Q13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="R13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:18" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
@@ -1033,8 +1052,11 @@
       <c r="Q14" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="15" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="R14" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:18" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
@@ -1080,8 +1102,11 @@
       <c r="Q15" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="16" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="R15" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:18" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1096,13 +1121,14 @@
       <c r="O16" s="3"/>
       <c r="P16" s="3"/>
       <c r="Q16" s="3"/>
-    </row>
-    <row r="17" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R16" s="3"/>
+    </row>
+    <row r="17" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
-        <v>3000</v>
+        <v>2600</v>
       </c>
       <c r="E17" s="3">
         <v>3000</v>
@@ -1111,87 +1137,93 @@
         <v>3000</v>
       </c>
       <c r="G17" s="3">
+        <v>3000</v>
+      </c>
+      <c r="H17" s="3">
         <v>2600</v>
-      </c>
-      <c r="H17" s="3">
-        <v>3000</v>
       </c>
       <c r="I17" s="3">
         <v>3000</v>
       </c>
       <c r="J17" s="3">
+        <v>3000</v>
+      </c>
+      <c r="K17" s="3">
         <v>2600</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>11200</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>5700</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>10700</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>5100</v>
       </c>
-      <c r="O17" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="P17" s="3" t="s">
         <v>3</v>
       </c>
       <c r="Q17" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="18" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R17" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="18" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="D18" s="3">
+      <c r="D18" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="E18" s="3">
         <v>-2900</v>
-      </c>
-      <c r="E18" s="3">
-        <v>-3000</v>
       </c>
       <c r="F18" s="3">
         <v>-3000</v>
       </c>
       <c r="G18" s="3">
+        <v>-3000</v>
+      </c>
+      <c r="H18" s="3">
         <v>-2600</v>
       </c>
-      <c r="H18" s="3">
+      <c r="I18" s="3">
         <v>-2800</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>-3000</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>-2400</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>-10300</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>-5300</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>-10700</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>-5100</v>
       </c>
-      <c r="O18" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="P18" s="3" t="s">
         <v>3</v>
       </c>
       <c r="Q18" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="19" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R18" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="19" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1209,46 +1241,47 @@
       <c r="O19" s="3"/>
       <c r="P19" s="3"/>
       <c r="Q19" s="3"/>
-    </row>
-    <row r="20" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R19" s="3"/>
+    </row>
+    <row r="20" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="D20" s="3">
+      <c r="D20" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="E20" s="3">
         <v>100</v>
       </c>
-      <c r="E20" s="3">
-        <v>0</v>
-      </c>
       <c r="F20" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="G20" s="3">
         <v>100</v>
       </c>
       <c r="H20" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="I20" s="3">
+        <v>0</v>
+      </c>
+      <c r="J20" s="3">
         <v>100</v>
       </c>
-      <c r="J20" s="3">
-        <v>0</v>
-      </c>
       <c r="K20" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="L20" s="3">
         <v>100</v>
       </c>
       <c r="M20" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="N20" s="3">
         <v>0</v>
       </c>
-      <c r="O20" s="3" t="s">
-        <v>3</v>
+      <c r="O20" s="3">
+        <v>0</v>
       </c>
       <c r="P20" s="3" t="s">
         <v>3</v>
@@ -1256,55 +1289,61 @@
       <c r="Q20" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="21" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R20" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="21" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="D21" s="3">
+      <c r="D21" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="E21" s="3">
         <v>-2700</v>
       </c>
-      <c r="E21" s="3">
+      <c r="F21" s="3">
         <v>-2900</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>-2800</v>
       </c>
-      <c r="G21" s="3">
+      <c r="H21" s="3">
         <v>-2400</v>
       </c>
-      <c r="H21" s="3">
+      <c r="I21" s="3">
         <v>-2700</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>-2900</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>-2300</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>-10100</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>-5100</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>-10500</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>-5000</v>
       </c>
-      <c r="O21" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="P21" s="3" t="s">
         <v>3</v>
       </c>
       <c r="Q21" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="22" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R21" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="22" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
@@ -1350,55 +1389,61 @@
       <c r="Q22" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="23" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R22" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>-2500</v>
+      </c>
+      <c r="E23" s="3">
         <v>-2800</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>-3000</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>-2900</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>-2500</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>-2800</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>-2900</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>-2300</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>-10200</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>-5100</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>-10700</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>-5100</v>
       </c>
-      <c r="O23" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="P23" s="3" t="s">
         <v>3</v>
       </c>
       <c r="Q23" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="24" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R23" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="24" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
@@ -1444,8 +1489,11 @@
       <c r="Q24" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="25" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R24" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -1491,102 +1539,111 @@
       <c r="Q25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>-2500</v>
+      </c>
+      <c r="E26" s="3">
         <v>-2800</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>-3000</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>-2900</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>-2500</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>-2800</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>-2900</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>-2300</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>-10200</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>-5100</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>-10700</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>-5100</v>
       </c>
-      <c r="O26" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="P26" s="3" t="s">
         <v>3</v>
       </c>
       <c r="Q26" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="27" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R26" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="27" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>-2500</v>
+      </c>
+      <c r="E27" s="3">
         <v>-2800</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>-3000</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>-2900</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>-2500</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>-2800</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>-2900</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>-2300</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>-10200</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>-5100</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>-10700</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>-5100</v>
       </c>
-      <c r="O27" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="P27" s="3" t="s">
         <v>3</v>
       </c>
       <c r="Q27" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="28" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R27" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="28" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -1632,8 +1689,11 @@
       <c r="Q28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -1679,8 +1739,11 @@
       <c r="Q29" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="30" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R29" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -1726,8 +1789,11 @@
       <c r="Q30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -1773,46 +1839,49 @@
       <c r="Q31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
-      <c r="D32" s="3">
+      <c r="D32" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="E32" s="3">
         <v>-100</v>
       </c>
-      <c r="E32" s="3">
-        <v>0</v>
-      </c>
       <c r="F32" s="3">
-        <v>-100</v>
+        <v>0</v>
       </c>
       <c r="G32" s="3">
         <v>-100</v>
       </c>
       <c r="H32" s="3">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="I32" s="3">
+        <v>0</v>
+      </c>
+      <c r="J32" s="3">
         <v>-100</v>
       </c>
-      <c r="J32" s="3">
-        <v>0</v>
-      </c>
       <c r="K32" s="3">
-        <v>-100</v>
+        <v>0</v>
       </c>
       <c r="L32" s="3">
         <v>-100</v>
       </c>
       <c r="M32" s="3">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="N32" s="3">
         <v>0</v>
       </c>
-      <c r="O32" s="3" t="s">
-        <v>3</v>
+      <c r="O32" s="3">
+        <v>0</v>
       </c>
       <c r="P32" s="3" t="s">
         <v>3</v>
@@ -1820,55 +1889,61 @@
       <c r="Q32" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="33" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R32" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="33" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>-2500</v>
+      </c>
+      <c r="E33" s="3">
         <v>-2800</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>-3000</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>-2900</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>-2500</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>-2800</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>-2900</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>-2300</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>-10200</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>-5100</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>-10700</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>-5100</v>
       </c>
-      <c r="O33" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="P33" s="3" t="s">
         <v>3</v>
       </c>
       <c r="Q33" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="34" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R33" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="34" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -1914,107 +1989,116 @@
       <c r="Q34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>-2500</v>
+      </c>
+      <c r="E35" s="3">
         <v>-2800</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>-3000</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>-2900</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>-2500</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>-2800</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>-2900</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>-2300</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>-10200</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>-5100</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>-10700</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>-5100</v>
       </c>
-      <c r="O35" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="P35" s="3" t="s">
         <v>3</v>
       </c>
       <c r="Q35" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="37" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R35" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="37" spans="2:18" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:17" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45291</v>
+      </c>
+      <c r="E38" s="2">
         <v>45199</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45107</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45016</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>44926</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>44834</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>44742</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>44651</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>44561</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>44377</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>44196</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>44012</v>
       </c>
-      <c r="O38" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="P38" s="2" t="s">
         <v>3</v>
       </c>
       <c r="Q38" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="39" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R38" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="39" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -2032,8 +2116,9 @@
       <c r="O39" s="3"/>
       <c r="P39" s="3"/>
       <c r="Q39" s="3"/>
-    </row>
-    <row r="40" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R39" s="3"/>
+    </row>
+    <row r="40" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -2051,35 +2136,36 @@
       <c r="O40" s="3"/>
       <c r="P40" s="3"/>
       <c r="Q40" s="3"/>
-    </row>
-    <row r="41" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R40" s="3"/>
+    </row>
+    <row r="41" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>3100</v>
+      </c>
+      <c r="E41" s="3">
         <v>4900</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>8200</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>5600</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>8300</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>10400</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>12900</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>2200</v>
       </c>
-      <c r="K41" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="L41" s="3" t="s">
         <v>3</v>
       </c>
@@ -2098,8 +2184,11 @@
       <c r="Q41" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="42" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R41" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="42" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
@@ -2145,34 +2234,37 @@
       <c r="Q42" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="43" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R42" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
         <v>0</v>
       </c>
-      <c r="E43" s="3" t="s">
-        <v>3</v>
+      <c r="E43" s="3">
+        <v>0</v>
       </c>
       <c r="F43" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="G43" s="3">
-        <v>100</v>
+      <c r="G43" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="H43" s="3">
         <v>100</v>
       </c>
-      <c r="I43" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="J43" s="3">
+      <c r="I43" s="3">
         <v>100</v>
       </c>
-      <c r="K43" s="3" t="s">
-        <v>3</v>
+      <c r="J43" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="K43" s="3">
+        <v>100</v>
       </c>
       <c r="L43" s="3" t="s">
         <v>3</v>
@@ -2192,8 +2284,11 @@
       <c r="Q43" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="44" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R43" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="44" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
@@ -2201,14 +2296,14 @@
         <v>1000</v>
       </c>
       <c r="E44" s="3">
+        <v>1000</v>
+      </c>
+      <c r="F44" s="3">
         <v>500</v>
       </c>
-      <c r="F44" s="3">
+      <c r="G44" s="3">
         <v>100</v>
       </c>
-      <c r="G44" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="H44" s="3" t="s">
         <v>3</v>
       </c>
@@ -2221,8 +2316,8 @@
       <c r="K44" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="L44" s="3">
-        <v>0</v>
+      <c r="L44" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="M44" s="3">
         <v>0</v>
@@ -2239,34 +2334,37 @@
       <c r="Q44" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="45" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R44" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="45" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
+        <v>600</v>
+      </c>
+      <c r="E45" s="3">
         <v>500</v>
-      </c>
-      <c r="E45" s="3">
-        <v>600</v>
       </c>
       <c r="F45" s="3">
         <v>600</v>
       </c>
       <c r="G45" s="3">
+        <v>600</v>
+      </c>
+      <c r="H45" s="3">
         <v>400</v>
       </c>
-      <c r="H45" s="3">
+      <c r="I45" s="3">
         <v>700</v>
-      </c>
-      <c r="I45" s="3">
-        <v>1000</v>
       </c>
       <c r="J45" s="3">
         <v>1000</v>
       </c>
-      <c r="K45" s="3" t="s">
-        <v>3</v>
+      <c r="K45" s="3">
+        <v>1000</v>
       </c>
       <c r="L45" s="3" t="s">
         <v>3</v>
@@ -2286,35 +2384,38 @@
       <c r="Q45" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="46" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R45" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="46" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>4600</v>
+      </c>
+      <c r="E46" s="3">
         <v>6400</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>9300</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>6300</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>8800</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>11200</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>14000</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>3300</v>
       </c>
-      <c r="K46" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="L46" s="3" t="s">
         <v>3</v>
       </c>
@@ -2333,8 +2434,11 @@
       <c r="Q46" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="47" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R46" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="47" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
@@ -2380,35 +2484,38 @@
       <c r="Q47" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="48" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R47" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="48" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>1300</v>
+      </c>
+      <c r="E48" s="3">
         <v>1400</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>1500</v>
-      </c>
-      <c r="F48" s="3">
-        <v>1600</v>
       </c>
       <c r="G48" s="3">
         <v>1600</v>
       </c>
       <c r="H48" s="3">
+        <v>1600</v>
+      </c>
+      <c r="I48" s="3">
         <v>1700</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>1800</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>1900</v>
       </c>
-      <c r="K48" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="L48" s="3" t="s">
         <v>3</v>
       </c>
@@ -2427,8 +2534,11 @@
       <c r="Q48" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="49" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R48" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="49" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
@@ -2474,8 +2584,11 @@
       <c r="Q49" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="50" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R49" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="50" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -2521,8 +2634,11 @@
       <c r="Q50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -2568,8 +2684,11 @@
       <c r="Q51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
@@ -2615,8 +2734,11 @@
       <c r="Q52" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="53" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R52" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="53" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -2662,35 +2784,38 @@
       <c r="Q53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>5900</v>
+      </c>
+      <c r="E54" s="3">
         <v>7900</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>10800</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>7900</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>10400</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>12900</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>15700</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>5200</v>
       </c>
-      <c r="K54" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="L54" s="3" t="s">
         <v>3</v>
       </c>
@@ -2709,8 +2834,11 @@
       <c r="Q54" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="55" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R54" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="55" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -2728,8 +2856,9 @@
       <c r="O55" s="3"/>
       <c r="P55" s="3"/>
       <c r="Q55" s="3"/>
-    </row>
-    <row r="56" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R55" s="3"/>
+    </row>
+    <row r="56" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -2747,22 +2876,23 @@
       <c r="O56" s="3"/>
       <c r="P56" s="3"/>
       <c r="Q56" s="3"/>
-    </row>
-    <row r="57" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R56" s="3"/>
+    </row>
+    <row r="57" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>200</v>
+      </c>
+      <c r="E57" s="3">
         <v>300</v>
-      </c>
-      <c r="E57" s="3">
-        <v>200</v>
       </c>
       <c r="F57" s="3">
         <v>200</v>
       </c>
       <c r="G57" s="3">
-        <v>100</v>
+        <v>200</v>
       </c>
       <c r="H57" s="3">
         <v>100</v>
@@ -2773,8 +2903,8 @@
       <c r="J57" s="3">
         <v>100</v>
       </c>
-      <c r="K57" s="3" t="s">
-        <v>3</v>
+      <c r="K57" s="3">
+        <v>100</v>
       </c>
       <c r="L57" s="3" t="s">
         <v>3</v>
@@ -2794,8 +2924,11 @@
       <c r="Q57" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="58" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R57" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="58" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
@@ -2817,12 +2950,12 @@
       <c r="I58" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="J58" s="3">
+      <c r="J58" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="K58" s="3">
         <v>1000</v>
       </c>
-      <c r="K58" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="L58" s="3" t="s">
         <v>3</v>
       </c>
@@ -2841,35 +2974,38 @@
       <c r="Q58" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="59" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R58" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="59" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>2400</v>
+      </c>
+      <c r="E59" s="3">
         <v>1800</v>
       </c>
-      <c r="E59" s="3">
+      <c r="F59" s="3">
         <v>2000</v>
       </c>
-      <c r="F59" s="3">
+      <c r="G59" s="3">
         <v>1500</v>
-      </c>
-      <c r="G59" s="3">
-        <v>1300</v>
       </c>
       <c r="H59" s="3">
         <v>1300</v>
       </c>
       <c r="I59" s="3">
+        <v>1300</v>
+      </c>
+      <c r="J59" s="3">
         <v>1400</v>
       </c>
-      <c r="J59" s="3">
+      <c r="K59" s="3">
         <v>1600</v>
       </c>
-      <c r="K59" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="L59" s="3" t="s">
         <v>3</v>
       </c>
@@ -2888,35 +3024,38 @@
       <c r="Q59" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="60" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R59" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="60" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>2600</v>
+      </c>
+      <c r="E60" s="3">
         <v>2000</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>2200</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>1800</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>1400</v>
-      </c>
-      <c r="H60" s="3">
-        <v>1500</v>
       </c>
       <c r="I60" s="3">
         <v>1500</v>
       </c>
       <c r="J60" s="3">
+        <v>1500</v>
+      </c>
+      <c r="K60" s="3">
         <v>2700</v>
       </c>
-      <c r="K60" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="L60" s="3" t="s">
         <v>3</v>
       </c>
@@ -2935,8 +3074,11 @@
       <c r="Q60" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="61" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R60" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="61" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
@@ -2982,8 +3124,11 @@
       <c r="Q61" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="62" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R61" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
@@ -2991,26 +3136,26 @@
         <v>500</v>
       </c>
       <c r="E62" s="3">
+        <v>500</v>
+      </c>
+      <c r="F62" s="3">
         <v>600</v>
       </c>
-      <c r="F62" s="3">
+      <c r="G62" s="3">
         <v>700</v>
-      </c>
-      <c r="G62" s="3">
-        <v>800</v>
       </c>
       <c r="H62" s="3">
         <v>800</v>
       </c>
       <c r="I62" s="3">
+        <v>800</v>
+      </c>
+      <c r="J62" s="3">
         <v>900</v>
       </c>
-      <c r="J62" s="3">
+      <c r="K62" s="3">
         <v>1100</v>
       </c>
-      <c r="K62" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="L62" s="3" t="s">
         <v>3</v>
       </c>
@@ -3029,8 +3174,11 @@
       <c r="Q62" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="63" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R62" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="63" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -3076,8 +3224,11 @@
       <c r="Q63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -3123,8 +3274,11 @@
       <c r="Q64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -3170,35 +3324,38 @@
       <c r="Q65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>3100</v>
+      </c>
+      <c r="E66" s="3">
         <v>2600</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>2800</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>2500</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>2200</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>2300</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>2500</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>3800</v>
       </c>
-      <c r="K66" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="L66" s="3" t="s">
         <v>3</v>
       </c>
@@ -3217,8 +3374,11 @@
       <c r="Q66" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="67" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R66" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="67" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -3236,8 +3396,9 @@
       <c r="O67" s="3"/>
       <c r="P67" s="3"/>
       <c r="Q67" s="3"/>
-    </row>
-    <row r="68" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R67" s="3"/>
+    </row>
+    <row r="68" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -3283,8 +3444,11 @@
       <c r="Q68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -3330,8 +3494,11 @@
       <c r="Q69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -3354,11 +3521,11 @@
         <v>0</v>
       </c>
       <c r="J70" s="3">
+        <v>0</v>
+      </c>
+      <c r="K70" s="3">
         <v>12000</v>
       </c>
-      <c r="K70" s="3">
-        <v>0</v>
-      </c>
       <c r="L70" s="3">
         <v>0</v>
       </c>
@@ -3377,8 +3544,11 @@
       <c r="Q70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -3424,35 +3594,38 @@
       <c r="Q71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>-66000</v>
+      </c>
+      <c r="E72" s="3">
         <v>-63400</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>-60600</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>-57700</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>-54800</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>-52400</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>-49600</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>-46700</v>
       </c>
-      <c r="K72" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="L72" s="3" t="s">
         <v>3</v>
       </c>
@@ -3471,8 +3644,11 @@
       <c r="Q72" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="73" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R72" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="73" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -3518,8 +3694,11 @@
       <c r="Q73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -3565,8 +3744,11 @@
       <c r="Q74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -3612,35 +3794,38 @@
       <c r="Q75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>2800</v>
+      </c>
+      <c r="E76" s="3">
         <v>5300</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>8000</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>5400</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>8300</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>10600</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>13300</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>-10500</v>
       </c>
-      <c r="K76" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="L76" s="3" t="s">
         <v>3</v>
       </c>
@@ -3659,8 +3844,11 @@
       <c r="Q76" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="77" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R76" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="77" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -3706,107 +3894,116 @@
       <c r="Q77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:18" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:17" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45291</v>
+      </c>
+      <c r="E80" s="2">
         <v>45199</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45107</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45016</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>44926</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>44834</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>44742</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>44651</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>44561</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>44377</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>44196</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>44012</v>
       </c>
-      <c r="O80" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="P80" s="2" t="s">
         <v>3</v>
       </c>
       <c r="Q80" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="81" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R80" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="81" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>-2500</v>
+      </c>
+      <c r="E81" s="3">
         <v>-2800</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>-3000</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>-2900</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>-2500</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>-2800</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>-2900</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>-2300</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>-10200</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>-5100</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>-10700</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>-5100</v>
       </c>
-      <c r="O81" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="P81" s="3" t="s">
         <v>3</v>
       </c>
       <c r="Q81" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="82" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R81" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="82" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -3824,8 +4021,9 @@
       <c r="O82" s="3"/>
       <c r="P82" s="3"/>
       <c r="Q82" s="3"/>
-    </row>
-    <row r="83" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R82" s="3"/>
+    </row>
+    <row r="83" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
@@ -3851,28 +4049,31 @@
         <v>0</v>
       </c>
       <c r="K83" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="L83" s="3">
         <v>100</v>
       </c>
       <c r="M83" s="3">
+        <v>100</v>
+      </c>
+      <c r="N83" s="3">
         <v>200</v>
       </c>
-      <c r="N83" s="3">
+      <c r="O83" s="3">
         <v>100</v>
       </c>
-      <c r="O83" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="P83" s="3" t="s">
         <v>3</v>
       </c>
       <c r="Q83" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="84" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R83" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="84" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -3918,8 +4119,11 @@
       <c r="Q84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -3965,8 +4169,11 @@
       <c r="Q85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -4012,8 +4219,11 @@
       <c r="Q86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -4059,8 +4269,11 @@
       <c r="Q87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -4106,55 +4319,61 @@
       <c r="Q88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>-1900</v>
+      </c>
+      <c r="E89" s="3">
         <v>-3200</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>-2900</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>-2500</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>-2100</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>-2500</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>-2900</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>-2500</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>-9900</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>-5000</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>-7200</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>-4100</v>
       </c>
-      <c r="O89" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="P89" s="3" t="s">
         <v>3</v>
       </c>
       <c r="Q89" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="90" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R89" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="90" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -4172,8 +4391,9 @@
       <c r="O90" s="3"/>
       <c r="P90" s="3"/>
       <c r="Q90" s="3"/>
-    </row>
-    <row r="91" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R90" s="3"/>
+    </row>
+    <row r="91" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
@@ -4181,13 +4401,13 @@
         <v>0</v>
       </c>
       <c r="E91" s="3">
-        <v>-100</v>
+        <v>0</v>
       </c>
       <c r="F91" s="3">
         <v>-100</v>
       </c>
       <c r="G91" s="3">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="H91" s="3">
         <v>0</v>
@@ -4199,28 +4419,31 @@
         <v>0</v>
       </c>
       <c r="K91" s="3">
+        <v>0</v>
+      </c>
+      <c r="L91" s="3">
         <v>-200</v>
       </c>
-      <c r="L91" s="3">
-        <v>0</v>
-      </c>
       <c r="M91" s="3">
         <v>0</v>
       </c>
       <c r="N91" s="3">
+        <v>0</v>
+      </c>
+      <c r="O91" s="3">
         <v>-100</v>
       </c>
-      <c r="O91" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="P91" s="3" t="s">
         <v>3</v>
       </c>
       <c r="Q91" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="92" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R91" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="92" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -4266,8 +4489,11 @@
       <c r="Q92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -4313,8 +4539,11 @@
       <c r="Q93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
@@ -4322,13 +4551,13 @@
         <v>0</v>
       </c>
       <c r="E94" s="3">
-        <v>-100</v>
+        <v>0</v>
       </c>
       <c r="F94" s="3">
         <v>-100</v>
       </c>
       <c r="G94" s="3">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="H94" s="3">
         <v>0</v>
@@ -4340,19 +4569,19 @@
         <v>0</v>
       </c>
       <c r="K94" s="3">
+        <v>0</v>
+      </c>
+      <c r="L94" s="3">
         <v>-300</v>
       </c>
-      <c r="L94" s="3">
-        <v>0</v>
-      </c>
       <c r="M94" s="3">
-        <v>-100</v>
+        <v>0</v>
       </c>
       <c r="N94" s="3">
         <v>-100</v>
       </c>
-      <c r="O94" s="3" t="s">
-        <v>3</v>
+      <c r="O94" s="3">
+        <v>-100</v>
       </c>
       <c r="P94" s="3" t="s">
         <v>3</v>
@@ -4360,8 +4589,11 @@
       <c r="Q94" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="95" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R94" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="95" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -4379,8 +4611,9 @@
       <c r="O95" s="3"/>
       <c r="P95" s="3"/>
       <c r="Q95" s="3"/>
-    </row>
-    <row r="96" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R95" s="3"/>
+    </row>
+    <row r="96" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -4426,8 +4659,11 @@
       <c r="Q96" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="97" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R96" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -4473,8 +4709,11 @@
       <c r="Q97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -4520,8 +4759,11 @@
       <c r="Q98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -4567,20 +4809,23 @@
       <c r="Q99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>0</v>
+      </c>
+      <c r="E100" s="3">
         <v>-100</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>5500</v>
       </c>
-      <c r="F100" s="3">
-        <v>0</v>
-      </c>
       <c r="G100" s="3">
         <v>0</v>
       </c>
@@ -4588,25 +4833,25 @@
         <v>0</v>
       </c>
       <c r="I100" s="3">
+        <v>0</v>
+      </c>
+      <c r="J100" s="3">
         <v>13600</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>3000</v>
-      </c>
-      <c r="K100" s="3">
-        <v>5100</v>
       </c>
       <c r="L100" s="3">
         <v>5100</v>
       </c>
       <c r="M100" s="3">
+        <v>5100</v>
+      </c>
+      <c r="N100" s="3">
         <v>5000</v>
       </c>
-      <c r="N100" s="3">
-        <v>0</v>
-      </c>
-      <c r="O100" s="3" t="s">
-        <v>3</v>
+      <c r="O100" s="3">
+        <v>0</v>
       </c>
       <c r="P100" s="3" t="s">
         <v>3</v>
@@ -4614,8 +4859,11 @@
       <c r="Q100" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="101" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R100" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="101" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
@@ -4661,51 +4909,57 @@
       <c r="Q101" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="102" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R101" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="102" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>-1800</v>
+      </c>
+      <c r="E102" s="3">
         <v>-3300</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>2500</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>-2600</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>-2200</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>-2500</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>10700</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>600</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>-5100</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>100</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>-2400</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>-4200</v>
       </c>
-      <c r="O102" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="P102" s="3" t="s">
         <v>3</v>
       </c>
       <c r="Q102" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R102" s="3" t="s">
         <v>3</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/RVSN_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/RVSN_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="299" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="300" uniqueCount="92">
   <si>
     <t>RVSN</t>
   </si>
@@ -656,99 +656,103 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:R102"/>
+  <dimension ref="A5:S102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="7.5703125" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="5" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="9" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="18" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="6" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="10" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="19" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:19" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:19" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45473</v>
+      </c>
+      <c r="E7" s="2">
         <v>45291</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45199</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45107</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45016</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>44926</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>44834</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>44742</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>44651</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>44561</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>44377</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>44196</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>44012</v>
       </c>
-      <c r="P7" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="Q7" s="2" t="s">
         <v>3</v>
       </c>
       <c r="R7" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="8" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="S7" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="8" spans="1:19" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D8" s="3" t="s">
-        <v>3</v>
+      <c r="D8" s="3">
+        <v>800</v>
       </c>
       <c r="E8" s="3">
+        <v>0</v>
+      </c>
+      <c r="F8" s="3">
         <v>100</v>
       </c>
-      <c r="F8" s="3">
-        <v>0</v>
-      </c>
       <c r="G8" s="3">
         <v>0</v>
       </c>
@@ -756,28 +760,28 @@
         <v>0</v>
       </c>
       <c r="I8" s="3">
+        <v>0</v>
+      </c>
+      <c r="J8" s="3">
         <v>200</v>
       </c>
-      <c r="J8" s="3">
-        <v>0</v>
-      </c>
       <c r="K8" s="3">
+        <v>0</v>
+      </c>
+      <c r="L8" s="3">
         <v>200</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>900</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>400</v>
       </c>
-      <c r="N8" s="3">
-        <v>0</v>
-      </c>
       <c r="O8" s="3">
         <v>0</v>
       </c>
-      <c r="P8" s="3" t="s">
-        <v>3</v>
+      <c r="P8" s="3">
+        <v>0</v>
       </c>
       <c r="Q8" s="3" t="s">
         <v>3</v>
@@ -785,44 +789,47 @@
       <c r="R8" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="9" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="S8" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="9" spans="1:19" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="D9" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="E9" s="3">
+      <c r="D9" s="3">
+        <v>400</v>
+      </c>
+      <c r="E9" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="F9" s="3">
         <v>100</v>
       </c>
-      <c r="F9" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="G9" s="3" t="s">
         <v>3</v>
       </c>
       <c r="H9" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="I9" s="3">
+      <c r="I9" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="J9" s="3">
         <v>300</v>
       </c>
-      <c r="J9" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="K9" s="3">
+      <c r="K9" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="L9" s="3">
         <v>400</v>
       </c>
-      <c r="L9" s="3">
+      <c r="M9" s="3">
         <v>700</v>
       </c>
-      <c r="M9" s="3">
+      <c r="N9" s="3">
         <v>100</v>
       </c>
-      <c r="N9" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="O9" s="3" t="s">
         <v>3</v>
       </c>
@@ -835,19 +842,22 @@
       <c r="R9" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="10" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="S9" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="10" spans="1:19" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="D10" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="E10" s="3">
-        <v>0</v>
-      </c>
-      <c r="F10" s="3" t="s">
-        <v>3</v>
+      <c r="D10" s="3">
+        <v>400</v>
+      </c>
+      <c r="E10" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="F10" s="3">
+        <v>0</v>
       </c>
       <c r="G10" s="3" t="s">
         <v>3</v>
@@ -855,24 +865,24 @@
       <c r="H10" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="I10" s="3">
+      <c r="I10" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="J10" s="3">
         <v>-100</v>
       </c>
-      <c r="J10" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="K10" s="3">
+      <c r="K10" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="L10" s="3">
         <v>-200</v>
       </c>
-      <c r="L10" s="3">
+      <c r="M10" s="3">
         <v>200</v>
       </c>
-      <c r="M10" s="3">
+      <c r="N10" s="3">
         <v>300</v>
       </c>
-      <c r="N10" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="O10" s="3" t="s">
         <v>3</v>
       </c>
@@ -885,8 +895,11 @@
       <c r="R10" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="11" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="S10" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="11" spans="1:19" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -905,58 +918,62 @@
       <c r="P11" s="3"/>
       <c r="Q11" s="3"/>
       <c r="R11" s="3"/>
-    </row>
-    <row r="12" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="S11" s="3"/>
+    </row>
+    <row r="12" spans="1:19" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
       <c r="D12" s="3">
+        <v>2400</v>
+      </c>
+      <c r="E12" s="3">
         <v>1600</v>
       </c>
-      <c r="E12" s="3">
+      <c r="F12" s="3">
         <v>1900</v>
-      </c>
-      <c r="F12" s="3">
-        <v>1800</v>
       </c>
       <c r="G12" s="3">
         <v>1800</v>
       </c>
       <c r="H12" s="3">
+        <v>1800</v>
+      </c>
+      <c r="I12" s="3">
         <v>1500</v>
-      </c>
-      <c r="I12" s="3">
-        <v>1700</v>
       </c>
       <c r="J12" s="3">
         <v>1700</v>
       </c>
       <c r="K12" s="3">
+        <v>1700</v>
+      </c>
+      <c r="L12" s="3">
         <v>1400</v>
       </c>
-      <c r="L12" s="3">
+      <c r="M12" s="3">
         <v>7200</v>
       </c>
-      <c r="M12" s="3">
+      <c r="N12" s="3">
         <v>3800</v>
       </c>
-      <c r="N12" s="3">
+      <c r="O12" s="3">
         <v>7200</v>
       </c>
-      <c r="O12" s="3">
+      <c r="P12" s="3">
         <v>3600</v>
       </c>
-      <c r="P12" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Q12" s="3" t="s">
         <v>3</v>
       </c>
       <c r="R12" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="13" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="S12" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="13" spans="1:19" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1005,8 +1022,11 @@
       <c r="R13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="S13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:19" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
@@ -1055,31 +1075,34 @@
       <c r="R14" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="15" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="S14" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:19" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D15" s="3">
-        <v>0</v>
-      </c>
-      <c r="E15" s="3">
-        <v>0</v>
-      </c>
-      <c r="F15" s="3">
-        <v>0</v>
-      </c>
-      <c r="G15" s="3">
-        <v>0</v>
-      </c>
-      <c r="H15" s="3">
-        <v>0</v>
-      </c>
-      <c r="I15" s="3">
-        <v>0</v>
-      </c>
-      <c r="J15" s="3">
-        <v>0</v>
+        <v>100</v>
+      </c>
+      <c r="E15" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="F15" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="G15" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="H15" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="I15" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="J15" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="K15" s="3">
         <v>0</v>
@@ -1105,8 +1128,11 @@
       <c r="R15" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="16" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="S15" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:19" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1122,16 +1148,17 @@
       <c r="P16" s="3"/>
       <c r="Q16" s="3"/>
       <c r="R16" s="3"/>
-    </row>
-    <row r="17" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S16" s="3"/>
+    </row>
+    <row r="17" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>4900</v>
+      </c>
+      <c r="E17" s="3">
         <v>2600</v>
-      </c>
-      <c r="E17" s="3">
-        <v>3000</v>
       </c>
       <c r="F17" s="3">
         <v>3000</v>
@@ -1140,90 +1167,96 @@
         <v>3000</v>
       </c>
       <c r="H17" s="3">
+        <v>3000</v>
+      </c>
+      <c r="I17" s="3">
         <v>2600</v>
-      </c>
-      <c r="I17" s="3">
-        <v>3000</v>
       </c>
       <c r="J17" s="3">
         <v>3000</v>
       </c>
       <c r="K17" s="3">
+        <v>3000</v>
+      </c>
+      <c r="L17" s="3">
         <v>2600</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>11200</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>5700</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>10700</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>5100</v>
       </c>
-      <c r="P17" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Q17" s="3" t="s">
         <v>3</v>
       </c>
       <c r="R17" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="18" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S17" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="18" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="D18" s="3" t="s">
-        <v>3</v>
+      <c r="D18" s="3">
+        <v>-4100</v>
       </c>
       <c r="E18" s="3">
+        <v>-2600</v>
+      </c>
+      <c r="F18" s="3">
         <v>-2900</v>
-      </c>
-      <c r="F18" s="3">
-        <v>-3000</v>
       </c>
       <c r="G18" s="3">
         <v>-3000</v>
       </c>
       <c r="H18" s="3">
+        <v>-3000</v>
+      </c>
+      <c r="I18" s="3">
         <v>-2600</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>-2800</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>-3000</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>-2400</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>-10300</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>-5300</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>-10700</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>-5100</v>
       </c>
-      <c r="P18" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Q18" s="3" t="s">
         <v>3</v>
       </c>
       <c r="R18" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="19" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S18" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="19" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1242,49 +1275,50 @@
       <c r="P19" s="3"/>
       <c r="Q19" s="3"/>
       <c r="R19" s="3"/>
-    </row>
-    <row r="20" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S19" s="3"/>
+    </row>
+    <row r="20" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="D20" s="3" t="s">
-        <v>3</v>
+      <c r="D20" s="3">
+        <v>-20200</v>
       </c>
       <c r="E20" s="3">
         <v>100</v>
       </c>
       <c r="F20" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="G20" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="H20" s="3">
         <v>100</v>
       </c>
       <c r="I20" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="J20" s="3">
+        <v>0</v>
+      </c>
+      <c r="K20" s="3">
         <v>100</v>
       </c>
-      <c r="K20" s="3">
-        <v>0</v>
-      </c>
       <c r="L20" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="M20" s="3">
         <v>100</v>
       </c>
       <c r="N20" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="O20" s="3">
         <v>0</v>
       </c>
-      <c r="P20" s="3" t="s">
-        <v>3</v>
+      <c r="P20" s="3">
+        <v>0</v>
       </c>
       <c r="Q20" s="3" t="s">
         <v>3</v>
@@ -1292,58 +1326,64 @@
       <c r="R20" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="21" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S20" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="21" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="D21" s="3" t="s">
-        <v>3</v>
+      <c r="D21" s="3">
+        <v>-24200</v>
       </c>
       <c r="E21" s="3">
+        <v>-2500</v>
+      </c>
+      <c r="F21" s="3">
         <v>-2700</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>-2900</v>
       </c>
-      <c r="G21" s="3">
+      <c r="H21" s="3">
         <v>-2800</v>
       </c>
-      <c r="H21" s="3">
+      <c r="I21" s="3">
         <v>-2400</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>-2700</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>-2900</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>-2300</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>-10100</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>-5100</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>-10500</v>
       </c>
-      <c r="O21" s="3">
+      <c r="P21" s="3">
         <v>-5000</v>
       </c>
-      <c r="P21" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Q21" s="3" t="s">
         <v>3</v>
       </c>
       <c r="R21" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="22" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S21" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="22" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
@@ -1392,58 +1432,64 @@
       <c r="R22" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="23" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S22" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>-24300</v>
+      </c>
+      <c r="E23" s="3">
         <v>-2500</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>-2800</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>-3000</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>-2900</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>-2500</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>-2800</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>-2900</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>-2300</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>-10200</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>-5100</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>-10700</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>-5100</v>
       </c>
-      <c r="P23" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Q23" s="3" t="s">
         <v>3</v>
       </c>
       <c r="R23" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="24" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S23" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="24" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
@@ -1492,8 +1538,11 @@
       <c r="R24" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="25" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S24" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -1542,108 +1591,117 @@
       <c r="R25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>-24300</v>
+      </c>
+      <c r="E26" s="3">
         <v>-2500</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>-2800</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>-3000</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>-2900</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>-2500</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>-2800</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>-2900</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>-2300</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>-10200</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>-5100</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>-10700</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>-5100</v>
       </c>
-      <c r="P26" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Q26" s="3" t="s">
         <v>3</v>
       </c>
       <c r="R26" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="27" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S26" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="27" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>-24300</v>
+      </c>
+      <c r="E27" s="3">
         <v>-2500</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>-2800</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>-3000</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>-2900</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>-2500</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>-2800</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>-2900</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>-2300</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>-10200</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>-5100</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>-10700</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>-5100</v>
       </c>
-      <c r="P27" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Q27" s="3" t="s">
         <v>3</v>
       </c>
       <c r="R27" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="28" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S27" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="28" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -1692,8 +1750,11 @@
       <c r="R28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -1742,8 +1803,11 @@
       <c r="R29" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="30" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S29" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -1792,8 +1856,11 @@
       <c r="R30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -1842,49 +1909,52 @@
       <c r="R31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
-      <c r="D32" s="3" t="s">
-        <v>3</v>
+      <c r="D32" s="3">
+        <v>20200</v>
       </c>
       <c r="E32" s="3">
         <v>-100</v>
       </c>
       <c r="F32" s="3">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="G32" s="3">
-        <v>-100</v>
+        <v>0</v>
       </c>
       <c r="H32" s="3">
         <v>-100</v>
       </c>
       <c r="I32" s="3">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="J32" s="3">
+        <v>0</v>
+      </c>
+      <c r="K32" s="3">
         <v>-100</v>
       </c>
-      <c r="K32" s="3">
-        <v>0</v>
-      </c>
       <c r="L32" s="3">
-        <v>-100</v>
+        <v>0</v>
       </c>
       <c r="M32" s="3">
         <v>-100</v>
       </c>
       <c r="N32" s="3">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="O32" s="3">
         <v>0</v>
       </c>
-      <c r="P32" s="3" t="s">
-        <v>3</v>
+      <c r="P32" s="3">
+        <v>0</v>
       </c>
       <c r="Q32" s="3" t="s">
         <v>3</v>
@@ -1892,58 +1962,64 @@
       <c r="R32" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="33" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S32" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="33" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>-24300</v>
+      </c>
+      <c r="E33" s="3">
         <v>-2500</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>-2800</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>-3000</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>-2900</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>-2500</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>-2800</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>-2900</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>-2300</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>-10200</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>-5100</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>-10700</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>-5100</v>
       </c>
-      <c r="P33" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Q33" s="3" t="s">
         <v>3</v>
       </c>
       <c r="R33" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="34" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S33" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="34" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -1992,113 +2068,122 @@
       <c r="R34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>-24300</v>
+      </c>
+      <c r="E35" s="3">
         <v>-2500</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>-2800</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>-3000</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>-2900</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>-2500</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>-2800</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>-2900</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>-2300</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>-10200</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>-5100</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>-10700</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>-5100</v>
       </c>
-      <c r="P35" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Q35" s="3" t="s">
         <v>3</v>
       </c>
       <c r="R35" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="37" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S35" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="37" spans="2:19" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:18" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45473</v>
+      </c>
+      <c r="E38" s="2">
         <v>45291</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45199</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45107</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45016</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>44926</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>44834</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>44742</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>44651</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>44561</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>44377</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>44196</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>44012</v>
       </c>
-      <c r="P38" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="Q38" s="2" t="s">
         <v>3</v>
       </c>
       <c r="R38" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="39" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S38" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="39" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -2117,8 +2202,9 @@
       <c r="P39" s="3"/>
       <c r="Q39" s="3"/>
       <c r="R39" s="3"/>
-    </row>
-    <row r="40" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S39" s="3"/>
+    </row>
+    <row r="40" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -2137,38 +2223,39 @@
       <c r="P40" s="3"/>
       <c r="Q40" s="3"/>
       <c r="R40" s="3"/>
-    </row>
-    <row r="41" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S40" s="3"/>
+    </row>
+    <row r="41" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>9700</v>
+      </c>
+      <c r="E41" s="3">
         <v>3100</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>4900</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>8200</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>5600</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>8300</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>10400</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>12900</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>2200</v>
       </c>
-      <c r="L41" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="M41" s="3" t="s">
         <v>3</v>
       </c>
@@ -2187,8 +2274,11 @@
       <c r="R41" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="42" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S41" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="42" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
@@ -2237,37 +2327,40 @@
       <c r="R42" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="43" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S42" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="E43" s="3">
         <v>0</v>
       </c>
-      <c r="F43" s="3" t="s">
-        <v>3</v>
+      <c r="F43" s="3">
+        <v>0</v>
       </c>
       <c r="G43" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="H43" s="3">
-        <v>100</v>
+      <c r="H43" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="I43" s="3">
         <v>100</v>
       </c>
-      <c r="J43" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="K43" s="3">
+      <c r="J43" s="3">
         <v>100</v>
       </c>
-      <c r="L43" s="3" t="s">
-        <v>3</v>
+      <c r="K43" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="L43" s="3">
+        <v>100</v>
       </c>
       <c r="M43" s="3" t="s">
         <v>3</v>
@@ -2287,8 +2380,11 @@
       <c r="R43" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="44" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S43" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="44" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
@@ -2299,14 +2395,14 @@
         <v>1000</v>
       </c>
       <c r="F44" s="3">
+        <v>1000</v>
+      </c>
+      <c r="G44" s="3">
         <v>500</v>
       </c>
-      <c r="G44" s="3">
+      <c r="H44" s="3">
         <v>100</v>
       </c>
-      <c r="H44" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="I44" s="3" t="s">
         <v>3</v>
       </c>
@@ -2319,8 +2415,8 @@
       <c r="L44" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="M44" s="3">
-        <v>0</v>
+      <c r="M44" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="N44" s="3">
         <v>0</v>
@@ -2337,8 +2433,11 @@
       <c r="R44" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="45" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S44" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="45" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
@@ -2346,28 +2445,28 @@
         <v>600</v>
       </c>
       <c r="E45" s="3">
+        <v>600</v>
+      </c>
+      <c r="F45" s="3">
         <v>500</v>
-      </c>
-      <c r="F45" s="3">
-        <v>600</v>
       </c>
       <c r="G45" s="3">
         <v>600</v>
       </c>
       <c r="H45" s="3">
+        <v>600</v>
+      </c>
+      <c r="I45" s="3">
         <v>400</v>
       </c>
-      <c r="I45" s="3">
+      <c r="J45" s="3">
         <v>700</v>
-      </c>
-      <c r="J45" s="3">
-        <v>1000</v>
       </c>
       <c r="K45" s="3">
         <v>1000</v>
       </c>
-      <c r="L45" s="3" t="s">
-        <v>3</v>
+      <c r="L45" s="3">
+        <v>1000</v>
       </c>
       <c r="M45" s="3" t="s">
         <v>3</v>
@@ -2387,38 +2486,41 @@
       <c r="R45" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="46" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S45" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="46" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>11400</v>
+      </c>
+      <c r="E46" s="3">
         <v>4600</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>6400</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>9300</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>6300</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>8800</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>11200</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>14000</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>3300</v>
       </c>
-      <c r="L46" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="M46" s="3" t="s">
         <v>3</v>
       </c>
@@ -2437,8 +2539,11 @@
       <c r="R46" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="47" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S46" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="47" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
@@ -2487,38 +2592,41 @@
       <c r="R47" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="48" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S47" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="48" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>1100</v>
+      </c>
+      <c r="E48" s="3">
         <v>1300</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>1400</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>1500</v>
-      </c>
-      <c r="G48" s="3">
-        <v>1600</v>
       </c>
       <c r="H48" s="3">
         <v>1600</v>
       </c>
       <c r="I48" s="3">
+        <v>1600</v>
+      </c>
+      <c r="J48" s="3">
         <v>1700</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>1800</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>1900</v>
       </c>
-      <c r="L48" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="M48" s="3" t="s">
         <v>3</v>
       </c>
@@ -2537,8 +2645,11 @@
       <c r="R48" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="49" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S48" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="49" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
@@ -2587,8 +2698,11 @@
       <c r="R49" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="50" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S49" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="50" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -2637,8 +2751,11 @@
       <c r="R50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -2687,8 +2804,11 @@
       <c r="R51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
@@ -2737,8 +2857,11 @@
       <c r="R52" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="53" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S52" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="53" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -2787,38 +2910,41 @@
       <c r="R53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>12500</v>
+      </c>
+      <c r="E54" s="3">
         <v>5900</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>7900</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>10800</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>7900</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>10400</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>12900</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>15700</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>5200</v>
       </c>
-      <c r="L54" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="M54" s="3" t="s">
         <v>3</v>
       </c>
@@ -2837,8 +2963,11 @@
       <c r="R54" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="55" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S54" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="55" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -2857,8 +2986,9 @@
       <c r="P55" s="3"/>
       <c r="Q55" s="3"/>
       <c r="R55" s="3"/>
-    </row>
-    <row r="56" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S55" s="3"/>
+    </row>
+    <row r="56" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -2877,25 +3007,26 @@
       <c r="P56" s="3"/>
       <c r="Q56" s="3"/>
       <c r="R56" s="3"/>
-    </row>
-    <row r="57" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S56" s="3"/>
+    </row>
+    <row r="57" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>100</v>
+      </c>
+      <c r="E57" s="3">
         <v>200</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>300</v>
-      </c>
-      <c r="F57" s="3">
-        <v>200</v>
       </c>
       <c r="G57" s="3">
         <v>200</v>
       </c>
       <c r="H57" s="3">
-        <v>100</v>
+        <v>200</v>
       </c>
       <c r="I57" s="3">
         <v>100</v>
@@ -2906,8 +3037,8 @@
       <c r="K57" s="3">
         <v>100</v>
       </c>
-      <c r="L57" s="3" t="s">
-        <v>3</v>
+      <c r="L57" s="3">
+        <v>100</v>
       </c>
       <c r="M57" s="3" t="s">
         <v>3</v>
@@ -2927,38 +3058,41 @@
       <c r="R57" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="58" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S57" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="58" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
-      <c r="D58" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="E58" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="F58" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="G58" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="H58" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="I58" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="J58" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="K58" s="3">
+      <c r="D58" s="3">
+        <v>0</v>
+      </c>
+      <c r="E58" s="3">
+        <v>0</v>
+      </c>
+      <c r="F58" s="3">
+        <v>0</v>
+      </c>
+      <c r="G58" s="3">
+        <v>0</v>
+      </c>
+      <c r="H58" s="3">
+        <v>0</v>
+      </c>
+      <c r="I58" s="3">
+        <v>0</v>
+      </c>
+      <c r="J58" s="3">
+        <v>0</v>
+      </c>
+      <c r="K58" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="L58" s="3">
         <v>1000</v>
       </c>
-      <c r="L58" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="M58" s="3" t="s">
         <v>3</v>
       </c>
@@ -2977,38 +3111,41 @@
       <c r="R58" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="59" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S58" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="59" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>2100</v>
+      </c>
+      <c r="E59" s="3">
         <v>2400</v>
       </c>
-      <c r="E59" s="3">
+      <c r="F59" s="3">
         <v>1800</v>
       </c>
-      <c r="F59" s="3">
+      <c r="G59" s="3">
         <v>2000</v>
       </c>
-      <c r="G59" s="3">
+      <c r="H59" s="3">
         <v>1500</v>
-      </c>
-      <c r="H59" s="3">
-        <v>1300</v>
       </c>
       <c r="I59" s="3">
         <v>1300</v>
       </c>
       <c r="J59" s="3">
+        <v>1300</v>
+      </c>
+      <c r="K59" s="3">
         <v>1400</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>1600</v>
       </c>
-      <c r="L59" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="M59" s="3" t="s">
         <v>3</v>
       </c>
@@ -3027,38 +3164,41 @@
       <c r="R59" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="60" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S59" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="60" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>2200</v>
+      </c>
+      <c r="E60" s="3">
         <v>2600</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>2000</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>2200</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>1800</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>1400</v>
-      </c>
-      <c r="I60" s="3">
-        <v>1500</v>
       </c>
       <c r="J60" s="3">
         <v>1500</v>
       </c>
       <c r="K60" s="3">
+        <v>1500</v>
+      </c>
+      <c r="L60" s="3">
         <v>2700</v>
       </c>
-      <c r="L60" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="M60" s="3" t="s">
         <v>3</v>
       </c>
@@ -3077,8 +3217,11 @@
       <c r="R60" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="61" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S60" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="61" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
@@ -3127,38 +3270,41 @@
       <c r="R61" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="62" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S61" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
-        <v>500</v>
+        <v>400</v>
       </c>
       <c r="E62" s="3">
         <v>500</v>
       </c>
       <c r="F62" s="3">
+        <v>500</v>
+      </c>
+      <c r="G62" s="3">
         <v>600</v>
       </c>
-      <c r="G62" s="3">
+      <c r="H62" s="3">
         <v>700</v>
-      </c>
-      <c r="H62" s="3">
-        <v>800</v>
       </c>
       <c r="I62" s="3">
         <v>800</v>
       </c>
       <c r="J62" s="3">
+        <v>800</v>
+      </c>
+      <c r="K62" s="3">
         <v>900</v>
       </c>
-      <c r="K62" s="3">
+      <c r="L62" s="3">
         <v>1100</v>
       </c>
-      <c r="L62" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="M62" s="3" t="s">
         <v>3</v>
       </c>
@@ -3177,8 +3323,11 @@
       <c r="R62" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="63" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S62" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="63" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -3227,8 +3376,11 @@
       <c r="R63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -3277,8 +3429,11 @@
       <c r="R64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -3327,38 +3482,41 @@
       <c r="R65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>2600</v>
+      </c>
+      <c r="E66" s="3">
         <v>3100</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>2600</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>2800</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>2500</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>2200</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>2300</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>2500</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>3800</v>
       </c>
-      <c r="L66" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="M66" s="3" t="s">
         <v>3</v>
       </c>
@@ -3377,8 +3535,11 @@
       <c r="R66" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="67" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S66" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="67" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -3397,8 +3558,9 @@
       <c r="P67" s="3"/>
       <c r="Q67" s="3"/>
       <c r="R67" s="3"/>
-    </row>
-    <row r="68" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S67" s="3"/>
+    </row>
+    <row r="68" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -3447,8 +3609,11 @@
       <c r="R68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -3497,8 +3662,11 @@
       <c r="R69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -3524,11 +3692,11 @@
         <v>0</v>
       </c>
       <c r="K70" s="3">
+        <v>0</v>
+      </c>
+      <c r="L70" s="3">
         <v>12000</v>
       </c>
-      <c r="L70" s="3">
-        <v>0</v>
-      </c>
       <c r="M70" s="3">
         <v>0</v>
       </c>
@@ -3547,8 +3715,11 @@
       <c r="R70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -3597,38 +3768,41 @@
       <c r="R71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>-90300</v>
+      </c>
+      <c r="E72" s="3">
         <v>-66000</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>-63400</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>-60600</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>-57700</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>-54800</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>-52400</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>-49600</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>-46700</v>
       </c>
-      <c r="L72" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="M72" s="3" t="s">
         <v>3</v>
       </c>
@@ -3647,8 +3821,11 @@
       <c r="R72" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="73" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S72" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="73" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -3697,8 +3874,11 @@
       <c r="R73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -3747,8 +3927,11 @@
       <c r="R74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -3797,38 +3980,41 @@
       <c r="R75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>9900</v>
+      </c>
+      <c r="E76" s="3">
         <v>2800</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>5300</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>8000</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>5400</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>8300</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>10600</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>13300</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>-10500</v>
       </c>
-      <c r="L76" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="M76" s="3" t="s">
         <v>3</v>
       </c>
@@ -3847,8 +4033,11 @@
       <c r="R76" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="77" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S76" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="77" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -3897,113 +4086,122 @@
       <c r="R77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:19" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:18" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45473</v>
+      </c>
+      <c r="E80" s="2">
         <v>45291</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45199</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45107</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45016</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>44926</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>44834</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>44742</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>44651</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>44561</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>44377</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>44196</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>44012</v>
       </c>
-      <c r="P80" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="Q80" s="2" t="s">
         <v>3</v>
       </c>
       <c r="R80" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="81" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S80" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="81" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>-24300</v>
+      </c>
+      <c r="E81" s="3">
         <v>-2500</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>-2800</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>-3000</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>-2900</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>-2500</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>-2800</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>-2900</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>-2300</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>-10200</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>-5100</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>-10700</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>-5100</v>
       </c>
-      <c r="P81" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Q81" s="3" t="s">
         <v>3</v>
       </c>
       <c r="R81" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="82" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S81" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="82" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -4022,13 +4220,14 @@
       <c r="P82" s="3"/>
       <c r="Q82" s="3"/>
       <c r="R82" s="3"/>
-    </row>
-    <row r="83" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S82" s="3"/>
+    </row>
+    <row r="83" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="E83" s="3">
         <v>0</v>
@@ -4052,28 +4251,31 @@
         <v>0</v>
       </c>
       <c r="L83" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="M83" s="3">
         <v>100</v>
       </c>
       <c r="N83" s="3">
+        <v>100</v>
+      </c>
+      <c r="O83" s="3">
         <v>200</v>
       </c>
-      <c r="O83" s="3">
+      <c r="P83" s="3">
         <v>100</v>
       </c>
-      <c r="P83" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Q83" s="3" t="s">
         <v>3</v>
       </c>
       <c r="R83" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="84" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S83" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="84" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -4122,8 +4324,11 @@
       <c r="R84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -4172,8 +4377,11 @@
       <c r="R85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -4222,8 +4430,11 @@
       <c r="R86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -4272,8 +4483,11 @@
       <c r="R87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -4322,58 +4536,64 @@
       <c r="R88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>-4600</v>
+      </c>
+      <c r="E89" s="3">
         <v>-1900</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>-3200</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>-2900</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>-2500</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>-2100</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>-2500</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>-2900</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>-2500</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>-9900</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>-5000</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>-7200</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>-4100</v>
       </c>
-      <c r="P89" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Q89" s="3" t="s">
         <v>3</v>
       </c>
       <c r="R89" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="90" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S89" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="90" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -4392,8 +4612,9 @@
       <c r="P90" s="3"/>
       <c r="Q90" s="3"/>
       <c r="R90" s="3"/>
-    </row>
-    <row r="91" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S90" s="3"/>
+    </row>
+    <row r="91" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
@@ -4404,13 +4625,13 @@
         <v>0</v>
       </c>
       <c r="F91" s="3">
-        <v>-100</v>
+        <v>0</v>
       </c>
       <c r="G91" s="3">
         <v>-100</v>
       </c>
       <c r="H91" s="3">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="I91" s="3">
         <v>0</v>
@@ -4422,28 +4643,31 @@
         <v>0</v>
       </c>
       <c r="L91" s="3">
+        <v>0</v>
+      </c>
+      <c r="M91" s="3">
         <v>-200</v>
       </c>
-      <c r="M91" s="3">
-        <v>0</v>
-      </c>
       <c r="N91" s="3">
         <v>0</v>
       </c>
       <c r="O91" s="3">
+        <v>0</v>
+      </c>
+      <c r="P91" s="3">
         <v>-100</v>
       </c>
-      <c r="P91" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Q91" s="3" t="s">
         <v>3</v>
       </c>
       <c r="R91" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="92" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S91" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="92" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -4492,8 +4716,11 @@
       <c r="R92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -4542,8 +4769,11 @@
       <c r="R93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
@@ -4554,13 +4784,13 @@
         <v>0</v>
       </c>
       <c r="F94" s="3">
-        <v>-100</v>
+        <v>0</v>
       </c>
       <c r="G94" s="3">
         <v>-100</v>
       </c>
       <c r="H94" s="3">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="I94" s="3">
         <v>0</v>
@@ -4572,19 +4802,19 @@
         <v>0</v>
       </c>
       <c r="L94" s="3">
+        <v>0</v>
+      </c>
+      <c r="M94" s="3">
         <v>-300</v>
       </c>
-      <c r="M94" s="3">
-        <v>0</v>
-      </c>
       <c r="N94" s="3">
-        <v>-100</v>
+        <v>0</v>
       </c>
       <c r="O94" s="3">
         <v>-100</v>
       </c>
-      <c r="P94" s="3" t="s">
-        <v>3</v>
+      <c r="P94" s="3">
+        <v>-100</v>
       </c>
       <c r="Q94" s="3" t="s">
         <v>3</v>
@@ -4592,8 +4822,11 @@
       <c r="R94" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="95" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S94" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="95" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -4612,8 +4845,9 @@
       <c r="P95" s="3"/>
       <c r="Q95" s="3"/>
       <c r="R95" s="3"/>
-    </row>
-    <row r="96" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S95" s="3"/>
+    </row>
+    <row r="96" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -4662,8 +4896,11 @@
       <c r="R96" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="97" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S96" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -4712,8 +4949,11 @@
       <c r="R97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -4762,8 +5002,11 @@
       <c r="R98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -4812,23 +5055,26 @@
       <c r="R99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
-        <v>0</v>
+        <v>11300</v>
       </c>
       <c r="E100" s="3">
+        <v>0</v>
+      </c>
+      <c r="F100" s="3">
         <v>-100</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>5500</v>
       </c>
-      <c r="G100" s="3">
-        <v>0</v>
-      </c>
       <c r="H100" s="3">
         <v>0</v>
       </c>
@@ -4836,25 +5082,25 @@
         <v>0</v>
       </c>
       <c r="J100" s="3">
+        <v>0</v>
+      </c>
+      <c r="K100" s="3">
         <v>13600</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>3000</v>
-      </c>
-      <c r="L100" s="3">
-        <v>5100</v>
       </c>
       <c r="M100" s="3">
         <v>5100</v>
       </c>
       <c r="N100" s="3">
+        <v>5100</v>
+      </c>
+      <c r="O100" s="3">
         <v>5000</v>
       </c>
-      <c r="O100" s="3">
-        <v>0</v>
-      </c>
-      <c r="P100" s="3" t="s">
-        <v>3</v>
+      <c r="P100" s="3">
+        <v>0</v>
       </c>
       <c r="Q100" s="3" t="s">
         <v>3</v>
@@ -4862,31 +5108,34 @@
       <c r="R100" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="101" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S100" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="101" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
       <c r="D101" s="3">
-        <v>0</v>
-      </c>
-      <c r="E101" s="3">
-        <v>0</v>
-      </c>
-      <c r="F101" s="3">
-        <v>0</v>
-      </c>
-      <c r="G101" s="3">
-        <v>0</v>
-      </c>
-      <c r="H101" s="3">
-        <v>0</v>
-      </c>
-      <c r="I101" s="3">
-        <v>0</v>
-      </c>
-      <c r="J101" s="3">
-        <v>0</v>
+        <v>-100</v>
+      </c>
+      <c r="E101" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="F101" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="G101" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="H101" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="I101" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="J101" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="K101" s="3">
         <v>0</v>
@@ -4912,54 +5161,60 @@
       <c r="R101" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="102" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S101" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="102" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>6600</v>
+      </c>
+      <c r="E102" s="3">
         <v>-1800</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>-3300</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>2500</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>-2600</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>-2200</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>-2500</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>10700</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>600</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>-5100</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>100</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>-2400</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>-4200</v>
       </c>
-      <c r="P102" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Q102" s="3" t="s">
         <v>3</v>
       </c>
       <c r="R102" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="S102" s="3" t="s">
         <v>3</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/RVSN_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/RVSN_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="300" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="352" uniqueCount="92">
   <si>
     <t>RVSN</t>
   </si>
@@ -663,10 +663,11 @@
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="6" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="10" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="7" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
     <col min="11" max="11" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
     <col min="12" max="12" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="13" max="13" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
@@ -695,22 +696,22 @@
         <v>45473</v>
       </c>
       <c r="E7" s="2">
+        <v>45382</v>
+      </c>
+      <c r="F7" s="2">
         <v>45291</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45199</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45107</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>45016</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>44926</v>
-      </c>
-      <c r="J7" s="2">
-        <v>44834</v>
       </c>
       <c r="K7" s="2">
         <v>44742</v>
@@ -745,25 +746,25 @@
         <v>4</v>
       </c>
       <c r="D8" s="3">
-        <v>800</v>
+        <v>400</v>
       </c>
       <c r="E8" s="3">
-        <v>0</v>
+        <v>400</v>
       </c>
       <c r="F8" s="3">
+        <v>0</v>
+      </c>
+      <c r="G8" s="3">
         <v>100</v>
       </c>
-      <c r="G8" s="3">
-        <v>0</v>
-      </c>
-      <c r="H8" s="3">
-        <v>0</v>
-      </c>
-      <c r="I8" s="3">
-        <v>0</v>
+      <c r="H8" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="I8" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="J8" s="3">
-        <v>200</v>
+        <v>0</v>
       </c>
       <c r="K8" s="3">
         <v>0</v>
@@ -798,17 +799,17 @@
         <v>5</v>
       </c>
       <c r="D9" s="3">
-        <v>400</v>
-      </c>
-      <c r="E9" s="3" t="s">
-        <v>3</v>
+        <v>200</v>
+      </c>
+      <c r="E9" s="3">
+        <v>200</v>
       </c>
       <c r="F9" s="3">
+        <v>0</v>
+      </c>
+      <c r="G9" s="3">
         <v>100</v>
       </c>
-      <c r="G9" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="H9" s="3" t="s">
         <v>3</v>
       </c>
@@ -816,7 +817,7 @@
         <v>3</v>
       </c>
       <c r="J9" s="3">
-        <v>300</v>
+        <v>0</v>
       </c>
       <c r="K9" s="3" t="s">
         <v>3</v>
@@ -851,16 +852,16 @@
         <v>6</v>
       </c>
       <c r="D10" s="3">
-        <v>400</v>
-      </c>
-      <c r="E10" s="3" t="s">
-        <v>3</v>
+        <v>200</v>
+      </c>
+      <c r="E10" s="3">
+        <v>200</v>
       </c>
       <c r="F10" s="3">
         <v>0</v>
       </c>
-      <c r="G10" s="3" t="s">
-        <v>3</v>
+      <c r="G10" s="3">
+        <v>100</v>
       </c>
       <c r="H10" s="3" t="s">
         <v>3</v>
@@ -869,7 +870,7 @@
         <v>3</v>
       </c>
       <c r="J10" s="3">
-        <v>-100</v>
+        <v>0</v>
       </c>
       <c r="K10" s="3" t="s">
         <v>3</v>
@@ -925,25 +926,25 @@
         <v>8</v>
       </c>
       <c r="D12" s="3">
-        <v>2400</v>
+        <v>1200</v>
       </c>
       <c r="E12" s="3">
+        <v>1200</v>
+      </c>
+      <c r="F12" s="3">
         <v>1600</v>
       </c>
-      <c r="F12" s="3">
+      <c r="G12" s="3">
         <v>1900</v>
-      </c>
-      <c r="G12" s="3">
-        <v>1800</v>
       </c>
       <c r="H12" s="3">
         <v>1800</v>
       </c>
       <c r="I12" s="3">
+        <v>1800</v>
+      </c>
+      <c r="J12" s="3">
         <v>1500</v>
-      </c>
-      <c r="J12" s="3">
-        <v>1700</v>
       </c>
       <c r="K12" s="3">
         <v>1700</v>
@@ -1030,26 +1031,26 @@
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="D14" s="3">
-        <v>0</v>
-      </c>
-      <c r="E14" s="3">
-        <v>0</v>
-      </c>
-      <c r="F14" s="3">
-        <v>0</v>
-      </c>
-      <c r="G14" s="3">
-        <v>0</v>
-      </c>
-      <c r="H14" s="3">
-        <v>0</v>
-      </c>
-      <c r="I14" s="3">
-        <v>0</v>
-      </c>
-      <c r="J14" s="3">
-        <v>0</v>
+      <c r="D14" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="E14" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="F14" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="G14" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="H14" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="I14" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="J14" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="K14" s="3">
         <v>0</v>
@@ -1084,25 +1085,25 @@
         <v>11</v>
       </c>
       <c r="D15" s="3">
-        <v>100</v>
-      </c>
-      <c r="E15" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="F15" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="G15" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="H15" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="I15" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="J15" s="3" t="s">
-        <v>3</v>
+        <v>0</v>
+      </c>
+      <c r="E15" s="3">
+        <v>0</v>
+      </c>
+      <c r="F15" s="3">
+        <v>0</v>
+      </c>
+      <c r="G15" s="3">
+        <v>0</v>
+      </c>
+      <c r="H15" s="3">
+        <v>0</v>
+      </c>
+      <c r="I15" s="3">
+        <v>0</v>
+      </c>
+      <c r="J15" s="3">
+        <v>0</v>
       </c>
       <c r="K15" s="3">
         <v>0</v>
@@ -1155,13 +1156,13 @@
         <v>12</v>
       </c>
       <c r="D17" s="3">
-        <v>4900</v>
+        <v>2500</v>
       </c>
       <c r="E17" s="3">
+        <v>2500</v>
+      </c>
+      <c r="F17" s="3">
         <v>2600</v>
-      </c>
-      <c r="F17" s="3">
-        <v>3000</v>
       </c>
       <c r="G17" s="3">
         <v>3000</v>
@@ -1170,10 +1171,10 @@
         <v>3000</v>
       </c>
       <c r="I17" s="3">
+        <v>3000</v>
+      </c>
+      <c r="J17" s="3">
         <v>2600</v>
-      </c>
-      <c r="J17" s="3">
-        <v>3000</v>
       </c>
       <c r="K17" s="3">
         <v>3000</v>
@@ -1208,25 +1209,25 @@
         <v>13</v>
       </c>
       <c r="D18" s="3">
-        <v>-4100</v>
+        <v>-2100</v>
       </c>
       <c r="E18" s="3">
+        <v>-2100</v>
+      </c>
+      <c r="F18" s="3">
         <v>-2600</v>
       </c>
-      <c r="F18" s="3">
-        <v>-2900</v>
-      </c>
       <c r="G18" s="3">
-        <v>-3000</v>
+        <v>-2800</v>
       </c>
       <c r="H18" s="3">
         <v>-3000</v>
       </c>
       <c r="I18" s="3">
+        <v>-3000</v>
+      </c>
+      <c r="J18" s="3">
         <v>-2600</v>
-      </c>
-      <c r="J18" s="3">
-        <v>-2800</v>
       </c>
       <c r="K18" s="3">
         <v>-3000</v>
@@ -1282,25 +1283,25 @@
         <v>15</v>
       </c>
       <c r="D20" s="3">
-        <v>-20200</v>
+        <v>9400</v>
       </c>
       <c r="E20" s="3">
-        <v>100</v>
-      </c>
-      <c r="F20" s="3">
-        <v>100</v>
-      </c>
-      <c r="G20" s="3">
-        <v>0</v>
-      </c>
-      <c r="H20" s="3">
-        <v>100</v>
-      </c>
-      <c r="I20" s="3">
-        <v>100</v>
-      </c>
-      <c r="J20" s="3">
-        <v>0</v>
+        <v>9400</v>
+      </c>
+      <c r="F20" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="G20" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="H20" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="I20" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="J20" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="K20" s="3">
         <v>100</v>
@@ -1335,25 +1336,25 @@
         <v>16</v>
       </c>
       <c r="D21" s="3">
-        <v>-24200</v>
+        <v>-11500</v>
       </c>
       <c r="E21" s="3">
+        <v>-11500</v>
+      </c>
+      <c r="F21" s="3">
+        <v>-2600</v>
+      </c>
+      <c r="G21" s="3">
+        <v>-2800</v>
+      </c>
+      <c r="H21" s="3">
+        <v>-2900</v>
+      </c>
+      <c r="I21" s="3">
+        <v>-3000</v>
+      </c>
+      <c r="J21" s="3">
         <v>-2500</v>
-      </c>
-      <c r="F21" s="3">
-        <v>-2700</v>
-      </c>
-      <c r="G21" s="3">
-        <v>-2900</v>
-      </c>
-      <c r="H21" s="3">
-        <v>-2800</v>
-      </c>
-      <c r="I21" s="3">
-        <v>-2400</v>
-      </c>
-      <c r="J21" s="3">
-        <v>-2700</v>
       </c>
       <c r="K21" s="3">
         <v>-2900</v>
@@ -1388,25 +1389,25 @@
         <v>17</v>
       </c>
       <c r="D22" s="3">
-        <v>0</v>
+        <v>700</v>
       </c>
       <c r="E22" s="3">
-        <v>0</v>
-      </c>
-      <c r="F22" s="3">
-        <v>0</v>
-      </c>
-      <c r="G22" s="3">
-        <v>0</v>
-      </c>
-      <c r="H22" s="3">
-        <v>0</v>
-      </c>
-      <c r="I22" s="3">
-        <v>0</v>
-      </c>
-      <c r="J22" s="3">
-        <v>0</v>
+        <v>700</v>
+      </c>
+      <c r="F22" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="G22" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="H22" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="I22" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="J22" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="K22" s="3">
         <v>0</v>
@@ -1441,25 +1442,25 @@
         <v>18</v>
       </c>
       <c r="D23" s="3">
-        <v>-24300</v>
+        <v>-12200</v>
       </c>
       <c r="E23" s="3">
+        <v>-12200</v>
+      </c>
+      <c r="F23" s="3">
         <v>-2500</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>-2800</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>-3000</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>-2900</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>-2500</v>
-      </c>
-      <c r="J23" s="3">
-        <v>-2800</v>
       </c>
       <c r="K23" s="3">
         <v>-2900</v>
@@ -1493,26 +1494,26 @@
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="D24" s="3">
-        <v>0</v>
-      </c>
-      <c r="E24" s="3">
-        <v>0</v>
-      </c>
-      <c r="F24" s="3">
-        <v>0</v>
-      </c>
-      <c r="G24" s="3">
-        <v>0</v>
-      </c>
-      <c r="H24" s="3">
-        <v>0</v>
-      </c>
-      <c r="I24" s="3">
-        <v>0</v>
-      </c>
-      <c r="J24" s="3">
-        <v>0</v>
+      <c r="D24" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="E24" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="F24" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="G24" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="H24" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="I24" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="J24" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="K24" s="3">
         <v>0</v>
@@ -1600,25 +1601,25 @@
         <v>21</v>
       </c>
       <c r="D26" s="3">
-        <v>-24300</v>
+        <v>-12200</v>
       </c>
       <c r="E26" s="3">
+        <v>-12200</v>
+      </c>
+      <c r="F26" s="3">
         <v>-2500</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>-2800</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>-3000</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>-2900</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>-2500</v>
-      </c>
-      <c r="J26" s="3">
-        <v>-2800</v>
       </c>
       <c r="K26" s="3">
         <v>-2900</v>
@@ -1653,25 +1654,25 @@
         <v>22</v>
       </c>
       <c r="D27" s="3">
-        <v>-24300</v>
+        <v>-12200</v>
       </c>
       <c r="E27" s="3">
+        <v>-12200</v>
+      </c>
+      <c r="F27" s="3">
         <v>-2500</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>-2800</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>-3000</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>-2900</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>-2500</v>
-      </c>
-      <c r="J27" s="3">
-        <v>-2800</v>
       </c>
       <c r="K27" s="3">
         <v>-2900</v>
@@ -1918,25 +1919,25 @@
         <v>27</v>
       </c>
       <c r="D32" s="3">
-        <v>20200</v>
+        <v>-9400</v>
       </c>
       <c r="E32" s="3">
-        <v>-100</v>
-      </c>
-      <c r="F32" s="3">
-        <v>-100</v>
-      </c>
-      <c r="G32" s="3">
-        <v>0</v>
-      </c>
-      <c r="H32" s="3">
-        <v>-100</v>
-      </c>
-      <c r="I32" s="3">
-        <v>-100</v>
-      </c>
-      <c r="J32" s="3">
-        <v>0</v>
+        <v>-9400</v>
+      </c>
+      <c r="F32" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="G32" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="H32" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="I32" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="J32" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="K32" s="3">
         <v>-100</v>
@@ -1971,25 +1972,25 @@
         <v>28</v>
       </c>
       <c r="D33" s="3">
-        <v>-24300</v>
+        <v>-12200</v>
       </c>
       <c r="E33" s="3">
+        <v>-12200</v>
+      </c>
+      <c r="F33" s="3">
         <v>-2500</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>-2800</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>-3000</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>-2900</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>-2500</v>
-      </c>
-      <c r="J33" s="3">
-        <v>-2800</v>
       </c>
       <c r="K33" s="3">
         <v>-2900</v>
@@ -2077,25 +2078,25 @@
         <v>30</v>
       </c>
       <c r="D35" s="3">
-        <v>-24300</v>
+        <v>-12200</v>
       </c>
       <c r="E35" s="3">
+        <v>-12200</v>
+      </c>
+      <c r="F35" s="3">
         <v>-2500</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>-2800</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>-3000</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>-2900</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>-2500</v>
-      </c>
-      <c r="J35" s="3">
-        <v>-2800</v>
       </c>
       <c r="K35" s="3">
         <v>-2900</v>
@@ -2138,22 +2139,22 @@
         <v>45473</v>
       </c>
       <c r="E38" s="2">
+        <v>45382</v>
+      </c>
+      <c r="F38" s="2">
         <v>45291</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45199</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45107</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>45016</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>44926</v>
-      </c>
-      <c r="J38" s="2">
-        <v>44834</v>
       </c>
       <c r="K38" s="2">
         <v>44742</v>
@@ -2233,22 +2234,22 @@
         <v>9700</v>
       </c>
       <c r="E41" s="3">
+        <v>9700</v>
+      </c>
+      <c r="F41" s="3">
         <v>3100</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>4900</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>8200</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>5600</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>8300</v>
-      </c>
-      <c r="J41" s="3">
-        <v>10400</v>
       </c>
       <c r="K41" s="3">
         <v>12900</v>
@@ -2339,19 +2340,19 @@
         <v>100</v>
       </c>
       <c r="E43" s="3">
-        <v>0</v>
-      </c>
-      <c r="F43" s="3">
-        <v>0</v>
-      </c>
-      <c r="G43" s="3" t="s">
-        <v>3</v>
+        <v>100</v>
+      </c>
+      <c r="F43" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="G43" s="3">
+        <v>0</v>
       </c>
       <c r="H43" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="I43" s="3">
-        <v>100</v>
+      <c r="I43" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="J43" s="3">
         <v>100</v>
@@ -2398,13 +2399,13 @@
         <v>1000</v>
       </c>
       <c r="G44" s="3">
+        <v>1000</v>
+      </c>
+      <c r="H44" s="3">
         <v>500</v>
       </c>
-      <c r="H44" s="3">
+      <c r="I44" s="3">
         <v>100</v>
-      </c>
-      <c r="I44" s="3" t="s">
-        <v>3</v>
       </c>
       <c r="J44" s="3" t="s">
         <v>3</v>
@@ -2442,25 +2443,25 @@
         <v>38</v>
       </c>
       <c r="D45" s="3">
-        <v>600</v>
+        <v>400</v>
       </c>
       <c r="E45" s="3">
-        <v>600</v>
+        <v>400</v>
       </c>
       <c r="F45" s="3">
-        <v>500</v>
+        <v>200</v>
       </c>
       <c r="G45" s="3">
-        <v>600</v>
+        <v>300</v>
       </c>
       <c r="H45" s="3">
-        <v>600</v>
+        <v>400</v>
       </c>
       <c r="I45" s="3">
         <v>400</v>
       </c>
       <c r="J45" s="3">
-        <v>700</v>
+        <v>100</v>
       </c>
       <c r="K45" s="3">
         <v>1000</v>
@@ -2498,22 +2499,22 @@
         <v>11400</v>
       </c>
       <c r="E46" s="3">
+        <v>11400</v>
+      </c>
+      <c r="F46" s="3">
         <v>4600</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>6400</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>9300</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>6300</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>8800</v>
-      </c>
-      <c r="J46" s="3">
-        <v>11200</v>
       </c>
       <c r="K46" s="3">
         <v>14000</v>
@@ -2547,26 +2548,26 @@
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
-      <c r="D47" s="3">
-        <v>0</v>
-      </c>
-      <c r="E47" s="3">
-        <v>0</v>
-      </c>
-      <c r="F47" s="3">
-        <v>0</v>
-      </c>
-      <c r="G47" s="3">
-        <v>0</v>
-      </c>
-      <c r="H47" s="3">
-        <v>0</v>
-      </c>
-      <c r="I47" s="3">
-        <v>0</v>
-      </c>
-      <c r="J47" s="3">
-        <v>0</v>
+      <c r="D47" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="E47" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="F47" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="G47" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="H47" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="I47" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="J47" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="K47" s="3">
         <v>0</v>
@@ -2604,22 +2605,22 @@
         <v>1100</v>
       </c>
       <c r="E48" s="3">
+        <v>1100</v>
+      </c>
+      <c r="F48" s="3">
         <v>1300</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>1400</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>1500</v>
-      </c>
-      <c r="H48" s="3">
-        <v>1600</v>
       </c>
       <c r="I48" s="3">
         <v>1600</v>
       </c>
       <c r="J48" s="3">
-        <v>1700</v>
+        <v>1600</v>
       </c>
       <c r="K48" s="3">
         <v>1800</v>
@@ -2812,26 +2813,26 @@
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
-      <c r="D52" s="3">
-        <v>0</v>
-      </c>
-      <c r="E52" s="3">
-        <v>0</v>
-      </c>
-      <c r="F52" s="3">
-        <v>0</v>
-      </c>
-      <c r="G52" s="3">
-        <v>0</v>
-      </c>
-      <c r="H52" s="3">
-        <v>0</v>
-      </c>
-      <c r="I52" s="3">
-        <v>0</v>
-      </c>
-      <c r="J52" s="3">
-        <v>0</v>
+      <c r="D52" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="E52" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="F52" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="G52" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="H52" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="I52" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="J52" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="K52" s="3">
         <v>0</v>
@@ -2922,22 +2923,22 @@
         <v>12500</v>
       </c>
       <c r="E54" s="3">
+        <v>12500</v>
+      </c>
+      <c r="F54" s="3">
         <v>5900</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>7900</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>10800</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>7900</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>10400</v>
-      </c>
-      <c r="J54" s="3">
-        <v>12900</v>
       </c>
       <c r="K54" s="3">
         <v>15700</v>
@@ -3017,19 +3018,19 @@
         <v>100</v>
       </c>
       <c r="E57" s="3">
+        <v>100</v>
+      </c>
+      <c r="F57" s="3">
         <v>200</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>300</v>
-      </c>
-      <c r="G57" s="3">
-        <v>200</v>
       </c>
       <c r="H57" s="3">
         <v>200</v>
       </c>
       <c r="I57" s="3">
-        <v>100</v>
+        <v>200</v>
       </c>
       <c r="J57" s="3">
         <v>100</v>
@@ -3067,25 +3068,25 @@
         <v>51</v>
       </c>
       <c r="D58" s="3">
-        <v>0</v>
+        <v>300</v>
       </c>
       <c r="E58" s="3">
-        <v>0</v>
+        <v>300</v>
       </c>
       <c r="F58" s="3">
-        <v>0</v>
+        <v>300</v>
       </c>
       <c r="G58" s="3">
-        <v>0</v>
+        <v>300</v>
       </c>
       <c r="H58" s="3">
-        <v>0</v>
+        <v>300</v>
       </c>
       <c r="I58" s="3">
-        <v>0</v>
+        <v>300</v>
       </c>
       <c r="J58" s="3">
-        <v>0</v>
+        <v>300</v>
       </c>
       <c r="K58" s="3" t="s">
         <v>3</v>
@@ -3120,25 +3121,25 @@
         <v>52</v>
       </c>
       <c r="D59" s="3">
-        <v>2100</v>
+        <v>1800</v>
       </c>
       <c r="E59" s="3">
-        <v>2400</v>
+        <v>1800</v>
       </c>
       <c r="F59" s="3">
-        <v>1800</v>
+        <v>1000</v>
       </c>
       <c r="G59" s="3">
-        <v>2000</v>
+        <v>0</v>
       </c>
       <c r="H59" s="3">
-        <v>1500</v>
+        <v>1700</v>
       </c>
       <c r="I59" s="3">
-        <v>1300</v>
-      </c>
-      <c r="J59" s="3">
-        <v>1300</v>
+        <v>1200</v>
+      </c>
+      <c r="J59" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="K59" s="3">
         <v>1400</v>
@@ -3176,22 +3177,22 @@
         <v>2200</v>
       </c>
       <c r="E60" s="3">
+        <v>2200</v>
+      </c>
+      <c r="F60" s="3">
         <v>2600</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>2000</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>2200</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>1800</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>1400</v>
-      </c>
-      <c r="J60" s="3">
-        <v>1500</v>
       </c>
       <c r="K60" s="3">
         <v>1500</v>
@@ -3226,25 +3227,25 @@
         <v>54</v>
       </c>
       <c r="D61" s="3">
-        <v>0</v>
+        <v>400</v>
       </c>
       <c r="E61" s="3">
-        <v>0</v>
+        <v>400</v>
       </c>
       <c r="F61" s="3">
-        <v>0</v>
+        <v>500</v>
       </c>
       <c r="G61" s="3">
-        <v>0</v>
+        <v>500</v>
       </c>
       <c r="H61" s="3">
-        <v>0</v>
+        <v>600</v>
       </c>
       <c r="I61" s="3">
-        <v>0</v>
+        <v>700</v>
       </c>
       <c r="J61" s="3">
-        <v>0</v>
+        <v>800</v>
       </c>
       <c r="K61" s="3">
         <v>0</v>
@@ -3278,26 +3279,26 @@
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
-      <c r="D62" s="3">
-        <v>400</v>
-      </c>
-      <c r="E62" s="3">
-        <v>500</v>
-      </c>
-      <c r="F62" s="3">
-        <v>500</v>
-      </c>
-      <c r="G62" s="3">
-        <v>600</v>
-      </c>
-      <c r="H62" s="3">
-        <v>700</v>
-      </c>
-      <c r="I62" s="3">
-        <v>800</v>
-      </c>
-      <c r="J62" s="3">
-        <v>800</v>
+      <c r="D62" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="E62" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="F62" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="G62" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="H62" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="I62" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="J62" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="K62" s="3">
         <v>900</v>
@@ -3494,22 +3495,22 @@
         <v>2600</v>
       </c>
       <c r="E66" s="3">
+        <v>2600</v>
+      </c>
+      <c r="F66" s="3">
         <v>3100</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>2600</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>2800</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>2500</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>2200</v>
-      </c>
-      <c r="J66" s="3">
-        <v>2300</v>
       </c>
       <c r="K66" s="3">
         <v>2500</v>
@@ -3780,22 +3781,22 @@
         <v>-90300</v>
       </c>
       <c r="E72" s="3">
+        <v>-90300</v>
+      </c>
+      <c r="F72" s="3">
         <v>-66000</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>-63400</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>-60600</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>-57700</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>-54800</v>
-      </c>
-      <c r="J72" s="3">
-        <v>-52400</v>
       </c>
       <c r="K72" s="3">
         <v>-49600</v>
@@ -3992,22 +3993,22 @@
         <v>9900</v>
       </c>
       <c r="E76" s="3">
+        <v>9900</v>
+      </c>
+      <c r="F76" s="3">
         <v>2800</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>5300</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>8000</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>5400</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>8300</v>
-      </c>
-      <c r="J76" s="3">
-        <v>10600</v>
       </c>
       <c r="K76" s="3">
         <v>13300</v>
@@ -4103,22 +4104,22 @@
         <v>45473</v>
       </c>
       <c r="E80" s="2">
+        <v>45382</v>
+      </c>
+      <c r="F80" s="2">
         <v>45291</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45199</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45107</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>45016</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>44926</v>
-      </c>
-      <c r="J80" s="2">
-        <v>44834</v>
       </c>
       <c r="K80" s="2">
         <v>44742</v>
@@ -4153,25 +4154,25 @@
         <v>28</v>
       </c>
       <c r="D81" s="3">
-        <v>-24300</v>
+        <v>-12200</v>
       </c>
       <c r="E81" s="3">
+        <v>-12200</v>
+      </c>
+      <c r="F81" s="3">
         <v>-2500</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>-2800</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>-3000</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>-2900</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>-2500</v>
-      </c>
-      <c r="J81" s="3">
-        <v>-2800</v>
       </c>
       <c r="K81" s="3">
         <v>-2900</v>
@@ -4227,7 +4228,7 @@
         <v>72</v>
       </c>
       <c r="D83" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="E83" s="3">
         <v>0</v>
@@ -4545,25 +4546,25 @@
         <v>78</v>
       </c>
       <c r="D89" s="3">
-        <v>-4600</v>
+        <v>-2300</v>
       </c>
       <c r="E89" s="3">
+        <v>-2300</v>
+      </c>
+      <c r="F89" s="3">
         <v>-1900</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>-3200</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>-2900</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>-2500</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>-2100</v>
-      </c>
-      <c r="J89" s="3">
-        <v>-2500</v>
       </c>
       <c r="K89" s="3">
         <v>-2900</v>
@@ -4628,13 +4629,13 @@
         <v>0</v>
       </c>
       <c r="G91" s="3">
-        <v>-100</v>
+        <v>0</v>
       </c>
       <c r="H91" s="3">
         <v>-100</v>
       </c>
       <c r="I91" s="3">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="J91" s="3">
         <v>0</v>
@@ -4787,13 +4788,13 @@
         <v>0</v>
       </c>
       <c r="G94" s="3">
-        <v>-100</v>
+        <v>0</v>
       </c>
       <c r="H94" s="3">
         <v>-100</v>
       </c>
       <c r="I94" s="3">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="J94" s="3">
         <v>0</v>
@@ -4851,26 +4852,26 @@
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
-      <c r="D96" s="3">
-        <v>0</v>
-      </c>
-      <c r="E96" s="3">
-        <v>0</v>
-      </c>
-      <c r="F96" s="3">
-        <v>0</v>
-      </c>
-      <c r="G96" s="3">
-        <v>0</v>
-      </c>
-      <c r="H96" s="3">
-        <v>0</v>
-      </c>
-      <c r="I96" s="3">
-        <v>0</v>
-      </c>
-      <c r="J96" s="3">
-        <v>0</v>
+      <c r="D96" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="E96" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="F96" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="G96" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="H96" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="I96" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="J96" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="K96" s="3">
         <v>0</v>
@@ -5064,22 +5065,22 @@
         <v>89</v>
       </c>
       <c r="D100" s="3">
-        <v>11300</v>
+        <v>5600</v>
       </c>
       <c r="E100" s="3">
-        <v>0</v>
+        <v>5600</v>
       </c>
       <c r="F100" s="3">
+        <v>0</v>
+      </c>
+      <c r="G100" s="3">
         <v>-100</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>5500</v>
       </c>
-      <c r="H100" s="3">
-        <v>0</v>
-      </c>
-      <c r="I100" s="3">
-        <v>0</v>
+      <c r="I100" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="J100" s="3">
         <v>0</v>
@@ -5116,8 +5117,8 @@
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
-      <c r="D101" s="3">
-        <v>-100</v>
+      <c r="D101" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="E101" s="3" t="s">
         <v>3</v>
@@ -5170,25 +5171,25 @@
         <v>91</v>
       </c>
       <c r="D102" s="3">
-        <v>6600</v>
+        <v>3300</v>
       </c>
       <c r="E102" s="3">
+        <v>3300</v>
+      </c>
+      <c r="F102" s="3">
         <v>-1800</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>-3300</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>2500</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>-2600</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>-2200</v>
-      </c>
-      <c r="J102" s="3">
-        <v>-2500</v>
       </c>
       <c r="K102" s="3">
         <v>10700</v>

--- a/AAII_Financials/Quarterly/RVSN_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/RVSN_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="352" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="365" uniqueCount="92">
   <si>
     <t>RVSN</t>
   </si>
@@ -656,145 +656,158 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:S102"/>
+  <dimension ref="A5:U102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="7.5703125" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="7" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="4" max="5" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="9" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="15" max="15" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
     <col min="16" max="16" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="19" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="20" max="16384" width="9.140625" style="1"/>
+    <col min="17" max="17" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="19" max="21" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="22" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:21" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:21" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45657</v>
+      </c>
+      <c r="E7" s="2">
+        <v>45565</v>
+      </c>
+      <c r="F7" s="2">
         <v>45473</v>
       </c>
-      <c r="E7" s="2">
+      <c r="G7" s="2">
         <v>45382</v>
       </c>
-      <c r="F7" s="2">
+      <c r="H7" s="2">
         <v>45291</v>
       </c>
-      <c r="G7" s="2">
+      <c r="I7" s="2">
         <v>45199</v>
       </c>
-      <c r="H7" s="2">
+      <c r="J7" s="2">
         <v>45107</v>
       </c>
-      <c r="I7" s="2">
+      <c r="K7" s="2">
         <v>45016</v>
       </c>
-      <c r="J7" s="2">
+      <c r="L7" s="2">
         <v>44926</v>
       </c>
-      <c r="K7" s="2">
+      <c r="M7" s="2">
         <v>44742</v>
       </c>
-      <c r="L7" s="2">
+      <c r="N7" s="2">
         <v>44651</v>
       </c>
-      <c r="M7" s="2">
+      <c r="O7" s="2">
         <v>44561</v>
       </c>
-      <c r="N7" s="2">
+      <c r="P7" s="2">
         <v>44377</v>
       </c>
-      <c r="O7" s="2">
+      <c r="Q7" s="2">
         <v>44196</v>
       </c>
-      <c r="P7" s="2">
+      <c r="R7" s="2">
         <v>44012</v>
       </c>
-      <c r="Q7" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="R7" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="S7" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="8" spans="1:19" x14ac:dyDescent="0.2">
+      <c r="T7" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="U7" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="8" spans="1:21" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D8" s="3">
+        <v>300</v>
+      </c>
+      <c r="E8" s="3">
+        <v>300</v>
+      </c>
+      <c r="F8" s="3">
         <v>400</v>
       </c>
-      <c r="E8" s="3">
+      <c r="G8" s="3">
         <v>400</v>
       </c>
-      <c r="F8" s="3">
-        <v>0</v>
-      </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
+        <v>0</v>
+      </c>
+      <c r="I8" s="3">
         <v>100</v>
       </c>
-      <c r="H8" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="I8" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="J8" s="3">
-        <v>0</v>
-      </c>
-      <c r="K8" s="3">
-        <v>0</v>
+      <c r="J8" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="K8" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="L8" s="3">
+        <v>0</v>
+      </c>
+      <c r="M8" s="3">
+        <v>0</v>
+      </c>
+      <c r="N8" s="3">
         <v>200</v>
       </c>
-      <c r="M8" s="3">
+      <c r="O8" s="3">
         <v>900</v>
       </c>
-      <c r="N8" s="3">
+      <c r="P8" s="3">
         <v>400</v>
       </c>
-      <c r="O8" s="3">
-        <v>0</v>
-      </c>
-      <c r="P8" s="3">
-        <v>0</v>
-      </c>
-      <c r="Q8" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="R8" s="3" t="s">
-        <v>3</v>
+      <c r="Q8" s="3">
+        <v>0</v>
+      </c>
+      <c r="R8" s="3">
+        <v>0</v>
       </c>
       <c r="S8" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="9" spans="1:19" x14ac:dyDescent="0.2">
+      <c r="T8" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="U8" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="9" spans="1:21" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>5</v>
       </c>
@@ -805,38 +818,38 @@
         <v>200</v>
       </c>
       <c r="F9" s="3">
-        <v>0</v>
+        <v>200</v>
       </c>
       <c r="G9" s="3">
+        <v>200</v>
+      </c>
+      <c r="H9" s="3">
+        <v>0</v>
+      </c>
+      <c r="I9" s="3">
         <v>100</v>
       </c>
-      <c r="H9" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="I9" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="J9" s="3">
-        <v>0</v>
+      <c r="J9" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="K9" s="3" t="s">
         <v>3</v>
       </c>
       <c r="L9" s="3">
+        <v>0</v>
+      </c>
+      <c r="M9" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="N9" s="3">
         <v>400</v>
       </c>
-      <c r="M9" s="3">
+      <c r="O9" s="3">
         <v>700</v>
       </c>
-      <c r="N9" s="3">
+      <c r="P9" s="3">
         <v>100</v>
       </c>
-      <c r="O9" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="P9" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Q9" s="3" t="s">
         <v>3</v>
       </c>
@@ -846,50 +859,56 @@
       <c r="S9" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="10" spans="1:19" x14ac:dyDescent="0.2">
+      <c r="T9" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="U9" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="10" spans="1:21" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D10" s="3">
+        <v>0</v>
+      </c>
+      <c r="E10" s="3">
+        <v>0</v>
+      </c>
+      <c r="F10" s="3">
         <v>200</v>
       </c>
-      <c r="E10" s="3">
+      <c r="G10" s="3">
         <v>200</v>
       </c>
-      <c r="F10" s="3">
-        <v>0</v>
-      </c>
-      <c r="G10" s="3">
+      <c r="H10" s="3">
+        <v>0</v>
+      </c>
+      <c r="I10" s="3">
         <v>100</v>
       </c>
-      <c r="H10" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="I10" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="J10" s="3">
-        <v>0</v>
+      <c r="J10" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="K10" s="3" t="s">
         <v>3</v>
       </c>
       <c r="L10" s="3">
+        <v>0</v>
+      </c>
+      <c r="M10" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="N10" s="3">
         <v>-200</v>
       </c>
-      <c r="M10" s="3">
+      <c r="O10" s="3">
         <v>200</v>
       </c>
-      <c r="N10" s="3">
+      <c r="P10" s="3">
         <v>300</v>
       </c>
-      <c r="O10" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="P10" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Q10" s="3" t="s">
         <v>3</v>
       </c>
@@ -899,8 +918,14 @@
       <c r="S10" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="11" spans="1:19" x14ac:dyDescent="0.2">
+      <c r="T10" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="U10" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="11" spans="1:21" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -920,61 +945,69 @@
       <c r="Q11" s="3"/>
       <c r="R11" s="3"/>
       <c r="S11" s="3"/>
-    </row>
-    <row r="12" spans="1:19" x14ac:dyDescent="0.2">
+      <c r="T11" s="3"/>
+      <c r="U11" s="3"/>
+    </row>
+    <row r="12" spans="1:21" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
       <c r="D12" s="3">
+        <v>1400</v>
+      </c>
+      <c r="E12" s="3">
+        <v>1400</v>
+      </c>
+      <c r="F12" s="3">
         <v>1200</v>
       </c>
-      <c r="E12" s="3">
+      <c r="G12" s="3">
         <v>1200</v>
       </c>
-      <c r="F12" s="3">
+      <c r="H12" s="3">
         <v>1600</v>
       </c>
-      <c r="G12" s="3">
+      <c r="I12" s="3">
         <v>1900</v>
       </c>
-      <c r="H12" s="3">
+      <c r="J12" s="3">
         <v>1800</v>
       </c>
-      <c r="I12" s="3">
+      <c r="K12" s="3">
         <v>1800</v>
       </c>
-      <c r="J12" s="3">
+      <c r="L12" s="3">
         <v>1500</v>
       </c>
-      <c r="K12" s="3">
+      <c r="M12" s="3">
         <v>1700</v>
       </c>
-      <c r="L12" s="3">
+      <c r="N12" s="3">
         <v>1400</v>
-      </c>
-      <c r="M12" s="3">
-        <v>7200</v>
-      </c>
-      <c r="N12" s="3">
-        <v>3800</v>
       </c>
       <c r="O12" s="3">
         <v>7200</v>
       </c>
       <c r="P12" s="3">
+        <v>3800</v>
+      </c>
+      <c r="Q12" s="3">
+        <v>7200</v>
+      </c>
+      <c r="R12" s="3">
         <v>3600</v>
       </c>
-      <c r="Q12" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="R12" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="S12" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="13" spans="1:19" x14ac:dyDescent="0.2">
+      <c r="T12" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="U12" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="13" spans="1:21" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1026,8 +1059,14 @@
       <c r="S13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:19" x14ac:dyDescent="0.2">
+      <c r="T13" s="3">
+        <v>0</v>
+      </c>
+      <c r="U13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:21" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
@@ -1052,11 +1091,11 @@
       <c r="J14" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="K14" s="3">
-        <v>0</v>
-      </c>
-      <c r="L14" s="3">
-        <v>0</v>
+      <c r="K14" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="L14" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="M14" s="3">
         <v>0</v>
@@ -1079,8 +1118,14 @@
       <c r="S14" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="15" spans="1:19" x14ac:dyDescent="0.2">
+      <c r="T14" s="3">
+        <v>0</v>
+      </c>
+      <c r="U14" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:21" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
@@ -1132,8 +1177,14 @@
       <c r="S15" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="16" spans="1:19" x14ac:dyDescent="0.2">
+      <c r="T15" s="3">
+        <v>0</v>
+      </c>
+      <c r="U15" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:21" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1150,31 +1201,33 @@
       <c r="Q16" s="3"/>
       <c r="R16" s="3"/>
       <c r="S16" s="3"/>
-    </row>
-    <row r="17" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T16" s="3"/>
+      <c r="U16" s="3"/>
+    </row>
+    <row r="17" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>2800</v>
+      </c>
+      <c r="E17" s="3">
+        <v>2800</v>
+      </c>
+      <c r="F17" s="3">
         <v>2500</v>
       </c>
-      <c r="E17" s="3">
+      <c r="G17" s="3">
         <v>2500</v>
       </c>
-      <c r="F17" s="3">
+      <c r="H17" s="3">
         <v>2600</v>
-      </c>
-      <c r="G17" s="3">
-        <v>3000</v>
-      </c>
-      <c r="H17" s="3">
-        <v>3000</v>
       </c>
       <c r="I17" s="3">
         <v>3000</v>
       </c>
       <c r="J17" s="3">
-        <v>2600</v>
+        <v>3000</v>
       </c>
       <c r="K17" s="3">
         <v>3000</v>
@@ -1183,81 +1236,93 @@
         <v>2600</v>
       </c>
       <c r="M17" s="3">
+        <v>3000</v>
+      </c>
+      <c r="N17" s="3">
+        <v>2600</v>
+      </c>
+      <c r="O17" s="3">
         <v>11200</v>
       </c>
-      <c r="N17" s="3">
+      <c r="P17" s="3">
         <v>5700</v>
       </c>
-      <c r="O17" s="3">
+      <c r="Q17" s="3">
         <v>10700</v>
       </c>
-      <c r="P17" s="3">
+      <c r="R17" s="3">
         <v>5100</v>
       </c>
-      <c r="Q17" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="R17" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="S17" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="18" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T17" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="U17" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="18" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>-2500</v>
+      </c>
+      <c r="E18" s="3">
+        <v>-2500</v>
+      </c>
+      <c r="F18" s="3">
         <v>-2100</v>
       </c>
-      <c r="E18" s="3">
+      <c r="G18" s="3">
         <v>-2100</v>
       </c>
-      <c r="F18" s="3">
+      <c r="H18" s="3">
         <v>-2600</v>
       </c>
-      <c r="G18" s="3">
+      <c r="I18" s="3">
         <v>-2800</v>
       </c>
-      <c r="H18" s="3">
+      <c r="J18" s="3">
         <v>-3000</v>
-      </c>
-      <c r="I18" s="3">
-        <v>-3000</v>
-      </c>
-      <c r="J18" s="3">
-        <v>-2600</v>
       </c>
       <c r="K18" s="3">
         <v>-3000</v>
       </c>
       <c r="L18" s="3">
+        <v>-2600</v>
+      </c>
+      <c r="M18" s="3">
+        <v>-3000</v>
+      </c>
+      <c r="N18" s="3">
         <v>-2400</v>
       </c>
-      <c r="M18" s="3">
+      <c r="O18" s="3">
         <v>-10300</v>
       </c>
-      <c r="N18" s="3">
+      <c r="P18" s="3">
         <v>-5300</v>
       </c>
-      <c r="O18" s="3">
+      <c r="Q18" s="3">
         <v>-10700</v>
       </c>
-      <c r="P18" s="3">
+      <c r="R18" s="3">
         <v>-5100</v>
       </c>
-      <c r="Q18" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="R18" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="S18" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="19" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T18" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="U18" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="19" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1277,23 +1342,25 @@
       <c r="Q19" s="3"/>
       <c r="R19" s="3"/>
       <c r="S19" s="3"/>
-    </row>
-    <row r="20" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T19" s="3"/>
+      <c r="U19" s="3"/>
+    </row>
+    <row r="20" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3">
+        <v>900</v>
+      </c>
+      <c r="E20" s="3">
+        <v>900</v>
+      </c>
+      <c r="F20" s="3">
         <v>9400</v>
       </c>
-      <c r="E20" s="3">
+      <c r="G20" s="3">
         <v>9400</v>
       </c>
-      <c r="F20" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="G20" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="H20" s="3" t="s">
         <v>3</v>
       </c>
@@ -1303,103 +1370,115 @@
       <c r="J20" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="K20" s="3">
-        <v>100</v>
-      </c>
-      <c r="L20" s="3">
-        <v>0</v>
+      <c r="K20" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="L20" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="M20" s="3">
         <v>100</v>
       </c>
       <c r="N20" s="3">
+        <v>0</v>
+      </c>
+      <c r="O20" s="3">
         <v>100</v>
       </c>
-      <c r="O20" s="3">
-        <v>0</v>
-      </c>
       <c r="P20" s="3">
-        <v>0</v>
-      </c>
-      <c r="Q20" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="R20" s="3" t="s">
-        <v>3</v>
+        <v>100</v>
+      </c>
+      <c r="Q20" s="3">
+        <v>0</v>
+      </c>
+      <c r="R20" s="3">
+        <v>0</v>
       </c>
       <c r="S20" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="21" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T20" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="U20" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="21" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
+        <v>-3300</v>
+      </c>
+      <c r="E21" s="3">
+        <v>-3300</v>
+      </c>
+      <c r="F21" s="3">
         <v>-11500</v>
       </c>
-      <c r="E21" s="3">
+      <c r="G21" s="3">
         <v>-11500</v>
       </c>
-      <c r="F21" s="3">
+      <c r="H21" s="3">
         <v>-2600</v>
       </c>
-      <c r="G21" s="3">
+      <c r="I21" s="3">
         <v>-2800</v>
       </c>
-      <c r="H21" s="3">
+      <c r="J21" s="3">
         <v>-2900</v>
       </c>
-      <c r="I21" s="3">
+      <c r="K21" s="3">
         <v>-3000</v>
       </c>
-      <c r="J21" s="3">
+      <c r="L21" s="3">
         <v>-2500</v>
       </c>
-      <c r="K21" s="3">
+      <c r="M21" s="3">
         <v>-2900</v>
       </c>
-      <c r="L21" s="3">
+      <c r="N21" s="3">
         <v>-2300</v>
       </c>
-      <c r="M21" s="3">
+      <c r="O21" s="3">
         <v>-10100</v>
       </c>
-      <c r="N21" s="3">
+      <c r="P21" s="3">
         <v>-5100</v>
       </c>
-      <c r="O21" s="3">
+      <c r="Q21" s="3">
         <v>-10500</v>
       </c>
-      <c r="P21" s="3">
+      <c r="R21" s="3">
         <v>-5000</v>
       </c>
-      <c r="Q21" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="R21" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="S21" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="22" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T21" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="U21" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="22" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
       <c r="D22" s="3">
+        <v>-600</v>
+      </c>
+      <c r="E22" s="3">
+        <v>-600</v>
+      </c>
+      <c r="F22" s="3">
         <v>700</v>
       </c>
-      <c r="E22" s="3">
+      <c r="G22" s="3">
         <v>700</v>
       </c>
-      <c r="F22" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="G22" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="H22" s="3" t="s">
         <v>3</v>
       </c>
@@ -1409,11 +1488,11 @@
       <c r="J22" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="K22" s="3">
-        <v>0</v>
-      </c>
-      <c r="L22" s="3">
-        <v>0</v>
+      <c r="K22" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="L22" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="M22" s="3">
         <v>0</v>
@@ -1436,61 +1515,73 @@
       <c r="S22" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="23" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T22" s="3">
+        <v>0</v>
+      </c>
+      <c r="U22" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>-3200</v>
+      </c>
+      <c r="E23" s="3">
+        <v>-3200</v>
+      </c>
+      <c r="F23" s="3">
         <v>-12200</v>
       </c>
-      <c r="E23" s="3">
+      <c r="G23" s="3">
         <v>-12200</v>
       </c>
-      <c r="F23" s="3">
+      <c r="H23" s="3">
         <v>-2500</v>
       </c>
-      <c r="G23" s="3">
+      <c r="I23" s="3">
         <v>-2800</v>
       </c>
-      <c r="H23" s="3">
+      <c r="J23" s="3">
         <v>-3000</v>
-      </c>
-      <c r="I23" s="3">
-        <v>-2900</v>
-      </c>
-      <c r="J23" s="3">
-        <v>-2500</v>
       </c>
       <c r="K23" s="3">
         <v>-2900</v>
       </c>
       <c r="L23" s="3">
+        <v>-2500</v>
+      </c>
+      <c r="M23" s="3">
+        <v>-2900</v>
+      </c>
+      <c r="N23" s="3">
         <v>-2300</v>
       </c>
-      <c r="M23" s="3">
+      <c r="O23" s="3">
         <v>-10200</v>
-      </c>
-      <c r="N23" s="3">
-        <v>-5100</v>
-      </c>
-      <c r="O23" s="3">
-        <v>-10700</v>
       </c>
       <c r="P23" s="3">
         <v>-5100</v>
       </c>
-      <c r="Q23" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="R23" s="3" t="s">
-        <v>3</v>
+      <c r="Q23" s="3">
+        <v>-10700</v>
+      </c>
+      <c r="R23" s="3">
+        <v>-5100</v>
       </c>
       <c r="S23" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="24" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T23" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="U23" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="24" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
@@ -1515,11 +1606,11 @@
       <c r="J24" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="K24" s="3">
-        <v>0</v>
-      </c>
-      <c r="L24" s="3">
-        <v>0</v>
+      <c r="K24" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="L24" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="M24" s="3">
         <v>0</v>
@@ -1542,8 +1633,14 @@
       <c r="S24" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="25" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T24" s="3">
+        <v>0</v>
+      </c>
+      <c r="U24" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -1595,114 +1692,132 @@
       <c r="S25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T25" s="3">
+        <v>0</v>
+      </c>
+      <c r="U25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>-3200</v>
+      </c>
+      <c r="E26" s="3">
+        <v>-3200</v>
+      </c>
+      <c r="F26" s="3">
         <v>-12200</v>
       </c>
-      <c r="E26" s="3">
+      <c r="G26" s="3">
         <v>-12200</v>
       </c>
-      <c r="F26" s="3">
+      <c r="H26" s="3">
         <v>-2500</v>
       </c>
-      <c r="G26" s="3">
+      <c r="I26" s="3">
         <v>-2800</v>
       </c>
-      <c r="H26" s="3">
+      <c r="J26" s="3">
         <v>-3000</v>
-      </c>
-      <c r="I26" s="3">
-        <v>-2900</v>
-      </c>
-      <c r="J26" s="3">
-        <v>-2500</v>
       </c>
       <c r="K26" s="3">
         <v>-2900</v>
       </c>
       <c r="L26" s="3">
+        <v>-2500</v>
+      </c>
+      <c r="M26" s="3">
+        <v>-2900</v>
+      </c>
+      <c r="N26" s="3">
         <v>-2300</v>
       </c>
-      <c r="M26" s="3">
+      <c r="O26" s="3">
         <v>-10200</v>
-      </c>
-      <c r="N26" s="3">
-        <v>-5100</v>
-      </c>
-      <c r="O26" s="3">
-        <v>-10700</v>
       </c>
       <c r="P26" s="3">
         <v>-5100</v>
       </c>
-      <c r="Q26" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="R26" s="3" t="s">
-        <v>3</v>
+      <c r="Q26" s="3">
+        <v>-10700</v>
+      </c>
+      <c r="R26" s="3">
+        <v>-5100</v>
       </c>
       <c r="S26" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="27" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T26" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="U26" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="27" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>-3200</v>
+      </c>
+      <c r="E27" s="3">
+        <v>-3200</v>
+      </c>
+      <c r="F27" s="3">
         <v>-12200</v>
       </c>
-      <c r="E27" s="3">
+      <c r="G27" s="3">
         <v>-12200</v>
       </c>
-      <c r="F27" s="3">
+      <c r="H27" s="3">
         <v>-2500</v>
       </c>
-      <c r="G27" s="3">
+      <c r="I27" s="3">
         <v>-2800</v>
       </c>
-      <c r="H27" s="3">
+      <c r="J27" s="3">
         <v>-3000</v>
-      </c>
-      <c r="I27" s="3">
-        <v>-2900</v>
-      </c>
-      <c r="J27" s="3">
-        <v>-2500</v>
       </c>
       <c r="K27" s="3">
         <v>-2900</v>
       </c>
       <c r="L27" s="3">
+        <v>-2500</v>
+      </c>
+      <c r="M27" s="3">
+        <v>-2900</v>
+      </c>
+      <c r="N27" s="3">
         <v>-2300</v>
       </c>
-      <c r="M27" s="3">
+      <c r="O27" s="3">
         <v>-10200</v>
-      </c>
-      <c r="N27" s="3">
-        <v>-5100</v>
-      </c>
-      <c r="O27" s="3">
-        <v>-10700</v>
       </c>
       <c r="P27" s="3">
         <v>-5100</v>
       </c>
-      <c r="Q27" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="R27" s="3" t="s">
-        <v>3</v>
+      <c r="Q27" s="3">
+        <v>-10700</v>
+      </c>
+      <c r="R27" s="3">
+        <v>-5100</v>
       </c>
       <c r="S27" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="28" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T27" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="U27" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="28" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -1754,8 +1869,14 @@
       <c r="S28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T28" s="3">
+        <v>0</v>
+      </c>
+      <c r="U28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -1807,8 +1928,14 @@
       <c r="S29" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="30" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T29" s="3">
+        <v>0</v>
+      </c>
+      <c r="U29" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -1860,8 +1987,14 @@
       <c r="S30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T30" s="3">
+        <v>0</v>
+      </c>
+      <c r="U30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -1913,23 +2046,29 @@
       <c r="S31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T31" s="3">
+        <v>0</v>
+      </c>
+      <c r="U31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
+        <v>-900</v>
+      </c>
+      <c r="E32" s="3">
+        <v>-900</v>
+      </c>
+      <c r="F32" s="3">
         <v>-9400</v>
       </c>
-      <c r="E32" s="3">
+      <c r="G32" s="3">
         <v>-9400</v>
       </c>
-      <c r="F32" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="G32" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="H32" s="3" t="s">
         <v>3</v>
       </c>
@@ -1939,88 +2078,100 @@
       <c r="J32" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="K32" s="3">
-        <v>-100</v>
-      </c>
-      <c r="L32" s="3">
-        <v>0</v>
+      <c r="K32" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="L32" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="M32" s="3">
         <v>-100</v>
       </c>
       <c r="N32" s="3">
+        <v>0</v>
+      </c>
+      <c r="O32" s="3">
         <v>-100</v>
       </c>
-      <c r="O32" s="3">
-        <v>0</v>
-      </c>
       <c r="P32" s="3">
-        <v>0</v>
-      </c>
-      <c r="Q32" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="R32" s="3" t="s">
-        <v>3</v>
+        <v>-100</v>
+      </c>
+      <c r="Q32" s="3">
+        <v>0</v>
+      </c>
+      <c r="R32" s="3">
+        <v>0</v>
       </c>
       <c r="S32" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="33" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T32" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="U32" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="33" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>-3200</v>
+      </c>
+      <c r="E33" s="3">
+        <v>-3200</v>
+      </c>
+      <c r="F33" s="3">
         <v>-12200</v>
       </c>
-      <c r="E33" s="3">
+      <c r="G33" s="3">
         <v>-12200</v>
       </c>
-      <c r="F33" s="3">
+      <c r="H33" s="3">
         <v>-2500</v>
       </c>
-      <c r="G33" s="3">
+      <c r="I33" s="3">
         <v>-2800</v>
       </c>
-      <c r="H33" s="3">
+      <c r="J33" s="3">
         <v>-3000</v>
-      </c>
-      <c r="I33" s="3">
-        <v>-2900</v>
-      </c>
-      <c r="J33" s="3">
-        <v>-2500</v>
       </c>
       <c r="K33" s="3">
         <v>-2900</v>
       </c>
       <c r="L33" s="3">
+        <v>-2500</v>
+      </c>
+      <c r="M33" s="3">
+        <v>-2900</v>
+      </c>
+      <c r="N33" s="3">
         <v>-2300</v>
       </c>
-      <c r="M33" s="3">
+      <c r="O33" s="3">
         <v>-10200</v>
-      </c>
-      <c r="N33" s="3">
-        <v>-5100</v>
-      </c>
-      <c r="O33" s="3">
-        <v>-10700</v>
       </c>
       <c r="P33" s="3">
         <v>-5100</v>
       </c>
-      <c r="Q33" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="R33" s="3" t="s">
-        <v>3</v>
+      <c r="Q33" s="3">
+        <v>-10700</v>
+      </c>
+      <c r="R33" s="3">
+        <v>-5100</v>
       </c>
       <c r="S33" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="34" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T33" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="U33" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="34" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -2072,119 +2223,137 @@
       <c r="S34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T34" s="3">
+        <v>0</v>
+      </c>
+      <c r="U34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>-3200</v>
+      </c>
+      <c r="E35" s="3">
+        <v>-3200</v>
+      </c>
+      <c r="F35" s="3">
         <v>-12200</v>
       </c>
-      <c r="E35" s="3">
+      <c r="G35" s="3">
         <v>-12200</v>
       </c>
-      <c r="F35" s="3">
+      <c r="H35" s="3">
         <v>-2500</v>
       </c>
-      <c r="G35" s="3">
+      <c r="I35" s="3">
         <v>-2800</v>
       </c>
-      <c r="H35" s="3">
+      <c r="J35" s="3">
         <v>-3000</v>
-      </c>
-      <c r="I35" s="3">
-        <v>-2900</v>
-      </c>
-      <c r="J35" s="3">
-        <v>-2500</v>
       </c>
       <c r="K35" s="3">
         <v>-2900</v>
       </c>
       <c r="L35" s="3">
+        <v>-2500</v>
+      </c>
+      <c r="M35" s="3">
+        <v>-2900</v>
+      </c>
+      <c r="N35" s="3">
         <v>-2300</v>
       </c>
-      <c r="M35" s="3">
+      <c r="O35" s="3">
         <v>-10200</v>
-      </c>
-      <c r="N35" s="3">
-        <v>-5100</v>
-      </c>
-      <c r="O35" s="3">
-        <v>-10700</v>
       </c>
       <c r="P35" s="3">
         <v>-5100</v>
       </c>
-      <c r="Q35" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="R35" s="3" t="s">
-        <v>3</v>
+      <c r="Q35" s="3">
+        <v>-10700</v>
+      </c>
+      <c r="R35" s="3">
+        <v>-5100</v>
       </c>
       <c r="S35" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="37" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T35" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="U35" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="37" spans="2:21" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:19" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45657</v>
+      </c>
+      <c r="E38" s="2">
+        <v>45565</v>
+      </c>
+      <c r="F38" s="2">
         <v>45473</v>
       </c>
-      <c r="E38" s="2">
+      <c r="G38" s="2">
         <v>45382</v>
       </c>
-      <c r="F38" s="2">
+      <c r="H38" s="2">
         <v>45291</v>
       </c>
-      <c r="G38" s="2">
+      <c r="I38" s="2">
         <v>45199</v>
       </c>
-      <c r="H38" s="2">
+      <c r="J38" s="2">
         <v>45107</v>
       </c>
-      <c r="I38" s="2">
+      <c r="K38" s="2">
         <v>45016</v>
       </c>
-      <c r="J38" s="2">
+      <c r="L38" s="2">
         <v>44926</v>
       </c>
-      <c r="K38" s="2">
+      <c r="M38" s="2">
         <v>44742</v>
       </c>
-      <c r="L38" s="2">
+      <c r="N38" s="2">
         <v>44651</v>
       </c>
-      <c r="M38" s="2">
+      <c r="O38" s="2">
         <v>44561</v>
       </c>
-      <c r="N38" s="2">
+      <c r="P38" s="2">
         <v>44377</v>
       </c>
-      <c r="O38" s="2">
+      <c r="Q38" s="2">
         <v>44196</v>
       </c>
-      <c r="P38" s="2">
+      <c r="R38" s="2">
         <v>44012</v>
       </c>
-      <c r="Q38" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="R38" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="S38" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="39" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T38" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="U38" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="39" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -2204,8 +2373,10 @@
       <c r="Q39" s="3"/>
       <c r="R39" s="3"/>
       <c r="S39" s="3"/>
-    </row>
-    <row r="40" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T39" s="3"/>
+      <c r="U39" s="3"/>
+    </row>
+    <row r="40" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -2225,44 +2396,46 @@
       <c r="Q40" s="3"/>
       <c r="R40" s="3"/>
       <c r="S40" s="3"/>
-    </row>
-    <row r="41" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T40" s="3"/>
+      <c r="U40" s="3"/>
+    </row>
+    <row r="41" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>17200</v>
+      </c>
+      <c r="E41" s="3">
+        <v>17200</v>
+      </c>
+      <c r="F41" s="3">
         <v>9700</v>
       </c>
-      <c r="E41" s="3">
+      <c r="G41" s="3">
         <v>9700</v>
       </c>
-      <c r="F41" s="3">
+      <c r="H41" s="3">
         <v>3100</v>
       </c>
-      <c r="G41" s="3">
+      <c r="I41" s="3">
         <v>4900</v>
       </c>
-      <c r="H41" s="3">
+      <c r="J41" s="3">
         <v>8200</v>
       </c>
-      <c r="I41" s="3">
+      <c r="K41" s="3">
         <v>5600</v>
       </c>
-      <c r="J41" s="3">
+      <c r="L41" s="3">
         <v>8300</v>
       </c>
-      <c r="K41" s="3">
+      <c r="M41" s="3">
         <v>12900</v>
       </c>
-      <c r="L41" s="3">
+      <c r="N41" s="3">
         <v>2200</v>
       </c>
-      <c r="M41" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="N41" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="O41" s="3" t="s">
         <v>3</v>
       </c>
@@ -2278,8 +2451,14 @@
       <c r="S41" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="42" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T41" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="U41" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="42" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
@@ -2331,31 +2510,37 @@
       <c r="S42" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="43" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T42" s="3">
+        <v>0</v>
+      </c>
+      <c r="U42" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>500</v>
+      </c>
+      <c r="E43" s="3">
+        <v>500</v>
+      </c>
+      <c r="F43" s="3">
         <v>100</v>
       </c>
-      <c r="E43" s="3">
+      <c r="G43" s="3">
         <v>100</v>
       </c>
-      <c r="F43" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="G43" s="3">
-        <v>0</v>
-      </c>
       <c r="H43" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="I43" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="J43" s="3">
-        <v>100</v>
+      <c r="I43" s="3">
+        <v>0</v>
+      </c>
+      <c r="J43" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="K43" s="3" t="s">
         <v>3</v>
@@ -2366,8 +2551,8 @@
       <c r="M43" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="N43" s="3" t="s">
-        <v>3</v>
+      <c r="N43" s="3">
+        <v>100</v>
       </c>
       <c r="O43" s="3" t="s">
         <v>3</v>
@@ -2384,16 +2569,22 @@
       <c r="S43" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="44" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T43" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="U43" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="44" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
       <c r="D44" s="3">
-        <v>1000</v>
+        <v>1300</v>
       </c>
       <c r="E44" s="3">
-        <v>1000</v>
+        <v>1300</v>
       </c>
       <c r="F44" s="3">
         <v>1000</v>
@@ -2402,28 +2593,28 @@
         <v>1000</v>
       </c>
       <c r="H44" s="3">
+        <v>1000</v>
+      </c>
+      <c r="I44" s="3">
+        <v>1000</v>
+      </c>
+      <c r="J44" s="3">
         <v>500</v>
       </c>
-      <c r="I44" s="3">
+      <c r="K44" s="3">
         <v>100</v>
       </c>
-      <c r="J44" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="K44" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="L44" s="3" t="s">
         <v>3</v>
       </c>
       <c r="M44" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="N44" s="3">
-        <v>0</v>
-      </c>
-      <c r="O44" s="3">
-        <v>0</v>
+      <c r="N44" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="O44" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="P44" s="3">
         <v>0</v>
@@ -2437,44 +2628,50 @@
       <c r="S44" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="45" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T44" s="3">
+        <v>0</v>
+      </c>
+      <c r="U44" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="45" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
+        <v>200</v>
+      </c>
+      <c r="E45" s="3">
+        <v>200</v>
+      </c>
+      <c r="F45" s="3">
         <v>400</v>
       </c>
-      <c r="E45" s="3">
+      <c r="G45" s="3">
         <v>400</v>
       </c>
-      <c r="F45" s="3">
+      <c r="H45" s="3">
         <v>200</v>
       </c>
-      <c r="G45" s="3">
+      <c r="I45" s="3">
         <v>300</v>
       </c>
-      <c r="H45" s="3">
+      <c r="J45" s="3">
         <v>400</v>
       </c>
-      <c r="I45" s="3">
+      <c r="K45" s="3">
         <v>400</v>
       </c>
-      <c r="J45" s="3">
+      <c r="L45" s="3">
         <v>100</v>
       </c>
-      <c r="K45" s="3">
+      <c r="M45" s="3">
         <v>1000</v>
       </c>
-      <c r="L45" s="3">
+      <c r="N45" s="3">
         <v>1000</v>
       </c>
-      <c r="M45" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="N45" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="O45" s="3" t="s">
         <v>3</v>
       </c>
@@ -2490,44 +2687,50 @@
       <c r="S45" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="46" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T45" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="U45" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="46" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>19700</v>
+      </c>
+      <c r="E46" s="3">
+        <v>19700</v>
+      </c>
+      <c r="F46" s="3">
         <v>11400</v>
       </c>
-      <c r="E46" s="3">
+      <c r="G46" s="3">
         <v>11400</v>
       </c>
-      <c r="F46" s="3">
+      <c r="H46" s="3">
         <v>4600</v>
       </c>
-      <c r="G46" s="3">
+      <c r="I46" s="3">
         <v>6400</v>
       </c>
-      <c r="H46" s="3">
+      <c r="J46" s="3">
         <v>9300</v>
       </c>
-      <c r="I46" s="3">
+      <c r="K46" s="3">
         <v>6300</v>
       </c>
-      <c r="J46" s="3">
+      <c r="L46" s="3">
         <v>8800</v>
       </c>
-      <c r="K46" s="3">
+      <c r="M46" s="3">
         <v>14000</v>
       </c>
-      <c r="L46" s="3">
+      <c r="N46" s="3">
         <v>3300</v>
       </c>
-      <c r="M46" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="N46" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="O46" s="3" t="s">
         <v>3</v>
       </c>
@@ -2543,8 +2746,14 @@
       <c r="S46" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="47" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T46" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="U46" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="47" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
@@ -2569,11 +2778,11 @@
       <c r="J47" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="K47" s="3">
-        <v>0</v>
-      </c>
-      <c r="L47" s="3">
-        <v>0</v>
+      <c r="K47" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="L47" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="M47" s="3">
         <v>0</v>
@@ -2596,44 +2805,50 @@
       <c r="S47" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="48" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T47" s="3">
+        <v>0</v>
+      </c>
+      <c r="U47" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="48" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>900</v>
+      </c>
+      <c r="E48" s="3">
+        <v>900</v>
+      </c>
+      <c r="F48" s="3">
         <v>1100</v>
       </c>
-      <c r="E48" s="3">
+      <c r="G48" s="3">
         <v>1100</v>
       </c>
-      <c r="F48" s="3">
+      <c r="H48" s="3">
         <v>1300</v>
       </c>
-      <c r="G48" s="3">
+      <c r="I48" s="3">
         <v>1400</v>
       </c>
-      <c r="H48" s="3">
+      <c r="J48" s="3">
         <v>1500</v>
       </c>
-      <c r="I48" s="3">
+      <c r="K48" s="3">
         <v>1600</v>
       </c>
-      <c r="J48" s="3">
+      <c r="L48" s="3">
         <v>1600</v>
       </c>
-      <c r="K48" s="3">
+      <c r="M48" s="3">
         <v>1800</v>
       </c>
-      <c r="L48" s="3">
+      <c r="N48" s="3">
         <v>1900</v>
       </c>
-      <c r="M48" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="N48" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="O48" s="3" t="s">
         <v>3</v>
       </c>
@@ -2649,8 +2864,14 @@
       <c r="S48" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="49" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T48" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="U48" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="49" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
@@ -2702,8 +2923,14 @@
       <c r="S49" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="50" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T49" s="3">
+        <v>0</v>
+      </c>
+      <c r="U49" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="50" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -2755,8 +2982,14 @@
       <c r="S50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T50" s="3">
+        <v>0</v>
+      </c>
+      <c r="U50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -2808,8 +3041,14 @@
       <c r="S51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T51" s="3">
+        <v>0</v>
+      </c>
+      <c r="U51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
@@ -2834,11 +3073,11 @@
       <c r="J52" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="K52" s="3">
-        <v>0</v>
-      </c>
-      <c r="L52" s="3">
-        <v>0</v>
+      <c r="K52" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="L52" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="M52" s="3">
         <v>0</v>
@@ -2861,8 +3100,14 @@
       <c r="S52" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="53" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T52" s="3">
+        <v>0</v>
+      </c>
+      <c r="U52" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="53" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -2914,44 +3159,50 @@
       <c r="S53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T53" s="3">
+        <v>0</v>
+      </c>
+      <c r="U53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>20600</v>
+      </c>
+      <c r="E54" s="3">
+        <v>20600</v>
+      </c>
+      <c r="F54" s="3">
         <v>12500</v>
       </c>
-      <c r="E54" s="3">
+      <c r="G54" s="3">
         <v>12500</v>
       </c>
-      <c r="F54" s="3">
+      <c r="H54" s="3">
         <v>5900</v>
-      </c>
-      <c r="G54" s="3">
-        <v>7900</v>
-      </c>
-      <c r="H54" s="3">
-        <v>10800</v>
       </c>
       <c r="I54" s="3">
         <v>7900</v>
       </c>
       <c r="J54" s="3">
+        <v>10800</v>
+      </c>
+      <c r="K54" s="3">
+        <v>7900</v>
+      </c>
+      <c r="L54" s="3">
         <v>10400</v>
       </c>
-      <c r="K54" s="3">
+      <c r="M54" s="3">
         <v>15700</v>
       </c>
-      <c r="L54" s="3">
+      <c r="N54" s="3">
         <v>5200</v>
       </c>
-      <c r="M54" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="N54" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="O54" s="3" t="s">
         <v>3</v>
       </c>
@@ -2967,8 +3218,14 @@
       <c r="S54" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="55" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T54" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="U54" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="55" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -2988,8 +3245,10 @@
       <c r="Q55" s="3"/>
       <c r="R55" s="3"/>
       <c r="S55" s="3"/>
-    </row>
-    <row r="56" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T55" s="3"/>
+      <c r="U55" s="3"/>
+    </row>
+    <row r="56" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -3009,8 +3268,10 @@
       <c r="Q56" s="3"/>
       <c r="R56" s="3"/>
       <c r="S56" s="3"/>
-    </row>
-    <row r="57" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T56" s="3"/>
+      <c r="U56" s="3"/>
+    </row>
+    <row r="57" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
@@ -3021,31 +3282,31 @@
         <v>100</v>
       </c>
       <c r="F57" s="3">
-        <v>200</v>
+        <v>100</v>
       </c>
       <c r="G57" s="3">
-        <v>300</v>
+        <v>100</v>
       </c>
       <c r="H57" s="3">
         <v>200</v>
       </c>
       <c r="I57" s="3">
+        <v>300</v>
+      </c>
+      <c r="J57" s="3">
         <v>200</v>
       </c>
-      <c r="J57" s="3">
-        <v>100</v>
-      </c>
       <c r="K57" s="3">
-        <v>100</v>
+        <v>200</v>
       </c>
       <c r="L57" s="3">
         <v>100</v>
       </c>
-      <c r="M57" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="N57" s="3" t="s">
-        <v>3</v>
+      <c r="M57" s="3">
+        <v>100</v>
+      </c>
+      <c r="N57" s="3">
+        <v>100</v>
       </c>
       <c r="O57" s="3" t="s">
         <v>3</v>
@@ -3062,8 +3323,14 @@
       <c r="S57" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="58" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T57" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="U57" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="58" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
@@ -3088,18 +3355,18 @@
       <c r="J58" s="3">
         <v>300</v>
       </c>
-      <c r="K58" s="3" t="s">
-        <v>3</v>
+      <c r="K58" s="3">
+        <v>300</v>
       </c>
       <c r="L58" s="3">
+        <v>300</v>
+      </c>
+      <c r="M58" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="N58" s="3">
         <v>1000</v>
       </c>
-      <c r="M58" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="N58" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="O58" s="3" t="s">
         <v>3</v>
       </c>
@@ -3115,44 +3382,50 @@
       <c r="S58" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="59" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T58" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="U58" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="59" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>1000</v>
+      </c>
+      <c r="E59" s="3">
+        <v>1000</v>
+      </c>
+      <c r="F59" s="3">
         <v>1800</v>
       </c>
-      <c r="E59" s="3">
+      <c r="G59" s="3">
         <v>1800</v>
       </c>
-      <c r="F59" s="3">
+      <c r="H59" s="3">
         <v>1000</v>
       </c>
-      <c r="G59" s="3">
-        <v>0</v>
-      </c>
-      <c r="H59" s="3">
+      <c r="I59" s="3">
+        <v>0</v>
+      </c>
+      <c r="J59" s="3">
         <v>1700</v>
       </c>
-      <c r="I59" s="3">
+      <c r="K59" s="3">
         <v>1200</v>
       </c>
-      <c r="J59" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="M59" s="3">
         <v>1400</v>
       </c>
-      <c r="L59" s="3">
+      <c r="N59" s="3">
         <v>1600</v>
       </c>
-      <c r="M59" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="N59" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="O59" s="3" t="s">
         <v>3</v>
       </c>
@@ -3168,44 +3441,50 @@
       <c r="S59" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="60" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T59" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="U59" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="60" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>2700</v>
+      </c>
+      <c r="E60" s="3">
+        <v>2700</v>
+      </c>
+      <c r="F60" s="3">
         <v>2200</v>
       </c>
-      <c r="E60" s="3">
+      <c r="G60" s="3">
         <v>2200</v>
       </c>
-      <c r="F60" s="3">
+      <c r="H60" s="3">
         <v>2600</v>
       </c>
-      <c r="G60" s="3">
+      <c r="I60" s="3">
         <v>2000</v>
       </c>
-      <c r="H60" s="3">
+      <c r="J60" s="3">
         <v>2200</v>
       </c>
-      <c r="I60" s="3">
+      <c r="K60" s="3">
         <v>1800</v>
       </c>
-      <c r="J60" s="3">
+      <c r="L60" s="3">
         <v>1400</v>
       </c>
-      <c r="K60" s="3">
+      <c r="M60" s="3">
         <v>1500</v>
       </c>
-      <c r="L60" s="3">
+      <c r="N60" s="3">
         <v>2700</v>
       </c>
-      <c r="M60" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="N60" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="O60" s="3" t="s">
         <v>3</v>
       </c>
@@ -3221,38 +3500,44 @@
       <c r="S60" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="61" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T60" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="U60" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="61" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>200</v>
+      </c>
+      <c r="E61" s="3">
+        <v>200</v>
+      </c>
+      <c r="F61" s="3">
         <v>400</v>
       </c>
-      <c r="E61" s="3">
+      <c r="G61" s="3">
         <v>400</v>
       </c>
-      <c r="F61" s="3">
+      <c r="H61" s="3">
         <v>500</v>
       </c>
-      <c r="G61" s="3">
+      <c r="I61" s="3">
         <v>500</v>
       </c>
-      <c r="H61" s="3">
+      <c r="J61" s="3">
         <v>600</v>
       </c>
-      <c r="I61" s="3">
+      <c r="K61" s="3">
         <v>700</v>
       </c>
-      <c r="J61" s="3">
+      <c r="L61" s="3">
         <v>800</v>
       </c>
-      <c r="K61" s="3">
-        <v>0</v>
-      </c>
-      <c r="L61" s="3">
-        <v>0</v>
-      </c>
       <c r="M61" s="3">
         <v>0</v>
       </c>
@@ -3274,8 +3559,14 @@
       <c r="S61" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="62" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T61" s="3">
+        <v>0</v>
+      </c>
+      <c r="U61" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
@@ -3300,18 +3591,18 @@
       <c r="J62" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="K62" s="3">
+      <c r="K62" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="L62" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="M62" s="3">
         <v>900</v>
       </c>
-      <c r="L62" s="3">
+      <c r="N62" s="3">
         <v>1100</v>
       </c>
-      <c r="M62" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="N62" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="O62" s="3" t="s">
         <v>3</v>
       </c>
@@ -3327,8 +3618,14 @@
       <c r="S62" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="63" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T62" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="U62" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="63" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -3380,8 +3677,14 @@
       <c r="S63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T63" s="3">
+        <v>0</v>
+      </c>
+      <c r="U63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -3433,8 +3736,14 @@
       <c r="S64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T64" s="3">
+        <v>0</v>
+      </c>
+      <c r="U64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -3486,44 +3795,50 @@
       <c r="S65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T65" s="3">
+        <v>0</v>
+      </c>
+      <c r="U65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>2900</v>
+      </c>
+      <c r="E66" s="3">
+        <v>2900</v>
+      </c>
+      <c r="F66" s="3">
         <v>2600</v>
-      </c>
-      <c r="E66" s="3">
-        <v>2600</v>
-      </c>
-      <c r="F66" s="3">
-        <v>3100</v>
       </c>
       <c r="G66" s="3">
         <v>2600</v>
       </c>
       <c r="H66" s="3">
+        <v>3100</v>
+      </c>
+      <c r="I66" s="3">
+        <v>2600</v>
+      </c>
+      <c r="J66" s="3">
         <v>2800</v>
-      </c>
-      <c r="I66" s="3">
-        <v>2500</v>
-      </c>
-      <c r="J66" s="3">
-        <v>2200</v>
       </c>
       <c r="K66" s="3">
         <v>2500</v>
       </c>
       <c r="L66" s="3">
+        <v>2200</v>
+      </c>
+      <c r="M66" s="3">
+        <v>2500</v>
+      </c>
+      <c r="N66" s="3">
         <v>3800</v>
       </c>
-      <c r="M66" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="N66" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="O66" s="3" t="s">
         <v>3</v>
       </c>
@@ -3539,8 +3854,14 @@
       <c r="S66" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="67" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T66" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="U66" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="67" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -3560,8 +3881,10 @@
       <c r="Q67" s="3"/>
       <c r="R67" s="3"/>
       <c r="S67" s="3"/>
-    </row>
-    <row r="68" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T67" s="3"/>
+      <c r="U67" s="3"/>
+    </row>
+    <row r="68" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -3613,8 +3936,14 @@
       <c r="S68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T68" s="3">
+        <v>0</v>
+      </c>
+      <c r="U68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -3666,8 +3995,14 @@
       <c r="S69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T69" s="3">
+        <v>0</v>
+      </c>
+      <c r="U69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -3696,14 +4031,14 @@
         <v>0</v>
       </c>
       <c r="L70" s="3">
+        <v>0</v>
+      </c>
+      <c r="M70" s="3">
+        <v>0</v>
+      </c>
+      <c r="N70" s="3">
         <v>12000</v>
       </c>
-      <c r="M70" s="3">
-        <v>0</v>
-      </c>
-      <c r="N70" s="3">
-        <v>0</v>
-      </c>
       <c r="O70" s="3">
         <v>0</v>
       </c>
@@ -3719,8 +4054,14 @@
       <c r="S70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T70" s="3">
+        <v>0</v>
+      </c>
+      <c r="U70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -3772,44 +4113,50 @@
       <c r="S71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T71" s="3">
+        <v>0</v>
+      </c>
+      <c r="U71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>-96700</v>
+      </c>
+      <c r="E72" s="3">
+        <v>-96700</v>
+      </c>
+      <c r="F72" s="3">
         <v>-90300</v>
       </c>
-      <c r="E72" s="3">
+      <c r="G72" s="3">
         <v>-90300</v>
       </c>
-      <c r="F72" s="3">
+      <c r="H72" s="3">
         <v>-66000</v>
       </c>
-      <c r="G72" s="3">
+      <c r="I72" s="3">
         <v>-63400</v>
       </c>
-      <c r="H72" s="3">
+      <c r="J72" s="3">
         <v>-60600</v>
       </c>
-      <c r="I72" s="3">
+      <c r="K72" s="3">
         <v>-57700</v>
       </c>
-      <c r="J72" s="3">
+      <c r="L72" s="3">
         <v>-54800</v>
       </c>
-      <c r="K72" s="3">
+      <c r="M72" s="3">
         <v>-49600</v>
       </c>
-      <c r="L72" s="3">
+      <c r="N72" s="3">
         <v>-46700</v>
       </c>
-      <c r="M72" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="N72" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="O72" s="3" t="s">
         <v>3</v>
       </c>
@@ -3825,8 +4172,14 @@
       <c r="S72" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="73" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T72" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="U72" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="73" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -3878,8 +4231,14 @@
       <c r="S73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T73" s="3">
+        <v>0</v>
+      </c>
+      <c r="U73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -3931,8 +4290,14 @@
       <c r="S74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T74" s="3">
+        <v>0</v>
+      </c>
+      <c r="U74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -3984,44 +4349,50 @@
       <c r="S75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T75" s="3">
+        <v>0</v>
+      </c>
+      <c r="U75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>17700</v>
+      </c>
+      <c r="E76" s="3">
+        <v>17700</v>
+      </c>
+      <c r="F76" s="3">
         <v>9900</v>
       </c>
-      <c r="E76" s="3">
+      <c r="G76" s="3">
         <v>9900</v>
       </c>
-      <c r="F76" s="3">
+      <c r="H76" s="3">
         <v>2800</v>
       </c>
-      <c r="G76" s="3">
+      <c r="I76" s="3">
         <v>5300</v>
       </c>
-      <c r="H76" s="3">
+      <c r="J76" s="3">
         <v>8000</v>
       </c>
-      <c r="I76" s="3">
+      <c r="K76" s="3">
         <v>5400</v>
       </c>
-      <c r="J76" s="3">
+      <c r="L76" s="3">
         <v>8300</v>
       </c>
-      <c r="K76" s="3">
+      <c r="M76" s="3">
         <v>13300</v>
       </c>
-      <c r="L76" s="3">
+      <c r="N76" s="3">
         <v>-10500</v>
       </c>
-      <c r="M76" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="N76" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="O76" s="3" t="s">
         <v>3</v>
       </c>
@@ -4037,8 +4408,14 @@
       <c r="S76" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="77" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T76" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="U76" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="77" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -4090,119 +4467,137 @@
       <c r="S77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T77" s="3">
+        <v>0</v>
+      </c>
+      <c r="U77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:21" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:19" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45657</v>
+      </c>
+      <c r="E80" s="2">
+        <v>45565</v>
+      </c>
+      <c r="F80" s="2">
         <v>45473</v>
       </c>
-      <c r="E80" s="2">
+      <c r="G80" s="2">
         <v>45382</v>
       </c>
-      <c r="F80" s="2">
+      <c r="H80" s="2">
         <v>45291</v>
       </c>
-      <c r="G80" s="2">
+      <c r="I80" s="2">
         <v>45199</v>
       </c>
-      <c r="H80" s="2">
+      <c r="J80" s="2">
         <v>45107</v>
       </c>
-      <c r="I80" s="2">
+      <c r="K80" s="2">
         <v>45016</v>
       </c>
-      <c r="J80" s="2">
+      <c r="L80" s="2">
         <v>44926</v>
       </c>
-      <c r="K80" s="2">
+      <c r="M80" s="2">
         <v>44742</v>
       </c>
-      <c r="L80" s="2">
+      <c r="N80" s="2">
         <v>44651</v>
       </c>
-      <c r="M80" s="2">
+      <c r="O80" s="2">
         <v>44561</v>
       </c>
-      <c r="N80" s="2">
+      <c r="P80" s="2">
         <v>44377</v>
       </c>
-      <c r="O80" s="2">
+      <c r="Q80" s="2">
         <v>44196</v>
       </c>
-      <c r="P80" s="2">
+      <c r="R80" s="2">
         <v>44012</v>
       </c>
-      <c r="Q80" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="R80" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="S80" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="81" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T80" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="U80" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="81" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>-3200</v>
+      </c>
+      <c r="E81" s="3">
+        <v>-3200</v>
+      </c>
+      <c r="F81" s="3">
         <v>-12200</v>
       </c>
-      <c r="E81" s="3">
+      <c r="G81" s="3">
         <v>-12200</v>
       </c>
-      <c r="F81" s="3">
+      <c r="H81" s="3">
         <v>-2500</v>
       </c>
-      <c r="G81" s="3">
+      <c r="I81" s="3">
         <v>-2800</v>
       </c>
-      <c r="H81" s="3">
+      <c r="J81" s="3">
         <v>-3000</v>
-      </c>
-      <c r="I81" s="3">
-        <v>-2900</v>
-      </c>
-      <c r="J81" s="3">
-        <v>-2500</v>
       </c>
       <c r="K81" s="3">
         <v>-2900</v>
       </c>
       <c r="L81" s="3">
+        <v>-2500</v>
+      </c>
+      <c r="M81" s="3">
+        <v>-2900</v>
+      </c>
+      <c r="N81" s="3">
         <v>-2300</v>
       </c>
-      <c r="M81" s="3">
+      <c r="O81" s="3">
         <v>-10200</v>
-      </c>
-      <c r="N81" s="3">
-        <v>-5100</v>
-      </c>
-      <c r="O81" s="3">
-        <v>-10700</v>
       </c>
       <c r="P81" s="3">
         <v>-5100</v>
       </c>
-      <c r="Q81" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="R81" s="3" t="s">
-        <v>3</v>
+      <c r="Q81" s="3">
+        <v>-10700</v>
+      </c>
+      <c r="R81" s="3">
+        <v>-5100</v>
       </c>
       <c r="S81" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="82" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T81" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="U81" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="82" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -4222,8 +4617,10 @@
       <c r="Q82" s="3"/>
       <c r="R82" s="3"/>
       <c r="S82" s="3"/>
-    </row>
-    <row r="83" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T82" s="3"/>
+      <c r="U82" s="3"/>
+    </row>
+    <row r="83" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
@@ -4255,28 +4652,34 @@
         <v>0</v>
       </c>
       <c r="M83" s="3">
+        <v>0</v>
+      </c>
+      <c r="N83" s="3">
+        <v>0</v>
+      </c>
+      <c r="O83" s="3">
         <v>100</v>
-      </c>
-      <c r="N83" s="3">
-        <v>100</v>
-      </c>
-      <c r="O83" s="3">
-        <v>200</v>
       </c>
       <c r="P83" s="3">
         <v>100</v>
       </c>
-      <c r="Q83" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="R83" s="3" t="s">
-        <v>3</v>
+      <c r="Q83" s="3">
+        <v>200</v>
+      </c>
+      <c r="R83" s="3">
+        <v>100</v>
       </c>
       <c r="S83" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="84" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T83" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="U83" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="84" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -4328,8 +4731,14 @@
       <c r="S84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T84" s="3">
+        <v>0</v>
+      </c>
+      <c r="U84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -4381,8 +4790,14 @@
       <c r="S85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T85" s="3">
+        <v>0</v>
+      </c>
+      <c r="U85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -4434,8 +4849,14 @@
       <c r="S86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T86" s="3">
+        <v>0</v>
+      </c>
+      <c r="U86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -4487,8 +4908,14 @@
       <c r="S87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T87" s="3">
+        <v>0</v>
+      </c>
+      <c r="U87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -4540,61 +4967,73 @@
       <c r="S88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T88" s="3">
+        <v>0</v>
+      </c>
+      <c r="U88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>-2500</v>
+      </c>
+      <c r="E89" s="3">
+        <v>-2500</v>
+      </c>
+      <c r="F89" s="3">
         <v>-2300</v>
       </c>
-      <c r="E89" s="3">
+      <c r="G89" s="3">
         <v>-2300</v>
       </c>
-      <c r="F89" s="3">
+      <c r="H89" s="3">
         <v>-1900</v>
       </c>
-      <c r="G89" s="3">
+      <c r="I89" s="3">
         <v>-3200</v>
       </c>
-      <c r="H89" s="3">
+      <c r="J89" s="3">
         <v>-2900</v>
       </c>
-      <c r="I89" s="3">
+      <c r="K89" s="3">
         <v>-2500</v>
       </c>
-      <c r="J89" s="3">
+      <c r="L89" s="3">
         <v>-2100</v>
       </c>
-      <c r="K89" s="3">
+      <c r="M89" s="3">
         <v>-2900</v>
       </c>
-      <c r="L89" s="3">
+      <c r="N89" s="3">
         <v>-2500</v>
       </c>
-      <c r="M89" s="3">
+      <c r="O89" s="3">
         <v>-9900</v>
       </c>
-      <c r="N89" s="3">
+      <c r="P89" s="3">
         <v>-5000</v>
       </c>
-      <c r="O89" s="3">
+      <c r="Q89" s="3">
         <v>-7200</v>
       </c>
-      <c r="P89" s="3">
+      <c r="R89" s="3">
         <v>-4100</v>
       </c>
-      <c r="Q89" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="R89" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="S89" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="90" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T89" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="U89" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="90" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -4614,8 +5053,10 @@
       <c r="Q90" s="3"/>
       <c r="R90" s="3"/>
       <c r="S90" s="3"/>
-    </row>
-    <row r="91" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T90" s="3"/>
+      <c r="U90" s="3"/>
+    </row>
+    <row r="91" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
@@ -4632,43 +5073,49 @@
         <v>0</v>
       </c>
       <c r="H91" s="3">
+        <v>0</v>
+      </c>
+      <c r="I91" s="3">
+        <v>0</v>
+      </c>
+      <c r="J91" s="3">
         <v>-100</v>
       </c>
-      <c r="I91" s="3">
+      <c r="K91" s="3">
         <v>-100</v>
       </c>
-      <c r="J91" s="3">
-        <v>0</v>
-      </c>
-      <c r="K91" s="3">
-        <v>0</v>
-      </c>
       <c r="L91" s="3">
         <v>0</v>
       </c>
       <c r="M91" s="3">
+        <v>0</v>
+      </c>
+      <c r="N91" s="3">
+        <v>0</v>
+      </c>
+      <c r="O91" s="3">
         <v>-200</v>
       </c>
-      <c r="N91" s="3">
-        <v>0</v>
-      </c>
-      <c r="O91" s="3">
-        <v>0</v>
-      </c>
       <c r="P91" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q91" s="3">
+        <v>0</v>
+      </c>
+      <c r="R91" s="3">
         <v>-100</v>
       </c>
-      <c r="Q91" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="R91" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="S91" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="92" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T91" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="U91" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="92" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -4720,8 +5167,14 @@
       <c r="S92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T92" s="3">
+        <v>0</v>
+      </c>
+      <c r="U92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -4773,8 +5226,14 @@
       <c r="S93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T93" s="3">
+        <v>0</v>
+      </c>
+      <c r="U93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
@@ -4791,43 +5250,49 @@
         <v>0</v>
       </c>
       <c r="H94" s="3">
+        <v>0</v>
+      </c>
+      <c r="I94" s="3">
+        <v>0</v>
+      </c>
+      <c r="J94" s="3">
         <v>-100</v>
       </c>
-      <c r="I94" s="3">
+      <c r="K94" s="3">
         <v>-100</v>
       </c>
-      <c r="J94" s="3">
-        <v>0</v>
-      </c>
-      <c r="K94" s="3">
-        <v>0</v>
-      </c>
       <c r="L94" s="3">
         <v>0</v>
       </c>
       <c r="M94" s="3">
+        <v>0</v>
+      </c>
+      <c r="N94" s="3">
+        <v>0</v>
+      </c>
+      <c r="O94" s="3">
         <v>-300</v>
       </c>
-      <c r="N94" s="3">
-        <v>0</v>
-      </c>
-      <c r="O94" s="3">
+      <c r="P94" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q94" s="3">
         <v>-100</v>
       </c>
-      <c r="P94" s="3">
+      <c r="R94" s="3">
         <v>-100</v>
       </c>
-      <c r="Q94" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="R94" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="S94" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="95" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T94" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="U94" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="95" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -4847,8 +5312,10 @@
       <c r="Q95" s="3"/>
       <c r="R95" s="3"/>
       <c r="S95" s="3"/>
-    </row>
-    <row r="96" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T95" s="3"/>
+      <c r="U95" s="3"/>
+    </row>
+    <row r="96" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -4873,11 +5340,11 @@
       <c r="J96" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="K96" s="3">
-        <v>0</v>
-      </c>
-      <c r="L96" s="3">
-        <v>0</v>
+      <c r="K96" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="L96" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="M96" s="3">
         <v>0</v>
@@ -4900,8 +5367,14 @@
       <c r="S96" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="97" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T96" s="3">
+        <v>0</v>
+      </c>
+      <c r="U96" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -4953,8 +5426,14 @@
       <c r="S97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T97" s="3">
+        <v>0</v>
+      </c>
+      <c r="U97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -5006,8 +5485,14 @@
       <c r="S98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T98" s="3">
+        <v>0</v>
+      </c>
+      <c r="U98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -5059,66 +5544,78 @@
       <c r="S99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T99" s="3">
+        <v>0</v>
+      </c>
+      <c r="U99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>6300</v>
+      </c>
+      <c r="E100" s="3">
+        <v>6300</v>
+      </c>
+      <c r="F100" s="3">
         <v>5600</v>
       </c>
-      <c r="E100" s="3">
+      <c r="G100" s="3">
         <v>5600</v>
       </c>
-      <c r="F100" s="3">
-        <v>0</v>
-      </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
+        <v>0</v>
+      </c>
+      <c r="I100" s="3">
         <v>-100</v>
       </c>
-      <c r="H100" s="3">
+      <c r="J100" s="3">
         <v>5500</v>
       </c>
-      <c r="I100" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="J100" s="3">
-        <v>0</v>
-      </c>
-      <c r="K100" s="3">
+      <c r="K100" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="L100" s="3">
+        <v>0</v>
+      </c>
+      <c r="M100" s="3">
         <v>13600</v>
       </c>
-      <c r="L100" s="3">
+      <c r="N100" s="3">
         <v>3000</v>
       </c>
-      <c r="M100" s="3">
+      <c r="O100" s="3">
         <v>5100</v>
       </c>
-      <c r="N100" s="3">
+      <c r="P100" s="3">
         <v>5100</v>
       </c>
-      <c r="O100" s="3">
+      <c r="Q100" s="3">
         <v>5000</v>
       </c>
-      <c r="P100" s="3">
-        <v>0</v>
-      </c>
-      <c r="Q100" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="R100" s="3" t="s">
-        <v>3</v>
+      <c r="R100" s="3">
+        <v>0</v>
       </c>
       <c r="S100" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="101" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T100" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="U100" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="101" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
-      <c r="D101" s="3" t="s">
-        <v>3</v>
+      <c r="D101" s="3">
+        <v>100</v>
       </c>
       <c r="E101" s="3" t="s">
         <v>3</v>
@@ -5138,11 +5635,11 @@
       <c r="J101" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="K101" s="3">
-        <v>0</v>
-      </c>
-      <c r="L101" s="3">
-        <v>0</v>
+      <c r="K101" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="L101" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="M101" s="3">
         <v>0</v>
@@ -5165,57 +5662,69 @@
       <c r="S101" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="102" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T101" s="3">
+        <v>0</v>
+      </c>
+      <c r="U101" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="102" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>3800</v>
+      </c>
+      <c r="E102" s="3">
+        <v>3800</v>
+      </c>
+      <c r="F102" s="3">
         <v>3300</v>
       </c>
-      <c r="E102" s="3">
+      <c r="G102" s="3">
         <v>3300</v>
       </c>
-      <c r="F102" s="3">
+      <c r="H102" s="3">
         <v>-1800</v>
       </c>
-      <c r="G102" s="3">
+      <c r="I102" s="3">
         <v>-3300</v>
       </c>
-      <c r="H102" s="3">
+      <c r="J102" s="3">
         <v>2500</v>
       </c>
-      <c r="I102" s="3">
+      <c r="K102" s="3">
         <v>-2600</v>
       </c>
-      <c r="J102" s="3">
+      <c r="L102" s="3">
         <v>-2200</v>
       </c>
-      <c r="K102" s="3">
+      <c r="M102" s="3">
         <v>10700</v>
       </c>
-      <c r="L102" s="3">
+      <c r="N102" s="3">
         <v>600</v>
       </c>
-      <c r="M102" s="3">
+      <c r="O102" s="3">
         <v>-5100</v>
       </c>
-      <c r="N102" s="3">
+      <c r="P102" s="3">
         <v>100</v>
       </c>
-      <c r="O102" s="3">
+      <c r="Q102" s="3">
         <v>-2400</v>
       </c>
-      <c r="P102" s="3">
+      <c r="R102" s="3">
         <v>-4200</v>
       </c>
-      <c r="Q102" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="R102" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="S102" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="T102" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="U102" s="3" t="s">
         <v>3</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/RVSN_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/RVSN_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="365" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="399" uniqueCount="92">
   <si>
     <t>RVSN</t>
   </si>
@@ -767,8 +767,8 @@
       <c r="H8" s="3">
         <v>0</v>
       </c>
-      <c r="I8" s="3">
-        <v>100</v>
+      <c r="I8" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="J8" s="3" t="s">
         <v>3</v>
@@ -826,8 +826,8 @@
       <c r="H9" s="3">
         <v>0</v>
       </c>
-      <c r="I9" s="3">
-        <v>100</v>
+      <c r="I9" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="J9" s="3" t="s">
         <v>3</v>
@@ -885,8 +885,8 @@
       <c r="H10" s="3">
         <v>0</v>
       </c>
-      <c r="I10" s="3">
-        <v>100</v>
+      <c r="I10" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="J10" s="3" t="s">
         <v>3</v>
@@ -967,8 +967,8 @@
       <c r="H12" s="3">
         <v>1600</v>
       </c>
-      <c r="I12" s="3">
-        <v>1900</v>
+      <c r="I12" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="J12" s="3">
         <v>1800</v>
@@ -1223,8 +1223,8 @@
       <c r="H17" s="3">
         <v>2600</v>
       </c>
-      <c r="I17" s="3">
-        <v>3000</v>
+      <c r="I17" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="J17" s="3">
         <v>3000</v>
@@ -1282,8 +1282,8 @@
       <c r="H18" s="3">
         <v>-2600</v>
       </c>
-      <c r="I18" s="3">
-        <v>-2800</v>
+      <c r="I18" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="J18" s="3">
         <v>-3000</v>
@@ -1424,7 +1424,7 @@
         <v>-2600</v>
       </c>
       <c r="I21" s="3">
-        <v>-2800</v>
+        <v>0</v>
       </c>
       <c r="J21" s="3">
         <v>-2900</v>
@@ -1541,8 +1541,8 @@
       <c r="H23" s="3">
         <v>-2500</v>
       </c>
-      <c r="I23" s="3">
-        <v>-2800</v>
+      <c r="I23" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="J23" s="3">
         <v>-3000</v>
@@ -1718,8 +1718,8 @@
       <c r="H26" s="3">
         <v>-2500</v>
       </c>
-      <c r="I26" s="3">
-        <v>-2800</v>
+      <c r="I26" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="J26" s="3">
         <v>-3000</v>
@@ -1777,8 +1777,8 @@
       <c r="H27" s="3">
         <v>-2500</v>
       </c>
-      <c r="I27" s="3">
-        <v>-2800</v>
+      <c r="I27" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="J27" s="3">
         <v>-3000</v>
@@ -2131,8 +2131,8 @@
       <c r="H33" s="3">
         <v>-2500</v>
       </c>
-      <c r="I33" s="3">
-        <v>-2800</v>
+      <c r="I33" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="J33" s="3">
         <v>-3000</v>
@@ -2249,8 +2249,8 @@
       <c r="H35" s="3">
         <v>-2500</v>
       </c>
-      <c r="I35" s="3">
-        <v>-2800</v>
+      <c r="I35" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="J35" s="3">
         <v>-3000</v>
@@ -2418,8 +2418,8 @@
       <c r="H41" s="3">
         <v>3100</v>
       </c>
-      <c r="I41" s="3">
-        <v>4900</v>
+      <c r="I41" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="J41" s="3">
         <v>8200</v>
@@ -2536,8 +2536,8 @@
       <c r="H43" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="I43" s="3">
-        <v>0</v>
+      <c r="I43" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="J43" s="3" t="s">
         <v>3</v>
@@ -2595,8 +2595,8 @@
       <c r="H44" s="3">
         <v>1000</v>
       </c>
-      <c r="I44" s="3">
-        <v>1000</v>
+      <c r="I44" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="J44" s="3">
         <v>500</v>
@@ -2654,8 +2654,8 @@
       <c r="H45" s="3">
         <v>200</v>
       </c>
-      <c r="I45" s="3">
-        <v>300</v>
+      <c r="I45" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="J45" s="3">
         <v>400</v>
@@ -2713,8 +2713,8 @@
       <c r="H46" s="3">
         <v>4600</v>
       </c>
-      <c r="I46" s="3">
-        <v>6400</v>
+      <c r="I46" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="J46" s="3">
         <v>9300</v>
@@ -2831,8 +2831,8 @@
       <c r="H48" s="3">
         <v>1300</v>
       </c>
-      <c r="I48" s="3">
-        <v>1400</v>
+      <c r="I48" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="J48" s="3">
         <v>1500</v>
@@ -2890,8 +2890,8 @@
       <c r="H49" s="3">
         <v>0</v>
       </c>
-      <c r="I49" s="3">
-        <v>0</v>
+      <c r="I49" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="J49" s="3">
         <v>0</v>
@@ -3185,8 +3185,8 @@
       <c r="H54" s="3">
         <v>5900</v>
       </c>
-      <c r="I54" s="3">
-        <v>7900</v>
+      <c r="I54" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="J54" s="3">
         <v>10800</v>
@@ -3290,8 +3290,8 @@
       <c r="H57" s="3">
         <v>200</v>
       </c>
-      <c r="I57" s="3">
-        <v>300</v>
+      <c r="I57" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="J57" s="3">
         <v>200</v>
@@ -3349,8 +3349,8 @@
       <c r="H58" s="3">
         <v>300</v>
       </c>
-      <c r="I58" s="3">
-        <v>300</v>
+      <c r="I58" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="J58" s="3">
         <v>300</v>
@@ -3408,8 +3408,8 @@
       <c r="H59" s="3">
         <v>1000</v>
       </c>
-      <c r="I59" s="3">
-        <v>0</v>
+      <c r="I59" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="J59" s="3">
         <v>1700</v>
@@ -3467,8 +3467,8 @@
       <c r="H60" s="3">
         <v>2600</v>
       </c>
-      <c r="I60" s="3">
-        <v>2000</v>
+      <c r="I60" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="J60" s="3">
         <v>2200</v>
@@ -3527,7 +3527,7 @@
         <v>500</v>
       </c>
       <c r="I61" s="3">
-        <v>500</v>
+        <v>0</v>
       </c>
       <c r="J61" s="3">
         <v>600</v>
@@ -3821,8 +3821,8 @@
       <c r="H66" s="3">
         <v>3100</v>
       </c>
-      <c r="I66" s="3">
-        <v>2600</v>
+      <c r="I66" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="J66" s="3">
         <v>2800</v>
@@ -4139,8 +4139,8 @@
       <c r="H72" s="3">
         <v>-66000</v>
       </c>
-      <c r="I72" s="3">
-        <v>-63400</v>
+      <c r="I72" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="J72" s="3">
         <v>-60600</v>
@@ -4375,8 +4375,8 @@
       <c r="H76" s="3">
         <v>2800</v>
       </c>
-      <c r="I76" s="3">
-        <v>5300</v>
+      <c r="I76" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="J76" s="3">
         <v>8000</v>
@@ -4557,8 +4557,8 @@
       <c r="H81" s="3">
         <v>-2500</v>
       </c>
-      <c r="I81" s="3">
-        <v>-2800</v>
+      <c r="I81" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="J81" s="3">
         <v>-3000</v>
@@ -4627,20 +4627,20 @@
       <c r="D83" s="3">
         <v>0</v>
       </c>
-      <c r="E83" s="3">
-        <v>0</v>
+      <c r="E83" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="F83" s="3">
         <v>0</v>
       </c>
-      <c r="G83" s="3">
-        <v>0</v>
+      <c r="G83" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="H83" s="3">
         <v>0</v>
       </c>
-      <c r="I83" s="3">
-        <v>0</v>
+      <c r="I83" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="J83" s="3">
         <v>0</v>
@@ -4993,8 +4993,8 @@
       <c r="H89" s="3">
         <v>-1900</v>
       </c>
-      <c r="I89" s="3">
-        <v>-3200</v>
+      <c r="I89" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="J89" s="3">
         <v>-2900</v>
@@ -5075,8 +5075,8 @@
       <c r="H91" s="3">
         <v>0</v>
       </c>
-      <c r="I91" s="3">
-        <v>0</v>
+      <c r="I91" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="J91" s="3">
         <v>-100</v>
@@ -5252,8 +5252,8 @@
       <c r="H94" s="3">
         <v>0</v>
       </c>
-      <c r="I94" s="3">
-        <v>0</v>
+      <c r="I94" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="J94" s="3">
         <v>-100</v>
@@ -5570,8 +5570,8 @@
       <c r="H100" s="3">
         <v>0</v>
       </c>
-      <c r="I100" s="3">
-        <v>-100</v>
+      <c r="I100" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="J100" s="3">
         <v>5500</v>
@@ -5689,7 +5689,7 @@
         <v>-1800</v>
       </c>
       <c r="I102" s="3">
-        <v>-3300</v>
+        <v>0</v>
       </c>
       <c r="J102" s="3">
         <v>2500</v>

--- a/AAII_Financials/Quarterly/RVSN_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/RVSN_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="411" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="423" uniqueCount="92">
   <si>
     <t>RVSN</t>
   </si>
@@ -656,186 +656,199 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:W102"/>
+  <dimension ref="A5:Y102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="7.5703125" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="7" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="11" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="4" max="5" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="9" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="13" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="19" max="19" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
     <col min="20" max="20" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="21" max="23" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="24" max="16384" width="9.140625" style="1"/>
+    <col min="21" max="21" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="23" max="25" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="26" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:23" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:23" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:25" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:23" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:25" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>46022</v>
+      </c>
+      <c r="E7" s="2">
+        <v>45930</v>
+      </c>
+      <c r="F7" s="2">
         <v>45838</v>
       </c>
-      <c r="E7" s="2">
+      <c r="G7" s="2">
         <v>45747</v>
       </c>
-      <c r="F7" s="2">
+      <c r="H7" s="2">
         <v>45657</v>
       </c>
-      <c r="G7" s="2">
+      <c r="I7" s="2">
         <v>45565</v>
       </c>
-      <c r="H7" s="2">
+      <c r="J7" s="2">
         <v>45473</v>
       </c>
-      <c r="I7" s="2">
+      <c r="K7" s="2">
         <v>45382</v>
       </c>
-      <c r="J7" s="2">
+      <c r="L7" s="2">
         <v>45291</v>
       </c>
-      <c r="K7" s="2">
+      <c r="M7" s="2">
         <v>45199</v>
       </c>
-      <c r="L7" s="2">
+      <c r="N7" s="2">
         <v>45107</v>
       </c>
-      <c r="M7" s="2">
+      <c r="O7" s="2">
         <v>45016</v>
       </c>
-      <c r="N7" s="2">
+      <c r="P7" s="2">
         <v>44926</v>
       </c>
-      <c r="O7" s="2">
+      <c r="Q7" s="2">
         <v>44742</v>
       </c>
-      <c r="P7" s="2">
+      <c r="R7" s="2">
         <v>44651</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="S7" s="2">
         <v>44561</v>
       </c>
-      <c r="R7" s="2">
+      <c r="T7" s="2">
         <v>44377</v>
       </c>
-      <c r="S7" s="2">
+      <c r="U7" s="2">
         <v>44196</v>
       </c>
-      <c r="T7" s="2">
+      <c r="V7" s="2">
         <v>44012</v>
       </c>
-      <c r="U7" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="V7" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="W7" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="8" spans="1:23" x14ac:dyDescent="0.2">
+      <c r="X7" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="Y7" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="8" spans="1:25" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D8" s="3">
+        <v>600</v>
+      </c>
+      <c r="E8" s="3">
+        <v>600</v>
+      </c>
+      <c r="F8" s="3">
         <v>100</v>
       </c>
-      <c r="E8" s="3">
+      <c r="G8" s="3">
         <v>100</v>
       </c>
-      <c r="F8" s="3">
+      <c r="H8" s="3">
         <v>300</v>
       </c>
-      <c r="G8" s="3">
+      <c r="I8" s="3">
         <v>300</v>
       </c>
-      <c r="H8" s="3">
+      <c r="J8" s="3">
         <v>400</v>
       </c>
-      <c r="I8" s="3">
+      <c r="K8" s="3">
         <v>400</v>
       </c>
-      <c r="J8" s="3">
-        <v>0</v>
-      </c>
-      <c r="K8" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="L8" s="3" t="s">
-        <v>3</v>
+      <c r="L8" s="3">
+        <v>0</v>
       </c>
       <c r="M8" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="N8" s="3">
-        <v>0</v>
-      </c>
-      <c r="O8" s="3">
-        <v>0</v>
+      <c r="N8" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="O8" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="P8" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q8" s="3">
+        <v>0</v>
+      </c>
+      <c r="R8" s="3">
         <v>200</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="S8" s="3">
         <v>900</v>
       </c>
-      <c r="R8" s="3">
+      <c r="T8" s="3">
         <v>400</v>
       </c>
-      <c r="S8" s="3">
-        <v>0</v>
-      </c>
-      <c r="T8" s="3">
-        <v>0</v>
-      </c>
-      <c r="U8" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="V8" s="3" t="s">
-        <v>3</v>
+      <c r="U8" s="3">
+        <v>0</v>
+      </c>
+      <c r="V8" s="3">
+        <v>0</v>
       </c>
       <c r="W8" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="9" spans="1:23" x14ac:dyDescent="0.2">
+      <c r="X8" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Y8" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="9" spans="1:25" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D9" s="3">
+        <v>400</v>
+      </c>
+      <c r="E9" s="3">
+        <v>400</v>
+      </c>
+      <c r="F9" s="3">
         <v>100</v>
       </c>
-      <c r="E9" s="3">
+      <c r="G9" s="3">
         <v>100</v>
-      </c>
-      <c r="F9" s="3">
-        <v>200</v>
-      </c>
-      <c r="G9" s="3">
-        <v>200</v>
       </c>
       <c r="H9" s="3">
         <v>200</v>
@@ -844,38 +857,38 @@
         <v>200</v>
       </c>
       <c r="J9" s="3">
-        <v>0</v>
-      </c>
-      <c r="K9" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="L9" s="3" t="s">
-        <v>3</v>
+        <v>200</v>
+      </c>
+      <c r="K9" s="3">
+        <v>200</v>
+      </c>
+      <c r="L9" s="3">
+        <v>0</v>
       </c>
       <c r="M9" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="N9" s="3">
-        <v>0</v>
+      <c r="N9" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="O9" s="3" t="s">
         <v>3</v>
       </c>
       <c r="P9" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q9" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R9" s="3">
         <v>400</v>
       </c>
-      <c r="Q9" s="3">
+      <c r="S9" s="3">
         <v>700</v>
       </c>
-      <c r="R9" s="3">
+      <c r="T9" s="3">
         <v>100</v>
       </c>
-      <c r="S9" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="T9" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="U9" s="3" t="s">
         <v>3</v>
       </c>
@@ -885,16 +898,22 @@
       <c r="W9" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="10" spans="1:23" x14ac:dyDescent="0.2">
+      <c r="X9" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Y9" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="10" spans="1:25" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D10" s="3">
-        <v>0</v>
+        <v>300</v>
       </c>
       <c r="E10" s="3">
-        <v>0</v>
+        <v>300</v>
       </c>
       <c r="F10" s="3">
         <v>0</v>
@@ -903,44 +922,44 @@
         <v>0</v>
       </c>
       <c r="H10" s="3">
+        <v>0</v>
+      </c>
+      <c r="I10" s="3">
+        <v>0</v>
+      </c>
+      <c r="J10" s="3">
         <v>200</v>
       </c>
-      <c r="I10" s="3">
+      <c r="K10" s="3">
         <v>200</v>
       </c>
-      <c r="J10" s="3">
-        <v>0</v>
-      </c>
-      <c r="K10" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="L10" s="3" t="s">
-        <v>3</v>
+      <c r="L10" s="3">
+        <v>0</v>
       </c>
       <c r="M10" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="N10" s="3">
-        <v>0</v>
+      <c r="N10" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="O10" s="3" t="s">
         <v>3</v>
       </c>
       <c r="P10" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q10" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R10" s="3">
         <v>-200</v>
       </c>
-      <c r="Q10" s="3">
+      <c r="S10" s="3">
         <v>200</v>
       </c>
-      <c r="R10" s="3">
+      <c r="T10" s="3">
         <v>300</v>
       </c>
-      <c r="S10" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="T10" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="U10" s="3" t="s">
         <v>3</v>
       </c>
@@ -950,8 +969,14 @@
       <c r="W10" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="11" spans="1:23" x14ac:dyDescent="0.2">
+      <c r="X10" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Y10" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="11" spans="1:25" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -975,73 +1000,81 @@
       <c r="U11" s="3"/>
       <c r="V11" s="3"/>
       <c r="W11" s="3"/>
-    </row>
-    <row r="12" spans="1:23" x14ac:dyDescent="0.2">
+      <c r="X11" s="3"/>
+      <c r="Y11" s="3"/>
+    </row>
+    <row r="12" spans="1:25" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
       <c r="D12" s="3">
+        <v>1800</v>
+      </c>
+      <c r="E12" s="3">
+        <v>1800</v>
+      </c>
+      <c r="F12" s="3">
         <v>1600</v>
       </c>
-      <c r="E12" s="3">
+      <c r="G12" s="3">
         <v>1600</v>
       </c>
-      <c r="F12" s="3">
+      <c r="H12" s="3">
         <v>1400</v>
       </c>
-      <c r="G12" s="3">
+      <c r="I12" s="3">
         <v>1400</v>
       </c>
-      <c r="H12" s="3">
+      <c r="J12" s="3">
         <v>1200</v>
       </c>
-      <c r="I12" s="3">
+      <c r="K12" s="3">
         <v>1200</v>
       </c>
-      <c r="J12" s="3">
+      <c r="L12" s="3">
         <v>1600</v>
       </c>
-      <c r="K12" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="L12" s="3">
+      <c r="M12" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="N12" s="3">
         <v>1800</v>
       </c>
-      <c r="M12" s="3">
+      <c r="O12" s="3">
         <v>1800</v>
       </c>
-      <c r="N12" s="3">
+      <c r="P12" s="3">
         <v>1500</v>
       </c>
-      <c r="O12" s="3">
+      <c r="Q12" s="3">
         <v>1700</v>
       </c>
-      <c r="P12" s="3">
+      <c r="R12" s="3">
         <v>1400</v>
-      </c>
-      <c r="Q12" s="3">
-        <v>7200</v>
-      </c>
-      <c r="R12" s="3">
-        <v>3800</v>
       </c>
       <c r="S12" s="3">
         <v>7200</v>
       </c>
       <c r="T12" s="3">
+        <v>3800</v>
+      </c>
+      <c r="U12" s="3">
+        <v>7200</v>
+      </c>
+      <c r="V12" s="3">
         <v>3600</v>
       </c>
-      <c r="U12" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="V12" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="W12" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="13" spans="1:23" x14ac:dyDescent="0.2">
+      <c r="X12" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Y12" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="13" spans="1:25" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1105,8 +1138,14 @@
       <c r="W13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:23" x14ac:dyDescent="0.2">
+      <c r="X13" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:25" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
@@ -1143,11 +1182,11 @@
       <c r="N14" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="O14" s="3">
-        <v>0</v>
-      </c>
-      <c r="P14" s="3">
-        <v>0</v>
+      <c r="O14" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="P14" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="Q14" s="3">
         <v>0</v>
@@ -1170,8 +1209,14 @@
       <c r="W14" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="15" spans="1:23" x14ac:dyDescent="0.2">
+      <c r="X14" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y14" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:25" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
@@ -1235,8 +1280,14 @@
       <c r="W15" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="16" spans="1:23" x14ac:dyDescent="0.2">
+      <c r="X15" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y15" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:25" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1257,43 +1308,45 @@
       <c r="U16" s="3"/>
       <c r="V16" s="3"/>
       <c r="W16" s="3"/>
-    </row>
-    <row r="17" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X16" s="3"/>
+      <c r="Y16" s="3"/>
+    </row>
+    <row r="17" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>3600</v>
+      </c>
+      <c r="E17" s="3">
+        <v>3600</v>
+      </c>
+      <c r="F17" s="3">
         <v>3000</v>
       </c>
-      <c r="E17" s="3">
+      <c r="G17" s="3">
         <v>3000</v>
       </c>
-      <c r="F17" s="3">
+      <c r="H17" s="3">
         <v>2800</v>
       </c>
-      <c r="G17" s="3">
+      <c r="I17" s="3">
         <v>2800</v>
       </c>
-      <c r="H17" s="3">
+      <c r="J17" s="3">
         <v>2500</v>
       </c>
-      <c r="I17" s="3">
+      <c r="K17" s="3">
         <v>2500</v>
       </c>
-      <c r="J17" s="3">
+      <c r="L17" s="3">
         <v>2600</v>
       </c>
-      <c r="K17" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="N17" s="3">
         <v>3000</v>
-      </c>
-      <c r="M17" s="3">
-        <v>3000</v>
-      </c>
-      <c r="N17" s="3">
-        <v>2600</v>
       </c>
       <c r="O17" s="3">
         <v>3000</v>
@@ -1302,93 +1355,105 @@
         <v>2600</v>
       </c>
       <c r="Q17" s="3">
+        <v>3000</v>
+      </c>
+      <c r="R17" s="3">
+        <v>2600</v>
+      </c>
+      <c r="S17" s="3">
         <v>11200</v>
       </c>
-      <c r="R17" s="3">
+      <c r="T17" s="3">
         <v>5700</v>
       </c>
-      <c r="S17" s="3">
+      <c r="U17" s="3">
         <v>10700</v>
       </c>
-      <c r="T17" s="3">
+      <c r="V17" s="3">
         <v>5100</v>
       </c>
-      <c r="U17" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="V17" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="W17" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="18" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X17" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Y17" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="18" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>-3000</v>
+      </c>
+      <c r="E18" s="3">
+        <v>-3000</v>
+      </c>
+      <c r="F18" s="3">
         <v>-2900</v>
       </c>
-      <c r="E18" s="3">
+      <c r="G18" s="3">
         <v>-2900</v>
       </c>
-      <c r="F18" s="3">
+      <c r="H18" s="3">
         <v>-2500</v>
       </c>
-      <c r="G18" s="3">
+      <c r="I18" s="3">
         <v>-2500</v>
       </c>
-      <c r="H18" s="3">
+      <c r="J18" s="3">
         <v>-2100</v>
       </c>
-      <c r="I18" s="3">
+      <c r="K18" s="3">
         <v>-2100</v>
       </c>
-      <c r="J18" s="3">
+      <c r="L18" s="3">
         <v>-2600</v>
       </c>
-      <c r="K18" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="N18" s="3">
         <v>-3000</v>
-      </c>
-      <c r="M18" s="3">
-        <v>-3000</v>
-      </c>
-      <c r="N18" s="3">
-        <v>-2600</v>
       </c>
       <c r="O18" s="3">
         <v>-3000</v>
       </c>
       <c r="P18" s="3">
+        <v>-2600</v>
+      </c>
+      <c r="Q18" s="3">
+        <v>-3000</v>
+      </c>
+      <c r="R18" s="3">
         <v>-2400</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="S18" s="3">
         <v>-10300</v>
       </c>
-      <c r="R18" s="3">
+      <c r="T18" s="3">
         <v>-5300</v>
       </c>
-      <c r="S18" s="3">
+      <c r="U18" s="3">
         <v>-10700</v>
       </c>
-      <c r="T18" s="3">
+      <c r="V18" s="3">
         <v>-5100</v>
       </c>
-      <c r="U18" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="V18" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="W18" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="19" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X18" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Y18" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="19" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1412,35 +1477,37 @@
       <c r="U19" s="3"/>
       <c r="V19" s="3"/>
       <c r="W19" s="3"/>
-    </row>
-    <row r="20" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X19" s="3"/>
+      <c r="Y19" s="3"/>
+    </row>
+    <row r="20" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3">
+        <v>-100</v>
+      </c>
+      <c r="E20" s="3">
+        <v>-100</v>
+      </c>
+      <c r="F20" s="3">
         <v>200</v>
       </c>
-      <c r="E20" s="3">
+      <c r="G20" s="3">
         <v>200</v>
       </c>
-      <c r="F20" s="3">
+      <c r="H20" s="3">
         <v>900</v>
       </c>
-      <c r="G20" s="3">
+      <c r="I20" s="3">
         <v>900</v>
       </c>
-      <c r="H20" s="3">
+      <c r="J20" s="3">
         <v>9400</v>
       </c>
-      <c r="I20" s="3">
+      <c r="K20" s="3">
         <v>9400</v>
       </c>
-      <c r="J20" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="K20" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="L20" s="3" t="s">
         <v>3</v>
       </c>
@@ -1450,127 +1517,139 @@
       <c r="N20" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="O20" s="3">
-        <v>100</v>
-      </c>
-      <c r="P20" s="3">
-        <v>0</v>
+      <c r="O20" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="P20" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="Q20" s="3">
         <v>100</v>
       </c>
       <c r="R20" s="3">
+        <v>0</v>
+      </c>
+      <c r="S20" s="3">
         <v>100</v>
       </c>
-      <c r="S20" s="3">
-        <v>0</v>
-      </c>
       <c r="T20" s="3">
-        <v>0</v>
-      </c>
-      <c r="U20" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="V20" s="3" t="s">
-        <v>3</v>
+        <v>100</v>
+      </c>
+      <c r="U20" s="3">
+        <v>0</v>
+      </c>
+      <c r="V20" s="3">
+        <v>0</v>
       </c>
       <c r="W20" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="21" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X20" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Y20" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="21" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
+        <v>-2900</v>
+      </c>
+      <c r="E21" s="3">
+        <v>-2900</v>
+      </c>
+      <c r="F21" s="3">
         <v>-3000</v>
       </c>
-      <c r="E21" s="3">
+      <c r="G21" s="3">
         <v>-3000</v>
       </c>
-      <c r="F21" s="3">
+      <c r="H21" s="3">
         <v>-3300</v>
       </c>
-      <c r="G21" s="3">
+      <c r="I21" s="3">
         <v>-3300</v>
       </c>
-      <c r="H21" s="3">
+      <c r="J21" s="3">
         <v>-11500</v>
       </c>
-      <c r="I21" s="3">
+      <c r="K21" s="3">
         <v>-11500</v>
       </c>
-      <c r="J21" s="3">
+      <c r="L21" s="3">
         <v>-2600</v>
       </c>
-      <c r="K21" s="3">
-        <v>0</v>
-      </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
+        <v>0</v>
+      </c>
+      <c r="N21" s="3">
         <v>-2900</v>
       </c>
-      <c r="M21" s="3">
+      <c r="O21" s="3">
         <v>-3000</v>
       </c>
-      <c r="N21" s="3">
+      <c r="P21" s="3">
         <v>-2500</v>
       </c>
-      <c r="O21" s="3">
+      <c r="Q21" s="3">
         <v>-2900</v>
       </c>
-      <c r="P21" s="3">
+      <c r="R21" s="3">
         <v>-2300</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="S21" s="3">
         <v>-10100</v>
       </c>
-      <c r="R21" s="3">
+      <c r="T21" s="3">
         <v>-5100</v>
       </c>
-      <c r="S21" s="3">
+      <c r="U21" s="3">
         <v>-10500</v>
       </c>
-      <c r="T21" s="3">
+      <c r="V21" s="3">
         <v>-5000</v>
       </c>
-      <c r="U21" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="V21" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="W21" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="22" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X21" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Y21" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="22" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="D22" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="E22" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="F22" s="3">
+      <c r="D22" s="3">
+        <v>0</v>
+      </c>
+      <c r="E22" s="3">
+        <v>0</v>
+      </c>
+      <c r="F22" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="G22" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="H22" s="3">
         <v>-600</v>
       </c>
-      <c r="G22" s="3">
+      <c r="I22" s="3">
         <v>-600</v>
       </c>
-      <c r="H22" s="3">
+      <c r="J22" s="3">
         <v>700</v>
       </c>
-      <c r="I22" s="3">
+      <c r="K22" s="3">
         <v>700</v>
       </c>
-      <c r="J22" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="K22" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="L22" s="3" t="s">
         <v>3</v>
       </c>
@@ -1580,11 +1659,11 @@
       <c r="N22" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="O22" s="3">
-        <v>0</v>
-      </c>
-      <c r="P22" s="3">
-        <v>0</v>
+      <c r="O22" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="P22" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="Q22" s="3">
         <v>0</v>
@@ -1607,73 +1686,85 @@
       <c r="W22" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="23" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X22" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y22" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>-2700</v>
+      </c>
+      <c r="E23" s="3">
+        <v>-2700</v>
+      </c>
+      <c r="F23" s="3">
         <v>-2800</v>
       </c>
-      <c r="E23" s="3">
+      <c r="G23" s="3">
         <v>-2800</v>
       </c>
-      <c r="F23" s="3">
+      <c r="H23" s="3">
         <v>-3200</v>
       </c>
-      <c r="G23" s="3">
+      <c r="I23" s="3">
         <v>-3200</v>
       </c>
-      <c r="H23" s="3">
+      <c r="J23" s="3">
         <v>-12200</v>
       </c>
-      <c r="I23" s="3">
+      <c r="K23" s="3">
         <v>-12200</v>
       </c>
-      <c r="J23" s="3">
+      <c r="L23" s="3">
         <v>-2500</v>
       </c>
-      <c r="K23" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="N23" s="3">
         <v>-3000</v>
-      </c>
-      <c r="M23" s="3">
-        <v>-2900</v>
-      </c>
-      <c r="N23" s="3">
-        <v>-2500</v>
       </c>
       <c r="O23" s="3">
         <v>-2900</v>
       </c>
       <c r="P23" s="3">
+        <v>-2500</v>
+      </c>
+      <c r="Q23" s="3">
+        <v>-2900</v>
+      </c>
+      <c r="R23" s="3">
         <v>-2300</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="S23" s="3">
         <v>-10200</v>
-      </c>
-      <c r="R23" s="3">
-        <v>-5100</v>
-      </c>
-      <c r="S23" s="3">
-        <v>-10700</v>
       </c>
       <c r="T23" s="3">
         <v>-5100</v>
       </c>
-      <c r="U23" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="V23" s="3" t="s">
-        <v>3</v>
+      <c r="U23" s="3">
+        <v>-10700</v>
+      </c>
+      <c r="V23" s="3">
+        <v>-5100</v>
       </c>
       <c r="W23" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="24" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X23" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Y23" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="24" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
@@ -1710,11 +1801,11 @@
       <c r="N24" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="O24" s="3">
-        <v>0</v>
-      </c>
-      <c r="P24" s="3">
-        <v>0</v>
+      <c r="O24" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="P24" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="Q24" s="3">
         <v>0</v>
@@ -1737,8 +1828,14 @@
       <c r="W24" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="25" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X24" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y24" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -1802,138 +1899,156 @@
       <c r="W25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X25" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>-2700</v>
+      </c>
+      <c r="E26" s="3">
+        <v>-2700</v>
+      </c>
+      <c r="F26" s="3">
         <v>-2800</v>
       </c>
-      <c r="E26" s="3">
+      <c r="G26" s="3">
         <v>-2800</v>
       </c>
-      <c r="F26" s="3">
+      <c r="H26" s="3">
         <v>-3200</v>
       </c>
-      <c r="G26" s="3">
+      <c r="I26" s="3">
         <v>-3200</v>
       </c>
-      <c r="H26" s="3">
+      <c r="J26" s="3">
         <v>-12200</v>
       </c>
-      <c r="I26" s="3">
+      <c r="K26" s="3">
         <v>-12200</v>
       </c>
-      <c r="J26" s="3">
+      <c r="L26" s="3">
         <v>-2500</v>
       </c>
-      <c r="K26" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="N26" s="3">
         <v>-3000</v>
-      </c>
-      <c r="M26" s="3">
-        <v>-2900</v>
-      </c>
-      <c r="N26" s="3">
-        <v>-2500</v>
       </c>
       <c r="O26" s="3">
         <v>-2900</v>
       </c>
       <c r="P26" s="3">
+        <v>-2500</v>
+      </c>
+      <c r="Q26" s="3">
+        <v>-2900</v>
+      </c>
+      <c r="R26" s="3">
         <v>-2300</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="S26" s="3">
         <v>-10200</v>
-      </c>
-      <c r="R26" s="3">
-        <v>-5100</v>
-      </c>
-      <c r="S26" s="3">
-        <v>-10700</v>
       </c>
       <c r="T26" s="3">
         <v>-5100</v>
       </c>
-      <c r="U26" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="V26" s="3" t="s">
-        <v>3</v>
+      <c r="U26" s="3">
+        <v>-10700</v>
+      </c>
+      <c r="V26" s="3">
+        <v>-5100</v>
       </c>
       <c r="W26" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="27" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X26" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Y26" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="27" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>-2700</v>
+      </c>
+      <c r="E27" s="3">
+        <v>-2700</v>
+      </c>
+      <c r="F27" s="3">
         <v>-2800</v>
       </c>
-      <c r="E27" s="3">
+      <c r="G27" s="3">
         <v>-2800</v>
       </c>
-      <c r="F27" s="3">
+      <c r="H27" s="3">
         <v>-3200</v>
       </c>
-      <c r="G27" s="3">
+      <c r="I27" s="3">
         <v>-3200</v>
       </c>
-      <c r="H27" s="3">
+      <c r="J27" s="3">
         <v>-12200</v>
       </c>
-      <c r="I27" s="3">
+      <c r="K27" s="3">
         <v>-12200</v>
       </c>
-      <c r="J27" s="3">
+      <c r="L27" s="3">
         <v>-2500</v>
       </c>
-      <c r="K27" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="N27" s="3">
         <v>-3000</v>
-      </c>
-      <c r="M27" s="3">
-        <v>-2900</v>
-      </c>
-      <c r="N27" s="3">
-        <v>-2500</v>
       </c>
       <c r="O27" s="3">
         <v>-2900</v>
       </c>
       <c r="P27" s="3">
+        <v>-2500</v>
+      </c>
+      <c r="Q27" s="3">
+        <v>-2900</v>
+      </c>
+      <c r="R27" s="3">
         <v>-2300</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="S27" s="3">
         <v>-10200</v>
-      </c>
-      <c r="R27" s="3">
-        <v>-5100</v>
-      </c>
-      <c r="S27" s="3">
-        <v>-10700</v>
       </c>
       <c r="T27" s="3">
         <v>-5100</v>
       </c>
-      <c r="U27" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="V27" s="3" t="s">
-        <v>3</v>
+      <c r="U27" s="3">
+        <v>-10700</v>
+      </c>
+      <c r="V27" s="3">
+        <v>-5100</v>
       </c>
       <c r="W27" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="28" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X27" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Y27" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="28" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -1997,8 +2112,14 @@
       <c r="W28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X28" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -2062,8 +2183,14 @@
       <c r="W29" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="30" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X29" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y29" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -2127,8 +2254,14 @@
       <c r="W30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X30" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -2192,35 +2325,41 @@
       <c r="W31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X31" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
+        <v>100</v>
+      </c>
+      <c r="E32" s="3">
+        <v>100</v>
+      </c>
+      <c r="F32" s="3">
         <v>-200</v>
       </c>
-      <c r="E32" s="3">
+      <c r="G32" s="3">
         <v>-200</v>
       </c>
-      <c r="F32" s="3">
+      <c r="H32" s="3">
         <v>-900</v>
       </c>
-      <c r="G32" s="3">
+      <c r="I32" s="3">
         <v>-900</v>
       </c>
-      <c r="H32" s="3">
+      <c r="J32" s="3">
         <v>-9400</v>
       </c>
-      <c r="I32" s="3">
+      <c r="K32" s="3">
         <v>-9400</v>
       </c>
-      <c r="J32" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="K32" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="L32" s="3" t="s">
         <v>3</v>
       </c>
@@ -2230,100 +2369,112 @@
       <c r="N32" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="O32" s="3">
-        <v>-100</v>
-      </c>
-      <c r="P32" s="3">
-        <v>0</v>
+      <c r="O32" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="P32" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="Q32" s="3">
         <v>-100</v>
       </c>
       <c r="R32" s="3">
+        <v>0</v>
+      </c>
+      <c r="S32" s="3">
         <v>-100</v>
       </c>
-      <c r="S32" s="3">
-        <v>0</v>
-      </c>
       <c r="T32" s="3">
-        <v>0</v>
-      </c>
-      <c r="U32" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="V32" s="3" t="s">
-        <v>3</v>
+        <v>-100</v>
+      </c>
+      <c r="U32" s="3">
+        <v>0</v>
+      </c>
+      <c r="V32" s="3">
+        <v>0</v>
       </c>
       <c r="W32" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="33" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X32" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Y32" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="33" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>-2700</v>
+      </c>
+      <c r="E33" s="3">
+        <v>-2700</v>
+      </c>
+      <c r="F33" s="3">
         <v>-2800</v>
       </c>
-      <c r="E33" s="3">
+      <c r="G33" s="3">
         <v>-2800</v>
       </c>
-      <c r="F33" s="3">
+      <c r="H33" s="3">
         <v>-3200</v>
       </c>
-      <c r="G33" s="3">
+      <c r="I33" s="3">
         <v>-3200</v>
       </c>
-      <c r="H33" s="3">
+      <c r="J33" s="3">
         <v>-12200</v>
       </c>
-      <c r="I33" s="3">
+      <c r="K33" s="3">
         <v>-12200</v>
       </c>
-      <c r="J33" s="3">
+      <c r="L33" s="3">
         <v>-2500</v>
       </c>
-      <c r="K33" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="N33" s="3">
         <v>-3000</v>
-      </c>
-      <c r="M33" s="3">
-        <v>-2900</v>
-      </c>
-      <c r="N33" s="3">
-        <v>-2500</v>
       </c>
       <c r="O33" s="3">
         <v>-2900</v>
       </c>
       <c r="P33" s="3">
+        <v>-2500</v>
+      </c>
+      <c r="Q33" s="3">
+        <v>-2900</v>
+      </c>
+      <c r="R33" s="3">
         <v>-2300</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="S33" s="3">
         <v>-10200</v>
-      </c>
-      <c r="R33" s="3">
-        <v>-5100</v>
-      </c>
-      <c r="S33" s="3">
-        <v>-10700</v>
       </c>
       <c r="T33" s="3">
         <v>-5100</v>
       </c>
-      <c r="U33" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="V33" s="3" t="s">
-        <v>3</v>
+      <c r="U33" s="3">
+        <v>-10700</v>
+      </c>
+      <c r="V33" s="3">
+        <v>-5100</v>
       </c>
       <c r="W33" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="34" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X33" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Y33" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="34" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -2387,143 +2538,161 @@
       <c r="W34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X34" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>-2700</v>
+      </c>
+      <c r="E35" s="3">
+        <v>-2700</v>
+      </c>
+      <c r="F35" s="3">
         <v>-2800</v>
       </c>
-      <c r="E35" s="3">
+      <c r="G35" s="3">
         <v>-2800</v>
       </c>
-      <c r="F35" s="3">
+      <c r="H35" s="3">
         <v>-3200</v>
       </c>
-      <c r="G35" s="3">
+      <c r="I35" s="3">
         <v>-3200</v>
       </c>
-      <c r="H35" s="3">
+      <c r="J35" s="3">
         <v>-12200</v>
       </c>
-      <c r="I35" s="3">
+      <c r="K35" s="3">
         <v>-12200</v>
       </c>
-      <c r="J35" s="3">
+      <c r="L35" s="3">
         <v>-2500</v>
       </c>
-      <c r="K35" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="N35" s="3">
         <v>-3000</v>
-      </c>
-      <c r="M35" s="3">
-        <v>-2900</v>
-      </c>
-      <c r="N35" s="3">
-        <v>-2500</v>
       </c>
       <c r="O35" s="3">
         <v>-2900</v>
       </c>
       <c r="P35" s="3">
+        <v>-2500</v>
+      </c>
+      <c r="Q35" s="3">
+        <v>-2900</v>
+      </c>
+      <c r="R35" s="3">
         <v>-2300</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="S35" s="3">
         <v>-10200</v>
-      </c>
-      <c r="R35" s="3">
-        <v>-5100</v>
-      </c>
-      <c r="S35" s="3">
-        <v>-10700</v>
       </c>
       <c r="T35" s="3">
         <v>-5100</v>
       </c>
-      <c r="U35" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="V35" s="3" t="s">
-        <v>3</v>
+      <c r="U35" s="3">
+        <v>-10700</v>
+      </c>
+      <c r="V35" s="3">
+        <v>-5100</v>
       </c>
       <c r="W35" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="37" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X35" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Y35" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="37" spans="2:25" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:23" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>46022</v>
+      </c>
+      <c r="E38" s="2">
+        <v>45930</v>
+      </c>
+      <c r="F38" s="2">
         <v>45838</v>
       </c>
-      <c r="E38" s="2">
+      <c r="G38" s="2">
         <v>45747</v>
       </c>
-      <c r="F38" s="2">
+      <c r="H38" s="2">
         <v>45657</v>
       </c>
-      <c r="G38" s="2">
+      <c r="I38" s="2">
         <v>45565</v>
       </c>
-      <c r="H38" s="2">
+      <c r="J38" s="2">
         <v>45473</v>
       </c>
-      <c r="I38" s="2">
+      <c r="K38" s="2">
         <v>45382</v>
       </c>
-      <c r="J38" s="2">
+      <c r="L38" s="2">
         <v>45291</v>
       </c>
-      <c r="K38" s="2">
+      <c r="M38" s="2">
         <v>45199</v>
       </c>
-      <c r="L38" s="2">
+      <c r="N38" s="2">
         <v>45107</v>
       </c>
-      <c r="M38" s="2">
+      <c r="O38" s="2">
         <v>45016</v>
       </c>
-      <c r="N38" s="2">
+      <c r="P38" s="2">
         <v>44926</v>
       </c>
-      <c r="O38" s="2">
+      <c r="Q38" s="2">
         <v>44742</v>
       </c>
-      <c r="P38" s="2">
+      <c r="R38" s="2">
         <v>44651</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="S38" s="2">
         <v>44561</v>
       </c>
-      <c r="R38" s="2">
+      <c r="T38" s="2">
         <v>44377</v>
       </c>
-      <c r="S38" s="2">
+      <c r="U38" s="2">
         <v>44196</v>
       </c>
-      <c r="T38" s="2">
+      <c r="V38" s="2">
         <v>44012</v>
       </c>
-      <c r="U38" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="V38" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="W38" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="39" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X38" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="Y38" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="39" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -2547,8 +2716,10 @@
       <c r="U39" s="3"/>
       <c r="V39" s="3"/>
       <c r="W39" s="3"/>
-    </row>
-    <row r="40" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X39" s="3"/>
+      <c r="Y39" s="3"/>
+    </row>
+    <row r="40" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -2572,56 +2743,58 @@
       <c r="U40" s="3"/>
       <c r="V40" s="3"/>
       <c r="W40" s="3"/>
-    </row>
-    <row r="41" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X40" s="3"/>
+      <c r="Y40" s="3"/>
+    </row>
+    <row r="41" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>20000</v>
+      </c>
+      <c r="E41" s="3">
+        <v>20000</v>
+      </c>
+      <c r="F41" s="3">
         <v>22400</v>
       </c>
-      <c r="E41" s="3">
+      <c r="G41" s="3">
         <v>22400</v>
       </c>
-      <c r="F41" s="3">
+      <c r="H41" s="3">
         <v>17200</v>
       </c>
-      <c r="G41" s="3">
+      <c r="I41" s="3">
         <v>17200</v>
       </c>
-      <c r="H41" s="3">
+      <c r="J41" s="3">
         <v>9700</v>
       </c>
-      <c r="I41" s="3">
+      <c r="K41" s="3">
         <v>9700</v>
       </c>
-      <c r="J41" s="3">
+      <c r="L41" s="3">
         <v>3100</v>
       </c>
-      <c r="K41" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="N41" s="3">
         <v>8200</v>
       </c>
-      <c r="M41" s="3">
+      <c r="O41" s="3">
         <v>5600</v>
       </c>
-      <c r="N41" s="3">
+      <c r="P41" s="3">
         <v>8300</v>
       </c>
-      <c r="O41" s="3">
+      <c r="Q41" s="3">
         <v>12900</v>
       </c>
-      <c r="P41" s="3">
+      <c r="R41" s="3">
         <v>2200</v>
       </c>
-      <c r="Q41" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="R41" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="S41" s="3" t="s">
         <v>3</v>
       </c>
@@ -2637,8 +2810,14 @@
       <c r="W41" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="42" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X41" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Y41" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="42" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
@@ -2702,43 +2881,49 @@
       <c r="W42" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="43" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X42" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y42" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>200</v>
+      </c>
+      <c r="E43" s="3">
+        <v>200</v>
+      </c>
+      <c r="F43" s="3">
         <v>100</v>
       </c>
-      <c r="E43" s="3">
+      <c r="G43" s="3">
         <v>100</v>
       </c>
-      <c r="F43" s="3">
+      <c r="H43" s="3">
         <v>500</v>
       </c>
-      <c r="G43" s="3">
+      <c r="I43" s="3">
         <v>500</v>
       </c>
-      <c r="H43" s="3">
+      <c r="J43" s="3">
         <v>100</v>
       </c>
-      <c r="I43" s="3">
+      <c r="K43" s="3">
         <v>100</v>
       </c>
-      <c r="J43" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="K43" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="L43" s="3" t="s">
         <v>3</v>
       </c>
       <c r="M43" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="N43" s="3">
-        <v>100</v>
+      <c r="N43" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="O43" s="3" t="s">
         <v>3</v>
@@ -2749,8 +2934,8 @@
       <c r="Q43" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="R43" s="3" t="s">
-        <v>3</v>
+      <c r="R43" s="3">
+        <v>100</v>
       </c>
       <c r="S43" s="3" t="s">
         <v>3</v>
@@ -2767,58 +2952,64 @@
       <c r="W43" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="44" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X43" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Y43" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="44" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
       <c r="D44" s="3">
+        <v>1200</v>
+      </c>
+      <c r="E44" s="3">
+        <v>1200</v>
+      </c>
+      <c r="F44" s="3">
         <v>1400</v>
       </c>
-      <c r="E44" s="3">
+      <c r="G44" s="3">
         <v>1400</v>
       </c>
-      <c r="F44" s="3">
+      <c r="H44" s="3">
         <v>1300</v>
       </c>
-      <c r="G44" s="3">
+      <c r="I44" s="3">
         <v>1300</v>
-      </c>
-      <c r="H44" s="3">
-        <v>1000</v>
-      </c>
-      <c r="I44" s="3">
-        <v>1000</v>
       </c>
       <c r="J44" s="3">
         <v>1000</v>
       </c>
-      <c r="K44" s="3" t="s">
-        <v>3</v>
+      <c r="K44" s="3">
+        <v>1000</v>
       </c>
       <c r="L44" s="3">
+        <v>1000</v>
+      </c>
+      <c r="M44" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="N44" s="3">
         <v>500</v>
       </c>
-      <c r="M44" s="3">
+      <c r="O44" s="3">
         <v>100</v>
       </c>
-      <c r="N44" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="O44" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="P44" s="3" t="s">
         <v>3</v>
       </c>
       <c r="Q44" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="R44" s="3">
-        <v>0</v>
-      </c>
-      <c r="S44" s="3">
-        <v>0</v>
+      <c r="R44" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="S44" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="T44" s="3">
         <v>0</v>
@@ -2832,56 +3023,62 @@
       <c r="W44" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="45" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X44" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y44" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="45" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
+        <v>100</v>
+      </c>
+      <c r="E45" s="3">
+        <v>100</v>
+      </c>
+      <c r="F45" s="3">
         <v>500</v>
       </c>
-      <c r="E45" s="3">
+      <c r="G45" s="3">
         <v>500</v>
       </c>
-      <c r="F45" s="3">
+      <c r="H45" s="3">
         <v>200</v>
       </c>
-      <c r="G45" s="3">
+      <c r="I45" s="3">
         <v>200</v>
       </c>
-      <c r="H45" s="3">
+      <c r="J45" s="3">
         <v>400</v>
       </c>
-      <c r="I45" s="3">
+      <c r="K45" s="3">
         <v>400</v>
       </c>
-      <c r="J45" s="3">
+      <c r="L45" s="3">
         <v>200</v>
       </c>
-      <c r="K45" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="L45" s="3">
+      <c r="M45" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="N45" s="3">
         <v>400</v>
       </c>
-      <c r="M45" s="3">
+      <c r="O45" s="3">
         <v>400</v>
       </c>
-      <c r="N45" s="3">
+      <c r="P45" s="3">
         <v>100</v>
       </c>
-      <c r="O45" s="3">
+      <c r="Q45" s="3">
         <v>1000</v>
       </c>
-      <c r="P45" s="3">
+      <c r="R45" s="3">
         <v>1000</v>
       </c>
-      <c r="Q45" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="R45" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="S45" s="3" t="s">
         <v>3</v>
       </c>
@@ -2897,56 +3094,62 @@
       <c r="W45" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="46" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X45" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Y45" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="46" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>22000</v>
+      </c>
+      <c r="E46" s="3">
+        <v>22000</v>
+      </c>
+      <c r="F46" s="3">
         <v>24700</v>
       </c>
-      <c r="E46" s="3">
+      <c r="G46" s="3">
         <v>24700</v>
       </c>
-      <c r="F46" s="3">
+      <c r="H46" s="3">
         <v>19700</v>
       </c>
-      <c r="G46" s="3">
+      <c r="I46" s="3">
         <v>19700</v>
       </c>
-      <c r="H46" s="3">
+      <c r="J46" s="3">
         <v>11400</v>
       </c>
-      <c r="I46" s="3">
+      <c r="K46" s="3">
         <v>11400</v>
       </c>
-      <c r="J46" s="3">
+      <c r="L46" s="3">
         <v>4600</v>
       </c>
-      <c r="K46" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="N46" s="3">
         <v>9300</v>
       </c>
-      <c r="M46" s="3">
+      <c r="O46" s="3">
         <v>6300</v>
       </c>
-      <c r="N46" s="3">
+      <c r="P46" s="3">
         <v>8800</v>
       </c>
-      <c r="O46" s="3">
+      <c r="Q46" s="3">
         <v>14000</v>
       </c>
-      <c r="P46" s="3">
+      <c r="R46" s="3">
         <v>3300</v>
       </c>
-      <c r="Q46" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="R46" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="S46" s="3" t="s">
         <v>3</v>
       </c>
@@ -2962,8 +3165,14 @@
       <c r="W46" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="47" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X46" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Y46" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="47" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
@@ -3000,11 +3209,11 @@
       <c r="N47" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="O47" s="3">
-        <v>0</v>
-      </c>
-      <c r="P47" s="3">
-        <v>0</v>
+      <c r="O47" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="P47" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="Q47" s="3">
         <v>0</v>
@@ -3027,56 +3236,62 @@
       <c r="W47" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="48" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X47" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y47" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="48" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>600</v>
+      </c>
+      <c r="E48" s="3">
+        <v>600</v>
+      </c>
+      <c r="F48" s="3">
         <v>700</v>
       </c>
-      <c r="E48" s="3">
+      <c r="G48" s="3">
         <v>700</v>
       </c>
-      <c r="F48" s="3">
+      <c r="H48" s="3">
         <v>900</v>
       </c>
-      <c r="G48" s="3">
+      <c r="I48" s="3">
         <v>900</v>
       </c>
-      <c r="H48" s="3">
+      <c r="J48" s="3">
         <v>1100</v>
       </c>
-      <c r="I48" s="3">
+      <c r="K48" s="3">
         <v>1100</v>
       </c>
-      <c r="J48" s="3">
+      <c r="L48" s="3">
         <v>1300</v>
       </c>
-      <c r="K48" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="N48" s="3">
         <v>1500</v>
       </c>
-      <c r="M48" s="3">
+      <c r="O48" s="3">
         <v>1600</v>
       </c>
-      <c r="N48" s="3">
+      <c r="P48" s="3">
         <v>1600</v>
       </c>
-      <c r="O48" s="3">
+      <c r="Q48" s="3">
         <v>1800</v>
       </c>
-      <c r="P48" s="3">
+      <c r="R48" s="3">
         <v>1900</v>
       </c>
-      <c r="Q48" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="R48" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="S48" s="3" t="s">
         <v>3</v>
       </c>
@@ -3092,8 +3307,14 @@
       <c r="W48" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="49" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X48" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Y48" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="49" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
@@ -3118,14 +3339,14 @@
       <c r="J49" s="3">
         <v>0</v>
       </c>
-      <c r="K49" s="3" t="s">
-        <v>3</v>
+      <c r="K49" s="3">
+        <v>0</v>
       </c>
       <c r="L49" s="3">
         <v>0</v>
       </c>
-      <c r="M49" s="3">
-        <v>0</v>
+      <c r="M49" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="N49" s="3">
         <v>0</v>
@@ -3157,8 +3378,14 @@
       <c r="W49" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="50" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X49" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y49" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="50" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -3222,8 +3449,14 @@
       <c r="W50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X50" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -3287,8 +3520,14 @@
       <c r="W51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X51" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
@@ -3325,11 +3564,11 @@
       <c r="N52" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="O52" s="3">
-        <v>0</v>
-      </c>
-      <c r="P52" s="3">
-        <v>0</v>
+      <c r="O52" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="P52" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="Q52" s="3">
         <v>0</v>
@@ -3352,8 +3591,14 @@
       <c r="W52" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="53" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X52" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y52" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="53" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -3417,56 +3662,62 @@
       <c r="W53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X53" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>22500</v>
+      </c>
+      <c r="E54" s="3">
+        <v>22500</v>
+      </c>
+      <c r="F54" s="3">
         <v>25400</v>
       </c>
-      <c r="E54" s="3">
+      <c r="G54" s="3">
         <v>25400</v>
       </c>
-      <c r="F54" s="3">
+      <c r="H54" s="3">
         <v>20600</v>
       </c>
-      <c r="G54" s="3">
+      <c r="I54" s="3">
         <v>20600</v>
       </c>
-      <c r="H54" s="3">
+      <c r="J54" s="3">
         <v>12500</v>
       </c>
-      <c r="I54" s="3">
+      <c r="K54" s="3">
         <v>12500</v>
       </c>
-      <c r="J54" s="3">
+      <c r="L54" s="3">
         <v>5900</v>
       </c>
-      <c r="K54" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="N54" s="3">
         <v>10800</v>
       </c>
-      <c r="M54" s="3">
+      <c r="O54" s="3">
         <v>7900</v>
       </c>
-      <c r="N54" s="3">
+      <c r="P54" s="3">
         <v>10400</v>
       </c>
-      <c r="O54" s="3">
+      <c r="Q54" s="3">
         <v>15700</v>
       </c>
-      <c r="P54" s="3">
+      <c r="R54" s="3">
         <v>5200</v>
       </c>
-      <c r="Q54" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="R54" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="S54" s="3" t="s">
         <v>3</v>
       </c>
@@ -3482,8 +3733,14 @@
       <c r="W54" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="55" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X54" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Y54" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="55" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -3507,8 +3764,10 @@
       <c r="U55" s="3"/>
       <c r="V55" s="3"/>
       <c r="W55" s="3"/>
-    </row>
-    <row r="56" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X55" s="3"/>
+      <c r="Y55" s="3"/>
+    </row>
+    <row r="56" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -3532,16 +3791,18 @@
       <c r="U56" s="3"/>
       <c r="V56" s="3"/>
       <c r="W56" s="3"/>
-    </row>
-    <row r="57" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X56" s="3"/>
+      <c r="Y56" s="3"/>
+    </row>
+    <row r="57" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
-        <v>100</v>
+        <v>200</v>
       </c>
       <c r="E57" s="3">
-        <v>100</v>
+        <v>200</v>
       </c>
       <c r="F57" s="3">
         <v>100</v>
@@ -3556,31 +3817,31 @@
         <v>100</v>
       </c>
       <c r="J57" s="3">
-        <v>200</v>
-      </c>
-      <c r="K57" s="3" t="s">
-        <v>3</v>
+        <v>100</v>
+      </c>
+      <c r="K57" s="3">
+        <v>100</v>
       </c>
       <c r="L57" s="3">
         <v>200</v>
       </c>
-      <c r="M57" s="3">
+      <c r="M57" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="N57" s="3">
         <v>200</v>
       </c>
-      <c r="N57" s="3">
-        <v>100</v>
-      </c>
       <c r="O57" s="3">
-        <v>100</v>
+        <v>200</v>
       </c>
       <c r="P57" s="3">
         <v>100</v>
       </c>
-      <c r="Q57" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="R57" s="3" t="s">
-        <v>3</v>
+      <c r="Q57" s="3">
+        <v>100</v>
+      </c>
+      <c r="R57" s="3">
+        <v>100</v>
       </c>
       <c r="S57" s="3" t="s">
         <v>3</v>
@@ -3597,16 +3858,22 @@
       <c r="W57" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="58" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X57" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Y57" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="58" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
-        <v>300</v>
+        <v>200</v>
       </c>
       <c r="E58" s="3">
-        <v>300</v>
+        <v>200</v>
       </c>
       <c r="F58" s="3">
         <v>300</v>
@@ -3623,30 +3890,30 @@
       <c r="J58" s="3">
         <v>300</v>
       </c>
-      <c r="K58" s="3" t="s">
-        <v>3</v>
+      <c r="K58" s="3">
+        <v>300</v>
       </c>
       <c r="L58" s="3">
         <v>300</v>
       </c>
-      <c r="M58" s="3">
-        <v>300</v>
+      <c r="M58" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="N58" s="3">
         <v>300</v>
       </c>
-      <c r="O58" s="3" t="s">
-        <v>3</v>
+      <c r="O58" s="3">
+        <v>300</v>
       </c>
       <c r="P58" s="3">
+        <v>300</v>
+      </c>
+      <c r="Q58" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R58" s="3">
         <v>1000</v>
       </c>
-      <c r="Q58" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="R58" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="S58" s="3" t="s">
         <v>3</v>
       </c>
@@ -3662,56 +3929,62 @@
       <c r="W58" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="59" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X58" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Y58" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="59" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>600</v>
+      </c>
+      <c r="E59" s="3">
+        <v>600</v>
+      </c>
+      <c r="F59" s="3">
         <v>2200</v>
       </c>
-      <c r="E59" s="3">
+      <c r="G59" s="3">
         <v>2200</v>
       </c>
-      <c r="F59" s="3">
+      <c r="H59" s="3">
         <v>1000</v>
       </c>
-      <c r="G59" s="3">
+      <c r="I59" s="3">
         <v>1000</v>
       </c>
-      <c r="H59" s="3">
+      <c r="J59" s="3">
         <v>1800</v>
       </c>
-      <c r="I59" s="3">
+      <c r="K59" s="3">
         <v>1800</v>
       </c>
-      <c r="J59" s="3">
+      <c r="L59" s="3">
         <v>1000</v>
       </c>
-      <c r="K59" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="N59" s="3">
         <v>1700</v>
       </c>
-      <c r="M59" s="3">
+      <c r="O59" s="3">
         <v>1200</v>
       </c>
-      <c r="N59" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q59" s="3">
         <v>1400</v>
       </c>
-      <c r="P59" s="3">
+      <c r="R59" s="3">
         <v>1600</v>
       </c>
-      <c r="Q59" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="R59" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="S59" s="3" t="s">
         <v>3</v>
       </c>
@@ -3727,56 +4000,62 @@
       <c r="W59" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="60" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X59" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Y59" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="60" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>2200</v>
+      </c>
+      <c r="E60" s="3">
+        <v>2200</v>
+      </c>
+      <c r="F60" s="3">
         <v>2600</v>
       </c>
-      <c r="E60" s="3">
+      <c r="G60" s="3">
         <v>2600</v>
       </c>
-      <c r="F60" s="3">
+      <c r="H60" s="3">
         <v>2700</v>
       </c>
-      <c r="G60" s="3">
+      <c r="I60" s="3">
         <v>2700</v>
       </c>
-      <c r="H60" s="3">
+      <c r="J60" s="3">
         <v>2200</v>
       </c>
-      <c r="I60" s="3">
+      <c r="K60" s="3">
         <v>2200</v>
       </c>
-      <c r="J60" s="3">
+      <c r="L60" s="3">
         <v>2600</v>
       </c>
-      <c r="K60" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="N60" s="3">
         <v>2200</v>
       </c>
-      <c r="M60" s="3">
+      <c r="O60" s="3">
         <v>1800</v>
       </c>
-      <c r="N60" s="3">
+      <c r="P60" s="3">
         <v>1400</v>
       </c>
-      <c r="O60" s="3">
+      <c r="Q60" s="3">
         <v>1500</v>
       </c>
-      <c r="P60" s="3">
+      <c r="R60" s="3">
         <v>2700</v>
       </c>
-      <c r="Q60" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="R60" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="S60" s="3" t="s">
         <v>3</v>
       </c>
@@ -3792,50 +4071,56 @@
       <c r="W60" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="61" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X60" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Y60" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="61" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>0</v>
+      </c>
+      <c r="E61" s="3">
+        <v>0</v>
+      </c>
+      <c r="F61" s="3">
         <v>100</v>
       </c>
-      <c r="E61" s="3">
+      <c r="G61" s="3">
         <v>100</v>
       </c>
-      <c r="F61" s="3">
+      <c r="H61" s="3">
         <v>200</v>
       </c>
-      <c r="G61" s="3">
+      <c r="I61" s="3">
         <v>200</v>
       </c>
-      <c r="H61" s="3">
+      <c r="J61" s="3">
         <v>400</v>
       </c>
-      <c r="I61" s="3">
+      <c r="K61" s="3">
         <v>400</v>
       </c>
-      <c r="J61" s="3">
+      <c r="L61" s="3">
         <v>500</v>
       </c>
-      <c r="K61" s="3">
-        <v>0</v>
-      </c>
-      <c r="L61" s="3">
+      <c r="M61" s="3">
+        <v>0</v>
+      </c>
+      <c r="N61" s="3">
         <v>600</v>
       </c>
-      <c r="M61" s="3">
+      <c r="O61" s="3">
         <v>700</v>
       </c>
-      <c r="N61" s="3">
+      <c r="P61" s="3">
         <v>800</v>
       </c>
-      <c r="O61" s="3">
-        <v>0</v>
-      </c>
-      <c r="P61" s="3">
-        <v>0</v>
-      </c>
       <c r="Q61" s="3">
         <v>0</v>
       </c>
@@ -3857,8 +4142,14 @@
       <c r="W61" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="62" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X61" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y61" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
@@ -3895,18 +4186,18 @@
       <c r="N62" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="O62" s="3">
+      <c r="O62" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="P62" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q62" s="3">
         <v>900</v>
       </c>
-      <c r="P62" s="3">
+      <c r="R62" s="3">
         <v>1100</v>
       </c>
-      <c r="Q62" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="R62" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="S62" s="3" t="s">
         <v>3</v>
       </c>
@@ -3922,8 +4213,14 @@
       <c r="W62" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="63" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X62" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Y62" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="63" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -3987,8 +4284,14 @@
       <c r="W63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X63" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -4052,8 +4355,14 @@
       <c r="W64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X64" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -4117,56 +4426,62 @@
       <c r="W65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X65" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>2200</v>
+      </c>
+      <c r="E66" s="3">
+        <v>2200</v>
+      </c>
+      <c r="F66" s="3">
         <v>2700</v>
       </c>
-      <c r="E66" s="3">
+      <c r="G66" s="3">
         <v>2700</v>
       </c>
-      <c r="F66" s="3">
+      <c r="H66" s="3">
         <v>2900</v>
       </c>
-      <c r="G66" s="3">
+      <c r="I66" s="3">
         <v>2900</v>
       </c>
-      <c r="H66" s="3">
+      <c r="J66" s="3">
         <v>2600</v>
       </c>
-      <c r="I66" s="3">
+      <c r="K66" s="3">
         <v>2600</v>
       </c>
-      <c r="J66" s="3">
+      <c r="L66" s="3">
         <v>3100</v>
       </c>
-      <c r="K66" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="N66" s="3">
         <v>2800</v>
-      </c>
-      <c r="M66" s="3">
-        <v>2500</v>
-      </c>
-      <c r="N66" s="3">
-        <v>2200</v>
       </c>
       <c r="O66" s="3">
         <v>2500</v>
       </c>
       <c r="P66" s="3">
+        <v>2200</v>
+      </c>
+      <c r="Q66" s="3">
+        <v>2500</v>
+      </c>
+      <c r="R66" s="3">
         <v>3800</v>
       </c>
-      <c r="Q66" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="R66" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="S66" s="3" t="s">
         <v>3</v>
       </c>
@@ -4182,8 +4497,14 @@
       <c r="W66" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="67" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X66" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Y66" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="67" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -4207,8 +4528,10 @@
       <c r="U67" s="3"/>
       <c r="V67" s="3"/>
       <c r="W67" s="3"/>
-    </row>
-    <row r="68" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X67" s="3"/>
+      <c r="Y67" s="3"/>
+    </row>
+    <row r="68" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -4272,8 +4595,14 @@
       <c r="W68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X68" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -4337,8 +4666,14 @@
       <c r="W69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X69" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -4379,14 +4714,14 @@
         <v>0</v>
       </c>
       <c r="P70" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q70" s="3">
+        <v>0</v>
+      </c>
+      <c r="R70" s="3">
         <v>12000</v>
       </c>
-      <c r="Q70" s="3">
-        <v>0</v>
-      </c>
-      <c r="R70" s="3">
-        <v>0</v>
-      </c>
       <c r="S70" s="3">
         <v>0</v>
       </c>
@@ -4402,8 +4737,14 @@
       <c r="W70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X70" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -4467,56 +4808,62 @@
       <c r="W71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X71" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>-107800</v>
+      </c>
+      <c r="E72" s="3">
+        <v>-107800</v>
+      </c>
+      <c r="F72" s="3">
         <v>-102300</v>
       </c>
-      <c r="E72" s="3">
+      <c r="G72" s="3">
         <v>-102300</v>
       </c>
-      <c r="F72" s="3">
+      <c r="H72" s="3">
         <v>-96700</v>
       </c>
-      <c r="G72" s="3">
+      <c r="I72" s="3">
         <v>-96700</v>
       </c>
-      <c r="H72" s="3">
+      <c r="J72" s="3">
         <v>-90300</v>
       </c>
-      <c r="I72" s="3">
+      <c r="K72" s="3">
         <v>-90300</v>
       </c>
-      <c r="J72" s="3">
+      <c r="L72" s="3">
         <v>-66000</v>
       </c>
-      <c r="K72" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="N72" s="3">
         <v>-60600</v>
       </c>
-      <c r="M72" s="3">
+      <c r="O72" s="3">
         <v>-57700</v>
       </c>
-      <c r="N72" s="3">
+      <c r="P72" s="3">
         <v>-54800</v>
       </c>
-      <c r="O72" s="3">
+      <c r="Q72" s="3">
         <v>-49600</v>
       </c>
-      <c r="P72" s="3">
+      <c r="R72" s="3">
         <v>-46700</v>
       </c>
-      <c r="Q72" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="R72" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="S72" s="3" t="s">
         <v>3</v>
       </c>
@@ -4532,8 +4879,14 @@
       <c r="W72" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="73" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X72" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Y72" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="73" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -4597,8 +4950,14 @@
       <c r="W73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X73" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -4662,8 +5021,14 @@
       <c r="W74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X74" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -4727,56 +5092,62 @@
       <c r="W75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X75" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>20300</v>
+      </c>
+      <c r="E76" s="3">
+        <v>20300</v>
+      </c>
+      <c r="F76" s="3">
         <v>22700</v>
       </c>
-      <c r="E76" s="3">
+      <c r="G76" s="3">
         <v>22700</v>
       </c>
-      <c r="F76" s="3">
+      <c r="H76" s="3">
         <v>17700</v>
       </c>
-      <c r="G76" s="3">
+      <c r="I76" s="3">
         <v>17700</v>
       </c>
-      <c r="H76" s="3">
+      <c r="J76" s="3">
         <v>9900</v>
       </c>
-      <c r="I76" s="3">
+      <c r="K76" s="3">
         <v>9900</v>
       </c>
-      <c r="J76" s="3">
+      <c r="L76" s="3">
         <v>2800</v>
       </c>
-      <c r="K76" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="N76" s="3">
         <v>8000</v>
       </c>
-      <c r="M76" s="3">
+      <c r="O76" s="3">
         <v>5400</v>
       </c>
-      <c r="N76" s="3">
+      <c r="P76" s="3">
         <v>8300</v>
       </c>
-      <c r="O76" s="3">
+      <c r="Q76" s="3">
         <v>13300</v>
       </c>
-      <c r="P76" s="3">
+      <c r="R76" s="3">
         <v>-10500</v>
       </c>
-      <c r="Q76" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="R76" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="S76" s="3" t="s">
         <v>3</v>
       </c>
@@ -4792,8 +5163,14 @@
       <c r="W76" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="77" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X76" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Y76" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="77" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -4857,143 +5234,161 @@
       <c r="W77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X77" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:25" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:23" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>46022</v>
+      </c>
+      <c r="E80" s="2">
+        <v>45930</v>
+      </c>
+      <c r="F80" s="2">
         <v>45838</v>
       </c>
-      <c r="E80" s="2">
+      <c r="G80" s="2">
         <v>45747</v>
       </c>
-      <c r="F80" s="2">
+      <c r="H80" s="2">
         <v>45657</v>
       </c>
-      <c r="G80" s="2">
+      <c r="I80" s="2">
         <v>45565</v>
       </c>
-      <c r="H80" s="2">
+      <c r="J80" s="2">
         <v>45473</v>
       </c>
-      <c r="I80" s="2">
+      <c r="K80" s="2">
         <v>45382</v>
       </c>
-      <c r="J80" s="2">
+      <c r="L80" s="2">
         <v>45291</v>
       </c>
-      <c r="K80" s="2">
+      <c r="M80" s="2">
         <v>45199</v>
       </c>
-      <c r="L80" s="2">
+      <c r="N80" s="2">
         <v>45107</v>
       </c>
-      <c r="M80" s="2">
+      <c r="O80" s="2">
         <v>45016</v>
       </c>
-      <c r="N80" s="2">
+      <c r="P80" s="2">
         <v>44926</v>
       </c>
-      <c r="O80" s="2">
+      <c r="Q80" s="2">
         <v>44742</v>
       </c>
-      <c r="P80" s="2">
+      <c r="R80" s="2">
         <v>44651</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="S80" s="2">
         <v>44561</v>
       </c>
-      <c r="R80" s="2">
+      <c r="T80" s="2">
         <v>44377</v>
       </c>
-      <c r="S80" s="2">
+      <c r="U80" s="2">
         <v>44196</v>
       </c>
-      <c r="T80" s="2">
+      <c r="V80" s="2">
         <v>44012</v>
       </c>
-      <c r="U80" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="V80" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="W80" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="81" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X80" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="Y80" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="81" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>-2700</v>
+      </c>
+      <c r="E81" s="3">
+        <v>-2700</v>
+      </c>
+      <c r="F81" s="3">
         <v>-2800</v>
       </c>
-      <c r="E81" s="3">
+      <c r="G81" s="3">
         <v>-2800</v>
       </c>
-      <c r="F81" s="3">
+      <c r="H81" s="3">
         <v>-3200</v>
       </c>
-      <c r="G81" s="3">
+      <c r="I81" s="3">
         <v>-3200</v>
       </c>
-      <c r="H81" s="3">
+      <c r="J81" s="3">
         <v>-12200</v>
       </c>
-      <c r="I81" s="3">
+      <c r="K81" s="3">
         <v>-12200</v>
       </c>
-      <c r="J81" s="3">
+      <c r="L81" s="3">
         <v>-2500</v>
       </c>
-      <c r="K81" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="N81" s="3">
         <v>-3000</v>
-      </c>
-      <c r="M81" s="3">
-        <v>-2900</v>
-      </c>
-      <c r="N81" s="3">
-        <v>-2500</v>
       </c>
       <c r="O81" s="3">
         <v>-2900</v>
       </c>
       <c r="P81" s="3">
+        <v>-2500</v>
+      </c>
+      <c r="Q81" s="3">
+        <v>-2900</v>
+      </c>
+      <c r="R81" s="3">
         <v>-2300</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="S81" s="3">
         <v>-10200</v>
-      </c>
-      <c r="R81" s="3">
-        <v>-5100</v>
-      </c>
-      <c r="S81" s="3">
-        <v>-10700</v>
       </c>
       <c r="T81" s="3">
         <v>-5100</v>
       </c>
-      <c r="U81" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="V81" s="3" t="s">
-        <v>3</v>
+      <c r="U81" s="3">
+        <v>-10700</v>
+      </c>
+      <c r="V81" s="3">
+        <v>-5100</v>
       </c>
       <c r="W81" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="82" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X81" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Y81" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="82" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -5017,8 +5412,10 @@
       <c r="U82" s="3"/>
       <c r="V82" s="3"/>
       <c r="W82" s="3"/>
-    </row>
-    <row r="83" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X82" s="3"/>
+      <c r="Y82" s="3"/>
+    </row>
+    <row r="83" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
@@ -5043,14 +5440,14 @@
       <c r="J83" s="3">
         <v>0</v>
       </c>
-      <c r="K83" s="3" t="s">
-        <v>3</v>
+      <c r="K83" s="3">
+        <v>0</v>
       </c>
       <c r="L83" s="3">
         <v>0</v>
       </c>
-      <c r="M83" s="3">
-        <v>0</v>
+      <c r="M83" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="N83" s="3">
         <v>0</v>
@@ -5062,28 +5459,34 @@
         <v>0</v>
       </c>
       <c r="Q83" s="3">
+        <v>0</v>
+      </c>
+      <c r="R83" s="3">
+        <v>0</v>
+      </c>
+      <c r="S83" s="3">
         <v>100</v>
-      </c>
-      <c r="R83" s="3">
-        <v>100</v>
-      </c>
-      <c r="S83" s="3">
-        <v>200</v>
       </c>
       <c r="T83" s="3">
         <v>100</v>
       </c>
-      <c r="U83" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="V83" s="3" t="s">
-        <v>3</v>
+      <c r="U83" s="3">
+        <v>200</v>
+      </c>
+      <c r="V83" s="3">
+        <v>100</v>
       </c>
       <c r="W83" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="84" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X83" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Y83" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="84" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -5147,8 +5550,14 @@
       <c r="W84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X84" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -5212,8 +5621,14 @@
       <c r="W85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X85" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -5277,8 +5692,14 @@
       <c r="W86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X86" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -5342,8 +5763,14 @@
       <c r="W87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X87" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -5407,73 +5834,85 @@
       <c r="W88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X88" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>-2200</v>
+      </c>
+      <c r="E89" s="3">
+        <v>-2200</v>
+      </c>
+      <c r="F89" s="3">
         <v>-2300</v>
       </c>
-      <c r="E89" s="3">
+      <c r="G89" s="3">
         <v>-2300</v>
       </c>
-      <c r="F89" s="3">
+      <c r="H89" s="3">
         <v>-2500</v>
       </c>
-      <c r="G89" s="3">
+      <c r="I89" s="3">
         <v>-2500</v>
       </c>
-      <c r="H89" s="3">
+      <c r="J89" s="3">
         <v>-2300</v>
       </c>
-      <c r="I89" s="3">
+      <c r="K89" s="3">
         <v>-2300</v>
       </c>
-      <c r="J89" s="3">
+      <c r="L89" s="3">
         <v>-1900</v>
       </c>
-      <c r="K89" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="N89" s="3">
         <v>-2900</v>
       </c>
-      <c r="M89" s="3">
+      <c r="O89" s="3">
         <v>-2500</v>
       </c>
-      <c r="N89" s="3">
+      <c r="P89" s="3">
         <v>-2100</v>
       </c>
-      <c r="O89" s="3">
+      <c r="Q89" s="3">
         <v>-2900</v>
       </c>
-      <c r="P89" s="3">
+      <c r="R89" s="3">
         <v>-2500</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="S89" s="3">
         <v>-9900</v>
       </c>
-      <c r="R89" s="3">
+      <c r="T89" s="3">
         <v>-5000</v>
       </c>
-      <c r="S89" s="3">
+      <c r="U89" s="3">
         <v>-7200</v>
       </c>
-      <c r="T89" s="3">
+      <c r="V89" s="3">
         <v>-4100</v>
       </c>
-      <c r="U89" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="V89" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="W89" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="90" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X89" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Y89" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="90" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -5497,16 +5936,18 @@
       <c r="U90" s="3"/>
       <c r="V90" s="3"/>
       <c r="W90" s="3"/>
-    </row>
-    <row r="91" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X90" s="3"/>
+      <c r="Y90" s="3"/>
+    </row>
+    <row r="91" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="E91" s="3">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="F91" s="3">
         <v>0</v>
@@ -5523,47 +5964,53 @@
       <c r="J91" s="3">
         <v>0</v>
       </c>
-      <c r="K91" s="3" t="s">
-        <v>3</v>
+      <c r="K91" s="3">
+        <v>0</v>
       </c>
       <c r="L91" s="3">
+        <v>0</v>
+      </c>
+      <c r="M91" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="N91" s="3">
         <v>-100</v>
       </c>
-      <c r="M91" s="3">
+      <c r="O91" s="3">
         <v>-100</v>
       </c>
-      <c r="N91" s="3">
-        <v>0</v>
-      </c>
-      <c r="O91" s="3">
-        <v>0</v>
-      </c>
       <c r="P91" s="3">
         <v>0</v>
       </c>
       <c r="Q91" s="3">
+        <v>0</v>
+      </c>
+      <c r="R91" s="3">
+        <v>0</v>
+      </c>
+      <c r="S91" s="3">
         <v>-200</v>
       </c>
-      <c r="R91" s="3">
-        <v>0</v>
-      </c>
-      <c r="S91" s="3">
-        <v>0</v>
-      </c>
       <c r="T91" s="3">
+        <v>0</v>
+      </c>
+      <c r="U91" s="3">
+        <v>0</v>
+      </c>
+      <c r="V91" s="3">
         <v>-100</v>
       </c>
-      <c r="U91" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="V91" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="W91" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="92" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X91" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Y91" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="92" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -5627,8 +6074,14 @@
       <c r="W92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X92" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -5692,16 +6145,22 @@
       <c r="W93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X93" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="E94" s="3">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="F94" s="3">
         <v>0</v>
@@ -5718,47 +6177,53 @@
       <c r="J94" s="3">
         <v>0</v>
       </c>
-      <c r="K94" s="3" t="s">
-        <v>3</v>
+      <c r="K94" s="3">
+        <v>0</v>
       </c>
       <c r="L94" s="3">
+        <v>0</v>
+      </c>
+      <c r="M94" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="N94" s="3">
         <v>-100</v>
       </c>
-      <c r="M94" s="3">
+      <c r="O94" s="3">
         <v>-100</v>
       </c>
-      <c r="N94" s="3">
-        <v>0</v>
-      </c>
-      <c r="O94" s="3">
-        <v>0</v>
-      </c>
       <c r="P94" s="3">
         <v>0</v>
       </c>
       <c r="Q94" s="3">
+        <v>0</v>
+      </c>
+      <c r="R94" s="3">
+        <v>0</v>
+      </c>
+      <c r="S94" s="3">
         <v>-300</v>
       </c>
-      <c r="R94" s="3">
-        <v>0</v>
-      </c>
-      <c r="S94" s="3">
+      <c r="T94" s="3">
+        <v>0</v>
+      </c>
+      <c r="U94" s="3">
         <v>-100</v>
       </c>
-      <c r="T94" s="3">
+      <c r="V94" s="3">
         <v>-100</v>
       </c>
-      <c r="U94" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="V94" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="W94" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="95" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X94" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Y94" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="95" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -5782,8 +6247,10 @@
       <c r="U95" s="3"/>
       <c r="V95" s="3"/>
       <c r="W95" s="3"/>
-    </row>
-    <row r="96" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X95" s="3"/>
+      <c r="Y95" s="3"/>
+    </row>
+    <row r="96" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -5820,11 +6287,11 @@
       <c r="N96" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="O96" s="3">
-        <v>0</v>
-      </c>
-      <c r="P96" s="3">
-        <v>0</v>
+      <c r="O96" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="P96" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="Q96" s="3">
         <v>0</v>
@@ -5847,8 +6314,14 @@
       <c r="W96" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="97" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X96" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y96" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -5912,8 +6385,14 @@
       <c r="W97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X97" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -5977,8 +6456,14 @@
       <c r="W98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X98" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -6042,73 +6527,85 @@
       <c r="W99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X99" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>1000</v>
+      </c>
+      <c r="E100" s="3">
+        <v>1000</v>
+      </c>
+      <c r="F100" s="3">
         <v>4900</v>
       </c>
-      <c r="E100" s="3">
+      <c r="G100" s="3">
         <v>4900</v>
       </c>
-      <c r="F100" s="3">
+      <c r="H100" s="3">
         <v>6300</v>
       </c>
-      <c r="G100" s="3">
+      <c r="I100" s="3">
         <v>6300</v>
       </c>
-      <c r="H100" s="3">
+      <c r="J100" s="3">
         <v>5600</v>
       </c>
-      <c r="I100" s="3">
+      <c r="K100" s="3">
         <v>5600</v>
       </c>
-      <c r="J100" s="3">
-        <v>0</v>
-      </c>
-      <c r="K100" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="L100" s="3">
+        <v>0</v>
+      </c>
+      <c r="M100" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="N100" s="3">
         <v>5500</v>
       </c>
-      <c r="M100" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="N100" s="3">
-        <v>0</v>
-      </c>
-      <c r="O100" s="3">
+      <c r="O100" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="P100" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q100" s="3">
         <v>13600</v>
       </c>
-      <c r="P100" s="3">
+      <c r="R100" s="3">
         <v>3000</v>
       </c>
-      <c r="Q100" s="3">
+      <c r="S100" s="3">
         <v>5100</v>
       </c>
-      <c r="R100" s="3">
+      <c r="T100" s="3">
         <v>5100</v>
       </c>
-      <c r="S100" s="3">
+      <c r="U100" s="3">
         <v>5000</v>
       </c>
-      <c r="T100" s="3">
-        <v>0</v>
-      </c>
-      <c r="U100" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="V100" s="3" t="s">
-        <v>3</v>
+      <c r="V100" s="3">
+        <v>0</v>
       </c>
       <c r="W100" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="101" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X100" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Y100" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="101" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
@@ -6119,14 +6616,14 @@
         <v>0</v>
       </c>
       <c r="F101" s="3">
+        <v>0</v>
+      </c>
+      <c r="G101" s="3">
+        <v>0</v>
+      </c>
+      <c r="H101" s="3">
         <v>100</v>
       </c>
-      <c r="G101" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="H101" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="I101" s="3" t="s">
         <v>3</v>
       </c>
@@ -6145,11 +6642,11 @@
       <c r="N101" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="O101" s="3">
-        <v>0</v>
-      </c>
-      <c r="P101" s="3">
-        <v>0</v>
+      <c r="O101" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="P101" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="Q101" s="3">
         <v>0</v>
@@ -6172,69 +6669,81 @@
       <c r="W101" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="102" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X101" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y101" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="102" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>-1200</v>
+      </c>
+      <c r="E102" s="3">
+        <v>-1200</v>
+      </c>
+      <c r="F102" s="3">
         <v>2600</v>
       </c>
-      <c r="E102" s="3">
+      <c r="G102" s="3">
         <v>2600</v>
       </c>
-      <c r="F102" s="3">
+      <c r="H102" s="3">
         <v>3800</v>
       </c>
-      <c r="G102" s="3">
+      <c r="I102" s="3">
         <v>3800</v>
       </c>
-      <c r="H102" s="3">
+      <c r="J102" s="3">
         <v>3300</v>
       </c>
-      <c r="I102" s="3">
+      <c r="K102" s="3">
         <v>3300</v>
       </c>
-      <c r="J102" s="3">
+      <c r="L102" s="3">
         <v>-1800</v>
       </c>
-      <c r="K102" s="3">
-        <v>0</v>
-      </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
+        <v>0</v>
+      </c>
+      <c r="N102" s="3">
         <v>2500</v>
       </c>
-      <c r="M102" s="3">
+      <c r="O102" s="3">
         <v>-2600</v>
       </c>
-      <c r="N102" s="3">
+      <c r="P102" s="3">
         <v>-2200</v>
       </c>
-      <c r="O102" s="3">
+      <c r="Q102" s="3">
         <v>10700</v>
       </c>
-      <c r="P102" s="3">
+      <c r="R102" s="3">
         <v>600</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="S102" s="3">
         <v>-5100</v>
       </c>
-      <c r="R102" s="3">
+      <c r="T102" s="3">
         <v>100</v>
       </c>
-      <c r="S102" s="3">
+      <c r="U102" s="3">
         <v>-2400</v>
       </c>
-      <c r="T102" s="3">
+      <c r="V102" s="3">
         <v>-4200</v>
       </c>
-      <c r="U102" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="V102" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="W102" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="X102" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Y102" s="3" t="s">
         <v>3</v>
       </c>
     </row>
